--- a/backend/files/TNP.xlsx
+++ b/backend/files/TNP.xlsx
@@ -1,50 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edu\Dropbox\ConsIA\BOOKS to Cons-IA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471FA04A-6556-460E-BB80-9A89DC6664C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38B6B0FF-51CB-4A85-B8B6-B790CB5CF658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="4536" windowWidth="41640" windowHeight="18540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25416" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Capítulos" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="378">
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
   <si>
     <t>**Manual.** Este volume é o *“livro sobre a tenepes”* que muitos colegas, colaboradores, energizadores, projeciólogos e conscienciólogos cobraram deste autor, nestas últimas 2 décadas.</t>
   </si>
   <si>
+    <t>INTRODUÇÃO</t>
+  </si>
+  <si>
     <t>**Pesquisas.** O *Manual* foi redigido a partir de notas pessoais, desde 1950; de pesquisas com praticantes adultos – homens e mulheres – das tarefas energéticas pessoais; e das perguntas e respostas colhidas nos *“Cursos da Tenepes”,* ministrados nos últimos tempos, através das programações didáticas do Instituto Internacional de Projeciologia e Conscienciologia (IIPC), em localidades diversas.</t>
   </si>
   <si>
     <t>**Paratecnologia.** Este livro, dedicado à execução de experimentos transcendentes, parapsíquicos, projetivos ou anímicos, enquadra-se numa área das pesquisas e recursos de ponta da alta *paratecnologia da consciência.*</t>
   </si>
   <si>
-    <t>**Variáveis.** Você – leitor que se depara com o assunto pela primeira vez – *não deve perder tempo* com este manual prático, *se não admite,* sem dúvidas mortificantes, estas 5 variáveis:|**1. EC.** A existência – bem definida por você – da *energia consciencial (EC),* além dos impulsos nervosos do corpo humano.|**2. Animismo.** As manifestações anímicas, benignas e evolutivas, além das crendices, delírios e tradições folclóricas.|**3. Parapsiquismo.** As *manifestações parapsíquicas* (mediúnicas, interdimensionais ou *paranormais*) sadias.|**4. Interassistencialidade.** A necessidade evolutiva de as consciências humanas se auxiliarem umas às outras, por intermédio de *trabalhos interassistenciais* lógicos, justos e maduros.|**5. Interdimensionalidade.** As comunicações interconscienciais entre as muitas *dimensões das consciências* intra e extrafísicas.</t>
+    <t>**Variáveis.** Você – leitor que se depara com o assunto pela primeira vez – *não deve perder tempo* com este manual prático, *se não admite,* sem dúvidas mortificantes, estas 5 variáveis: | **1. EC.** A existência – bem definida por você – da *energia consciencial (EC),* além dos impulsos nervosos do corpo humano. | **2. Animismo.** As manifestações anímicas, benignas e evolutivas, além das crendices, delírios e tradições folclóricas. | **3. Parapsiquismo.** As *manifestações parapsíquicas* (mediúnicas, interdimensionais ou *paranormais*) sadias. | **4. Interassistencialidade.** A necessidade evolutiva de as consciências humanas se auxiliarem umas às outras, por intermédio de *trabalhos interassistenciais* lógicos, justos e maduros. | **5. Interdimensionalidade.** As comunicações interconscienciais entre as muitas *dimensões das consciências* intra e extrafísicas.</t>
   </si>
   <si>
     <t>**Recursos.** O melhor, com lógica, neste caso, será deixar para enfrentar tais assuntos quando já tiver experimentado, por você mesmo, os recursos conscienciais enumerados, de modo tranquiloe sem os sobressaltos das controvérsias, dentro de uma inevitável microminoria intrafísica, social, cultural, discernidora.</t>
@@ -53,7 +49,7 @@
     <t>**Predisposição.** Este volume de experimentos não evidencia qualquer pretensão do autor-informador de persuadir alguém. É tão-só um código prático para *quem esteja predisposto ao tema.* Eis por que se você não se enquadra, dentro de si mesmo, nestas condições, o mais inteligente é adiar o seu desenvolvimento consciencial, energético, assistencial para mais tarde ou mesmo para as diretrizes intrafísicas de outra programação existencial (proéxis), um curso intermissivo melhor e com *outro soma* à frente, em novo estágio na serialidade das vidas humanas sucessivas.</t>
   </si>
   <si>
-    <t>**Verdade.** A maturidade consciencial expõe, com lógica, que toda verdade relativa de ponta, quando magna, é precedida por 3 ocorrências de discernimento, muito além da boa vontade e da boa intenção:|**1. Entropia.** Provoca *antes* a expansão da entropia (autodesorganização, indisciplina pessoal) próxima, para *depois* diminuir a entropia em geral.|**2. Estresse.** Gera *antes* estresse doentio, incômodo, a crise de crescimento dentro do imediatismo no aqui-e-agora multidimensional, para *depois* gerar estresse pessoal, sadio e libertador.|**3. Neofobia.** Irrita *antes,* dentro da condição da neofobia instintiva (o medo quanto às coisas novas, de vanguarda), para *depois* aumentar a neofilia evoluída ou o gosto e a gratificação pelas descobertas evolutivas, o ânimo e a motivação0 para o autoconhecimento disciplinado.</t>
+    <t>**Verdade.** A maturidade consciencial expõe, com lógica, que toda verdade relativa de ponta, quando magna, é precedida por 3 ocorrências de discernimento, muito além da boa vontade e da boa intenção: | **1. Entropia.** Provoca *antes* a expansão da entropia (autodesorganização, indisciplina pessoal) próxima, para *depois* diminuir a entropia em geral. | **2. Estresse.** Gera *antes* estresse doentio, incômodo, a crise de crescimento dentro do imediatismo no aqui-e-agora multidimensional, para *depois* gerar estresse pessoal, sadio e libertador. | **3. Neofobia.** Irrita *antes,* dentro da condição da neofobia instintiva (o medo quanto às coisas novas, de vanguarda), para *depois* aumentar a neofilia evoluída ou o gosto e a gratificação pelas descobertas evolutivas, o ânimo e a motivação0 para o autoconhecimento disciplinado.</t>
   </si>
   <si>
     <t>**Procedência.** A tenepes é a única técnica mais eficaz – conhecida e exercida por este autor em cerca de meio século de experiências parapsíquicas, e, agora, decodificada tecnicamente – para manter o ser humano (conscin) ligado à sua procedência consciencial, evolutiva, extrafísica, além da troposfera terrestre, e sem sujeições espúrias a quaisquer causas temporais ou intrafísicas.</t>
@@ -80,7 +76,10 @@
     <t>**Definição.** *Tenepes* (*t*arefa *ene*rgética *pes*soal) é a transmissão de energia consciencial (EC), assistencial, individual; programada com horário diário, da consciência humana, auxiliada por amparador ou amparadores; no estado da vigília física ordinária; diretamente para consciexes carentes ou enfermas, intangíveis e invisíveis à visão humana comum; ou conscins projetadas, ou não, próximas ou à distância, também carentes ou enfermas.</t>
   </si>
   <si>
-    <t>**Sinonímia.** Eis 9 expressões empregadas para caracterizar a prática da tenepes:|*1. Megadesafio* para o ser humano.|2. Passe energético no *paciente desconhecido.|3. Passes para o escuro.|4. Passividade parapsíquica* solitária.|*5. Psicogrupo unitário.|6. Semipossessão benigna assistencial.|*7. Serviço da *compensação energética.|8. Sessão energético-anímico-parapsíquica* individual.|*9. Sessão parapsíquica* ou mediúnica do eu sozinho.</t>
+    <t>1. DEFINIÇÕES</t>
+  </si>
+  <si>
+    <t>**Sinonímia.** Eis 9 expressões empregadas para caracterizar a prática da tenepes: | *1. Megadesafio* para o ser humano. | 2. Passe energético no *paciente desconhecido.* | *3. Passes para o escuro.* | *4. Passividade parapsíquica* solitária. | *5. Psicogrupo unitário.* | *6. Semipossessão benigna assistencial.* | 7. Serviço da *compensação energética.* | *8. Sessão energético-anímico-parapsíquica* individual. | *9. Sessão parapsíquica* ou mediúnica do eu sozinho.</t>
   </si>
   <si>
     <t>A PRÁTICA DA TENEPES É PRESTAÇÃO DE SERVIÇO ENERGÉTICO-ASSISTENCIAL NÃO-REMUNERADO.</t>
@@ -92,7 +91,7 @@
     <t>O PRATICANTE DA TENEPES É UM PIÃO INTERDIMENSIONAL.</t>
   </si>
   <si>
-    <t>**Denominações.** Quem desenvolve diariamente as tarefas energéticas pessoais, nos moldes analisados neste volume, em geral recebe 6 denominações diversas:|*1. Assistente interconsciencial* diário (homem ou mulher).|*2. Energizador* ou energizadora consciencial.|*3. Epicon* autoconsciente (homem ou mulher).|*4. Passista para o escuro* (homem ou mulher).|*5. Pião interdimensional* (homem ou mulher).|*6. Praticante da tenepes* (a expressão mais comum que significa, aqui, **o** praticante-homem ou **a** praticante-mulher).</t>
+    <t>**Denominações.** Quem desenvolve diariamente as tarefas energéticas pessoais, nos moldes analisados neste volume, em geral recebe 6 denominações diversas: | *1. Assistente interconsciencial* diário (homem ou mulher). | *2. Energizador* ou energizadora consciencial. | *3. Epicon* autoconsciente (homem ou mulher). | *4. Passista para o escuro* (homem ou mulher). | *5. Pião interdimensional* (homem ou mulher). | *6. Praticante da tenepes* (a expressão mais comum que significa, aqui, **o** praticante-homem ou **a** praticante-mulher).</t>
   </si>
   <si>
     <t>**Mó.** Busquemos entender com lógica: o praticante da tenepes, na qualidade de epicon, interconsciencial, é a *mó do moinho* do trabalho no maximecanismo energético, multidimensional, assistencial.</t>
@@ -101,6 +100,9 @@
     <t>**Histórico.** A tenepes instintiva, fetal, empírica e sem técnica sempre existiu de maneira esboçante entre as consciências humanas despertas para a multidimensionalidade, desde tempos imemoriais, práticas estas agravadas e *poluídas* pelas intrusões dos misticismos, arquétipos, *lavagens cerebrais,* condicionamentos intrafísicos, sacralizações, insuficiências humanas e repressões sociais de todos os tipos culturais.</t>
   </si>
   <si>
+    <t>2. HISTÓRICO DA TENEPES</t>
+  </si>
+  <si>
     <t>**Lançamento.** A tenepes foi lançada, de fato, ao grande público em 1966, conforme o registro feito no livro *“700 Experimentos da Conscienciologia”,* página 958.</t>
   </si>
   <si>
@@ -131,19 +133,31 @@
     <t>A TENEPES É UMA PRÁTICA EXTRA-HUMANA DA CONSCIÊNCIA INTRAFÍSICA.</t>
   </si>
   <si>
-    <t>**Extra-humanas.** Existem outras *práticas extra-humanas* que nenhum órgão ou instituição humana, repartição ou autarquia, cobra impostos ou fiscaliza o praticante, por exemplo, estas 5:|1. Execução da *proéxis.|2. Ofiex* ou oficina extrafísica*.|3. Sinalética* energético-anímico-parapsíquica.|*4. Estado vibracional* (EV).|*5. Projeção consciente* magna*.*</t>
+    <t>**Extra-humanas.** Existem outras *práticas extra-humanas* que nenhum órgão ou instituição humana, repartição ou autarquia, cobra impostos ou fiscaliza o praticante, por exemplo, estas 5: | 1. Execução da *proéxis.* | *2. Ofiex* ou oficina extrafísica. | *3. Sinalética* energético-anímico-parapsíquica. | *4. Estado vibracional* (EV). | *5. Projeção consciente* magna.</t>
   </si>
   <si>
     <t>**Cosmoética.** A vivência da cosmoética é o fiscal das práticas e do desenvolvimento natural da tenepes, ínsito na pessoa, através do convívio com os amparadores.</t>
   </si>
   <si>
-    <t>**Facetas.** As várias facetas, traços, trafores e trafares das conscins podem classificá-las em 2 grupos básicos de 23 tipos cada um, quanto à tenepes (Conscins Pró-Tenepes X Conscins Antitenepes): ***Homo amicus Homo animalis Homo arbiter Homo artifex Homo divinans Homo bellicosus Homo duplex Homo civicus Homo fraternus Homo competitor Homo habilis Homo erectus Homo humanus Homo eroticus Homo idealis Homo theatralis Homo informaticus Homo faber Homo intellegens Homo genuflexus Homo invulgaris Homo loquax Homo laboriosus Homo hostilis Homo logicus Homo ludens Homo pacificus Homo maniacus Homo projectius Homo mercurialis Homo psychicus Homo politicus Homo sanus Homo signifex Homo sapiens Homo mythicus Homo sapientor Homo stultus Homo socialis Homo supersticiosus Homo spiritualis Homo sportivus Homo tecnicus Homo viator Homo universalis Homo submissus***</t>
+    <t>**Facetas.** As várias facetas, traços, trafores e trafares das conscins podem classificá-las em 2 grupos básicos de 23 tipos cada um, quanto à tenepes:</t>
+  </si>
+  <si>
+    <t>3. CONSCINS</t>
+  </si>
+  <si>
+    <t>CONSCINS PRÓ-TENEPES CONSCINS ANTITENEPES</t>
+  </si>
+  <si>
+    <t>***Homo amicus Homo animalis Homo arbiter Homo artifex Homo divinans Homo bellicosus Homo duplex Homo civicus Homo fraternus Homo competitor Homo habilis Homo erectus Homo humanus Homo eroticus Homo idealis Homo theatralis Homo informaticus Homo faber Homo intellegens Homo genuflexus Homo invulgaris Homo loquax Homo laboriosus Homo hostilis Homo logicus Homo ludens Homo pacificus Homo maniacus Homo projectius Homo mercurialis Homo psychicus Homo politicus Homo sanus Homo signifex Homo sapiens Homo mythicus Homo sapientor Homo stultus Homo socialis Homo supersticiosus Homo spiritualis Homo sportivus Homo tecnicus Homo viator Homo universalis Homo submissus***</t>
   </si>
   <si>
     <t>VOCÊ É UMA CONSCIÊNCIA HUMANA PRÓ-TENEPES OU ANTITENEPES?</t>
   </si>
   <si>
-    <t>**Paradoxos.** Dentre as maiores demonstrações de autossuficiência da conscin destacam-se, por exemplo, 4 *técnicas conscienciológicas paradoxais,* porque se assentam em inevitáveis condições de interdependência, junto a outras consciências:|**1. Tenepes,** ou a tarefa energética pessoal, diária, prática que depende também dos amparadores.|**2. Ofiex,** ou a oficina extrafísica de assistência interconsciencial e interdimensional, cujo funcionamento avançado depende também dos amparadores.|**3. Compléxis,** ou o completismo existencial da proéxis, cuja obtenção depende de nossa relação geral com o grupo evolutivo ou grupocarma.|**4. Moréxis,** ou a moratória existencial, condição que depende do Orientador Evolutivo, até um certo grau.</t>
+    <t>**Paradoxos.** Dentre as maiores demonstrações de autossuficiência da conscin destacam-se, por exemplo, 4 *técnicas conscienciológicas paradoxais,* porque se assentam em inevitáveis condições de interdependência, junto a outras consciências: | **1. Tenepes,** ou a tarefa energética pessoal, diária, prática que depende também dos amparadores. | **2. Ofiex,** ou a oficina extrafísica de assistência interconsciencial e interdimensional, cujo funcionamento avançado depende também dos amparadores. | **3. Compléxis,** ou o completismo existencial da proéxis, cuja obtenção depende de nossa relação geral com o grupo evolutivo ou grupocarma. | **4. Moréxis,** ou a moratória existencial, condição que depende do Orientador Evolutivo, até um certo grau.</t>
+  </si>
+  <si>
+    <t>4. PARADOXOS</t>
   </si>
   <si>
     <t>NA PRÁTICA DA TENEPES, O INDIVIDUALISMO INTRAFÍSICO ATUA DENTRO DE UMA GRUPALIDADE INTERDIMENSIONAL.</t>
@@ -152,16 +166,19 @@
     <t>**Fundamentos.** Neste capítulo procuramos estabelecer algumas associações de ideias e comparações didáticas a fim de clarear e definir mais nitidamente os fundamentos das práticas da tenepes.</t>
   </si>
   <si>
+    <t>5. COMPARAÇÕES</t>
+  </si>
+  <si>
     <t>**Cosmoconsciência.** O estado físico, psíquico ou parapsíquico do praticante da tenepes durante as transmissões energéticas assistenciais, pode ser comparado a uma condição de cosmoconsciência, própria e *dentro* do estado da vigília física ordinária.</t>
   </si>
   <si>
-    <t>**Assistencialidade.** O nível percentual da possibilidade de assistência energética interconsciencial – através das ECs – que certas condições de afinizações permitem é, logicamente, bem diverso, por exemplo, numa escala crescente: |1. Casal incompleto = X.|2. Casal íntimo = XX.|3. Entrosamento praticante-amparador = XXX.</t>
+    <t>**Assistencialidade.** O nível percentual da possibilidade de assistência energética interconsciencial – através das ECs – que certas condições de afinizações permitem é, logicamente, bem diverso, por exemplo, numa escala crescente: | 1. Casal incompleto = X. | 2. Casal íntimo = XX. | 3. Entrosamento praticante-amparador = XXX.</t>
   </si>
   <si>
     <t>**Dupla.** Este quadro dos entrosamentos interconscienciais explica enfaticamente a superioridade crítica do comprometimento entre o praticante da tenepes e o amparador assistencial (2 *profissionais*) sobre a condição evoluída da dupla evolutiva (*literalmente:* sempre 2 amadores).</t>
   </si>
   <si>
-    <t>**Multidimensionalidade.** Eis 9 constatações quanto à multidimensionalidade ou a interdimensionalidade, *entre as dimensões* conscienciais: |**1. Maturidade.** A maturidade consciencial maior é interdimensional.|**2. Cosmoética.** A cosmoética é interdimensional.|**3. Carisma.** O carisma (energia consciencial) transcendente, máximo, é interdimensional.|**4. Projetabilidade.** Toda a projetabilidade da consciência é interdimensional.|**5. Universalismo.** Todo o universalismo puro com a cosmovisão maior da consciência é interdimensional.|**6. Tares.** A tares, tarefa assistencial do esclarecimento, abre as portas da vida interdimensional à conscin desperta.|**7. Policarmalidade.** A policarmalidade evoluída, além ou mais avançada do que o egocarma e o grupocarma, é interdimensional.|**8. Serenismo.** O serenismo vivido é interdimensional.|**9. Tenepes.** A tarefa energética pessoal, diária, é interdimensional.</t>
+    <t>**Multidimensionalidade.** Eis 9 constatações quanto à multidimensionalidade ou a interdimensionalidade, *entre as dimensões* conscienciais: | **1. Maturidade.** A maturidade consciencial maior é interdimensional. | **2. Cosmoética.** A cosmoética é interdimensional. | **3. Carisma.** O carisma (energia consciencial) transcendente, máximo, é interdimensional. | **4. Projetabilidade.** Toda a projetabilidade da consciência é interdimensional. | **5. Universalismo.** Todo o universalismo puro com a cosmovisão maior da consciência é interdimensional. | **6. Tares.** A tares, tarefa assistencial do esclarecimento, abre as portas da vida interdimensional à conscin desperta. | **7. Policarmalidade.** A policarmalidade evoluída, além ou mais avançada do que o egocarma e o grupocarma, é interdimensional. | **8. Serenismo.** O serenismo vivido é interdimensional. | **9. Tenepes.** A tarefa energética pessoal, diária, é interdimensional.</t>
   </si>
   <si>
     <t>**Disponibilidade.** A tenepes é a disponibilidade *pessoal* máxima para *o que der e vier* em prol da *impessoalidade* também máxima, dentro da assistência interconsciencial e multidimensional, na condição de obrigação regular, padronizada e definitiva para o resto da vida humana.</t>
@@ -200,7 +217,7 @@
     <t>**Transcendência.** Os fatos assistenciais decorrentes das práticas da tenepes são didáticos, evoluídos, transcendentes demais para a consciência intrafísica acomodar-se a uma mediocridade ainda subumana ou submissa, ao *subcérebro abdominal.*</t>
   </si>
   <si>
-    <t>**Epicon.** O praticante da tenepes, com o desenvolvimento dos seus exercícios, no passar do tempo, torna-se veterano ou o epicon – epicentro consciencial – na assistência interconsciencial, através de 6 condições pelo menos:|**1. Segurança.** Ponto de segurança autoconsciente.|**2. Apoio.** Ponto de apoio interconsciencial.|**3. Arrimo.** Arrimo energético onímodo ou multifacetado.|**4. Polo.** Polo de desassédio consciente.|**5. Minipeça.** *Mini*peça autoconsciente do *maxi*mecanismo intra e extrafísico assistencial.|**6. Embaixador.** Embaixador *intra*físico do Orientador Evolutivo *extra*físico.</t>
+    <t>**Epicon.** O praticante da tenepes, com o desenvolvimento dos seus exercícios, no passar do tempo, torna-se veterano ou o epicon – epicentro consciencial – na assistência interconsciencial, através de 6 condições pelo menos: | **1. Segurança.** Ponto de segurança autoconsciente. | **2. Apoio.** Ponto de apoio interconsciencial. | **3. Arrimo.** Arrimo energético onímodo ou multifacetado. | **4. Polo.** Polo de desassédio consciente. | **5. Minipeça.** *Mini*peça autoconsciente do *maxi*mecanismo intra e extrafísico assistencial. | **6. Embaixador.** Embaixador *intra*físico do Orientador Evolutivo *extra*físico.</t>
   </si>
   <si>
     <t>O ORIENTADOR EVOLUTIVO É O SUPERAMPARADOR EXTRAFÍSICO DO GRUPOCARMA.</t>
@@ -209,6 +226,9 @@
     <t>**Preparação.** Na tenepes, você, na condição de conscin parapsíquica, homem ou mulher, sozinho intrafisicamente, se acomoda no leito, de preferência no escuro, relaxa, pacifica a mente, e dá passividade parapsíquica e psicomotora (mental e muscular) ao amparador extrafísico, especialista na assistência interconsciencial.</t>
   </si>
   <si>
+    <t>6. TÉCNICA DA TENEPES</t>
+  </si>
+  <si>
     <t>**Semipossessão.** Sobrevem, então, o fenômeno da possessão ou semipossessão interconsciencial, parafisiológica, benigna ou sadia, para a transmissão das energias conscienciais com o praticante sentado no leito, recostado numa poltrona, ou de pé (ereto).</t>
   </si>
   <si>
@@ -284,7 +304,7 @@
     <t>**Começos.** A conscin *começa* a se libertar dos ciclos multiexistenciais quando *começa* a dar bons exemplos extrafísicos. A tenepes predispõe esses 2 começos simultâneos.</t>
   </si>
   <si>
-    <t>**Trinômio.** Existe um *trinômio assistencial,* interconsciencial, bem evidente, que se manifesta em um crescendo, sendo que cada componente específico depende do outro: |**1. Tacon** ou tarefa assistencial da consolação.|**2. Tares** ou tarefa assistencial do esclarecimento.|**3. Tenepes** ou tarefa energética, assistencial, diária, pessoal.</t>
+    <t>**Trinômio.** Existe um *trinômio assistencial,* interconsciencial, bem evidente, que se manifesta em um crescendo, sendo que cada componente específico depende do outro: | **1. Tacon** ou tarefa assistencial da consolação. | **2. Tares** ou tarefa assistencial do esclarecimento. | **3. Tenepes** ou tarefa energética, assistencial, diária, pessoal.</t>
   </si>
   <si>
     <t>**Holopensene.** Tentar implantar a prática diária da tenepes pela conscin ainda muito jovem, sem os alicerces da existência bem-consolidados, em razão da *pressão holopensênica* (influência mesológica, *porão consciencial,* autoinexperiência, *subcérebro abdominal*), é o mesmo que tentar fazer uma *sessão de musicoterapia* em pleno campo de guerra. A conscin escutará a música e, ao mesmo tempo, as balas de canhão silvando em seus ouvidos, ou paraouvidos.</t>
@@ -299,19 +319,25 @@
     <t>**Dupla.** A dupla evolutiva pode desenvolver as práticas da tenepes no *mesmo lugar,* até na *mesma cama,* desde que *não seja* no *mesmo horário* ou conjuntamente.</t>
   </si>
   <si>
-    <t>**Impossibilidades.** Eis, resumidamente, 9 variáveis, ou mais apropriadamente, 9 impossibilidades reais para o desenvolvimento sadio das práticas da tenepes:|**1.** **Assedialidade.** Condição de vítima de assédio interconsciencial cronicificado do praticante.|**2. Autocorrupção.** Autocorrupção por parte do praticante homem ou mulher.|**3. Divórcio.** Divórcio por parte do praticante quanto ao amparador.|**3. Estagnação.** Estagnação da consciência do praticantedesmotivado, uma prática de *auto-obcecação* ou mau hábito.|4. **Idolatrias.** Cultivo de idolatrias e sectarismos arraigados por parte do praticante da tenepes, uma posição calcada no *subcérebro abdominal.|***5. Intenção.** O ato de *pensar mal* dos outros (má intenção) por parte do praticante, uma condição anticosmoética grosseira.|**6. Soma.** O soma do praticante acometido de doença grave ou invalidante.|**7. Testemunha.** O praticante permitir qualquer testemunha humana presente no quarto, cômodo ou recinto, onde desenvolve as suas práticas, ou durante as assistências através da tenepes.|**8. Volta.** O praticante desejar voltar atrás em suas resoluções assistenciais depois de iniciadas as suas práticas. A fim de se desenvolver, a tenepes há de ser encarada com inteligência, de modo definitivo, sem a possibilidade de quaisquer acordos autocorruptores ou pactos espúrios, desde o primeiro momento, ao modo de *um caminho de abnegação sem volta* ou um empreendimento libertário sem retorno.</t>
+    <t>**Impossibilidades.** Eis, resumidamente, 9 variáveis, ou mais apropriadamente, 9 impossibilidades reais para o desenvolvimento sadio das práticas da tenepes: | **1. Assedialidade.** Condição de vítima de assédio interconsciencial cronicificado do praticante. | **2. Autocorrupção.** Autocorrupção por parte do praticante homem ou mulher. | **3. Divórcio.** Divórcio por parte do praticante quanto ao amparador. | **3. Estagnação.** Estagnação da consciência do praticantedesmotivado, uma prática de *auto-obcecação* ou mau hábito. | 4. **Idolatrias.** Cultivo de idolatrias e sectarismos arraigados por parte do praticante da tenepes, uma posição calcada no *subcérebro abdominal.* | **5. Intenção.** O ato de *pensar mal* dos outros (má intenção) por parte do praticante, uma condição anticosmoética grosseira. | **6. Soma.** O soma do praticante acometido de doença grave ou invalidante. | **7. Testemunha.** O praticante permitir qualquer testemunha humana presente no quarto, cômodo ou recinto, onde desenvolve as suas práticas, ou durante as assistências através da tenepes. | **8. Volta.** O praticante desejar voltar atrás em suas resoluções assistenciais depois de iniciadas as suas práticas. A fim de se desenvolver, a tenepes há de ser encarada com inteligência, de modo definitivo, sem a possibilidade de quaisquer acordos autocorruptores ou pactos espúrios, desde o primeiro momento, ao modo de *um caminho de abnegação sem volta* ou um empreendimento libertário sem retorno.</t>
   </si>
   <si>
     <t>NÃO SE PERMITEM TESTEMUNHAS HUMANAS NAS PRÁTICAS DA TENEPES.</t>
   </si>
   <si>
-    <t>**Antecipação.** Eis 3 condições técnicas mais propícias à antecipação útil das vivências ou práticas da tenepes: |1. **Invéxis.** A invéxis ou a condição da inversão existencial autoconsciente, pelo jovem – moça ou rapaz – interessado, é a condição factível mais conhecida, até o momento, que permite antecipar as práticas da tenepes para a *fase preparatória* da proéxis, até os 35 anos de idade física, antes da *fase executiva,* a partir (em média) dos 36 anos de idade. O(a) interessado(a), neste caso, deve recorrer aos *grinvexes* ou grupos de inversores existenciais.|**2. Itinerância.** A vivência da itinerância do colaborador, colaboradora, professor ou professora de Projeciologia e Conscienciologia, nos moldes da empregada pela administração do Instituto Internacional de Projeciologia e Conscienciologia, pode ser o prólogo, a preparação, o primeiro estágio ou a antecâmara da prática da tenepes.|**3. Recéxis.** Em certos casos de *recéxis,* ou reciclagem existencial, quando precoce, em alto nível, pode acontecer também a antecipação das práticas da tenepes. O(a) interessado(a), neste caso, deve recorrer aos *grecexes* ou grupos de reciclantes existenciais.</t>
+    <t>**Antecipação.** Eis 3 condições técnicas mais propícias à antecipação útil das vivências ou práticas da tenepes: | 1. **Invéxis.** A invéxis ou a condição da inversão existencial autoconsciente, pelo jovem – moça ou rapaz – interessado, é a condição factível mais conhecida, até o momento, que permite antecipar as práticas da tenepes para a *fase preparatória* da proéxis, até os 35 anos de idade física, antes da *fase executiva,* a partir (em média) dos 36 anos de idade. O(a) interessado(a), neste caso, deve recorrer aos *grinvexes* ou grupos de inversores existenciais. | **2. Itinerância.** A vivência da itinerância do colaborador, colaboradora, professor ou professora de Projeciologia e Conscienciologia, nos moldes da empregada pela administração do Instituto Internacional de Projeciologia e Conscienciologia, pode ser o prólogo, a preparação, o primeiro estágio ou a antecâmara da prática da tenepes. | **3. Recéxis.** Em certos casos de *recéxis,* ou reciclagem existencial, quando precoce, em alto nível, pode acontecer também a antecipação das práticas da tenepes. O(a) interessado(a), neste caso, deve recorrer aos *grecexes* ou grupos de reciclantes existenciais.</t>
+  </si>
+  <si>
+    <t>7. ANTECIPAÇÃO DA TENEPES</t>
   </si>
   <si>
     <t>**Abnegação.** O primeiro passo da abnegação do praticante da tenepes é iniciar a tarefa energética, diária, com a liberação de energias conscienciais, de modo consciente, tranquilo, o mais benigno possível, em favor de todos aqueles que não o entenderam, que ele *não tenha tratado bem,* ou com quem se desentendeu de maneira antifraterna, durante as últimas 24 horas.</t>
   </si>
   <si>
-    <t>**Contatos.** Esta providência – das mais evoluídas do praticante da tenepes – consiste em perpassar pela memória a imagem das *conscins e consciexes* de todos os contatos interconscienciais do dia, de 4 tipos bem característicos, mentalizando um banho de energias envolvendo a consciência, com a intenção sincera de colocá-la em *estado de graça,* na melhor condição, ideal, possível, aos seus olhos:|**1. Contatos diretos físicos:** cumprimentos, encontros, conversas, visitas, entrevistas, companhias de veículo ou condução, e outros.|**2. Contatos indiretos eletroeletrônicos:** telefone, interfone, fax, fax/modem, e outros.|**3. Contatos indiretos mentais:** cartas escritas, telegramas, evocações conscientes e inconscientes, reminiscências, e outros.|**4. Contatos diretos extrafísicos:** encontros extrafísicos por meio de projeções conscienciais lúcidas, e outros.</t>
+    <t>8. CONTATOS DIÁRIOS</t>
+  </si>
+  <si>
+    <t>**Contatos.** Esta providência – das mais evoluídas do praticante da tenepes – consiste em perpassar pela memória a imagem das *conscins e consciexes* de todos os contatos interconscienciais do dia, de 4 tipos bem característicos, mentalizando um banho de energias envolvendo a consciência, com a intenção sincera de colocá-la em *estado de graça,* na melhor condição, ideal, possível, aos seus olhos: | **1. Contatos diretos físicos:** cumprimentos, encontros, conversas, visitas, entrevistas, companhias de veículo ou condução, e outros. | **2. Contatos indiretos eletroeletrônicos:** telefone, interfone, fax, fax/modem, e outros. | **3. Contatos indiretos mentais:** cartas escritas, telegramas, evocações conscientes e inconscientes, reminiscências, e outros. | **4. Contatos diretos extrafísicos:** encontros extrafísicos por meio de projeções conscienciais lúcidas, e outros.</t>
   </si>
   <si>
     <t>**Assinaturas.** Esta providência de *assepsia das emoções* quanto aos contatos diários constitui a limpeza das assinaturas pensênicas *sujas* ou borradas, deixadas pelos rastros do praticante, durante as últimas 24 horas, por onde passou.</t>
@@ -323,31 +349,169 @@
     <t>A TENEPES É A VIVÊNCIA MÁXIMA DE TUDO O QUE SEJA SADIO PARA AS CONSCIÊNCIAS.</t>
   </si>
   <si>
-    <t>**Vivência.** A tenepes é o exercício por atacado, de uma vez, de modo permanente e de tudo o que a consciência sabe, ou especificamente de 7 fatores:|1. **Discernimento.** Possibilita ao praticante alcançar com discernimento a execução da proéxis, do compléxis e até da maximoréxis.|2. **Holochacralidade.** Oferece à consciência humana os meios de instalação do campo energético mais denso e permanente, ou a névoa sutil ou densificada, além da aura humana, vista por qualquer pessoa disposta, sobre homens, mulheres, meninos e meninas, nas mais diversas circunstâncias humanas.|**3. Holomaturidade.** Predispõe atingir a maturidade integrada, além da maturidade biológica e maturidade psicológica.|**4. Mentalsomática.** Faculta ao praticante o emprego em nível elevado dos atributos conscienciais, potencialidades individuais e mais de uma inteligência pessoal ao mesmo tempo (todos temos vários módulos de inteligência).|**5. Multidimensionalidade.** Conduz a conscin à desperticidade inevitável.|**6. Parapsiquismo.** Permite ao interessado ou interessada chegar à pangrafia lúcida.|**7. Praticidade.** Aponta os meios e os recursos para a execução vivencial mais raciocinada dos atos humanos e manifestações extrafísicas, enquanto na vida física, a fim de a conscin se aproveitar da dinâmica da consciência quanto à sua evolução mais lúcida.|</t>
-  </si>
-  <si>
-    <t>**Sensações.** Depois da atuação inconfundível de outra consciência extrafísica sobre os veículos de manifestação – no caso, o soma (corpo humano), o holochacra (corpo energético) e o psicossoma (corpo emocional) – da conscin praticante da tenepes; podem sobrevir, pelo menos, 33 ocorrências de vivência pessoal indiscutível, aqui enumeradas, no período preliminar ou inicial do *praticante-calouro* da tenepes, quando ele *levanta a poeira energética e multidimensional* em torno de si e de seus entes ou realidades mais queridas (homens, mulheres, meninos, meninas, subumanos, plantas e consciexes em multiformes níveis evolutivos):|**1. Assincronizações.** A interferência de assincronizações efêmeras entre os sons e as aspersões energéticas se deve à dificuldade da semipossessão benigna, ou ao entrosamento entre a mente da *conscin praticante* e a *consciex amparadora* responsável pela transmissão. O *amparador-possuidor* comanda, por exemplo, um braço e o *praticante-possuído* comanda o outro braço.|**2. Sincronizações.** Os sons das vibrações rítmicas na cabeça, durante as descargas energéticas, são sincrônicos com os movimentos de aspersões energéticas através dos braços e das mãos.|***3. Chacras.*** Depois de vários anos, os exercícios regulares, que não são sentidos como sacrifícios, mas diariamente aguardados com alegria íntima ou júbilo sincero, fazem o praticante perceber, no estado da vigília física ordinária, os chacras, notadamente 4 deles, ao mesmo tempo: **A. Sexochacra.** O sexochacra latejante como se o praticante estivesse sentado numa bola de fogo. É a chamada liberação da *kundalini,* muito estudada no Orientalismo. No caso, essa ocorrência é definitivamente sadia ou benigna. **B. Umbilicochacra.** O umbilicochacra ou todo o abdome energizado no sentido para a frente. Não raro, ao contrário, parece que o abdome se amolga ou adelgaça ao modo de uma fina folha de papel. **C. Frontochacra.** O frontochacra que parece pequeno, mas poderoso aparelho incrustado na testa, funcionante, discriminador, até uma certa distância. **D. Coronochacra.** O coronochacra com a impressionante sensação de dissolução da cabeça.|**4. Chama.** Não raro as exteriorizações de energia consciencial podem dar a impressão de que o soma (corpo humano) torna-se enorme chama, língua de fogo de uns 3 metros de altura, quentíssima na periferia e de núcleo gelado, a crepitar para a frente e para cima, e a reverberar como se fosse um foco de luz, expandindo-se e contraindo-se em movimentos para fora e para dentro, alternadamente, sob o comando de uma força intangível, poderosa, inteligente e controlada.|**5. Lança-chamas.** Durante a semipossessão benigna, o holochacra que vitaliza mais os braços e as mãos, parece um lança-chamas aspergindo, com aparente violência, as energias conscienciais para a frente através de descargas em ritmo acelerado e constante. Todo o processo aqui assemelha-se ao funcionamento de um centrifugador-consciencial-energético-interdimensional.|**6. Clarividências.** Clarividências diversas nas proximidades ou até mesmo clarividência viajora, com alto nível de lucidez.|**7. Desmaterializações.** Sensação de desmaterialização dos dedos das mãos e das próprias mãos.|**8. Entrosamento.** A primeira descarga energética, mais *receptora* para o conjunto praticante-transmissor extrafísico, do que *doadora* para a consciência receptora (consciex ou conscin projetada), estabelece o *entrosamento parapsíquico.|***9. Experiências.** O acúmulo das experiências diárias com a tenepes, é óbvio, melhora as performances e desempenhos do praticante dedicado e, com o tempo, os amparadores trazem consciexes enfermas mais perturbadas para abordá-lo diretamente no estado da vigília física ordinária ou mesmo quando se projeta com lucidez, fora do horário específico da tenepes. Ele atua, no caso, na condição de *isca assistencial consciente,* intra e extrafisicamente. Nesta altura, o *rapport* físico-extrafísico se intensifica e os resultados das transmissões energéticas melhoram até patamares inimagináveis.|**10. Extras.** Chegando o praticante da tenepes a um grau elevado de afinização com a consciex amparadora, transmissora, *titular,* mais permanente, de ECs, podem sobrevir exteriorizações energéticas extras ou emergenciais, ou seja: antes (principalmente), no período pré-tenepes, ou depois, no período pós-tenepes, diário, das transmissões, em momentos ou circunstâncias inesperadas. Isso acontece sem forçar física ou psiquicamente o praticante, mas de modo agradável, enriquecedor, saudável – que jamais trará qualquer conotação assediadora ou prejudicial – visando a atender consciexes enfermas em uma conjuntura crítica ou emergencial.|**11. Fenômenos.** A expansão do holochacra caracteriza os fenômenos sadios do *balonamento* e da *automicroscopia.|***12. Frio.** Sensação de ar frio, mais nas mãos, podendo, no entanto, tomar todo o corpo humano ou mesmo gelar o ambiente do quarto do praticante, independentemente da temperatura ambiental.|**13. Holochacra.** Durante as transmissões energéticas, às vezes o soma parece menor ou menos volumoso, devido à expansão do holochacra exteriorizado *(megabalonamento).|***14. Intensidade.** Eis um princípio prático: quanto *mais intensas* sejam as transmissões energéticas, *maior o bem-estar* do praticante no período de minutos ou horas, posterior às transmissões (período pós-tenepes).|**15. Intervalos.** O breve intervalo de tempo entre 1 transmissão energética e outra, serve para refazer fisiologicamente o praticante, reajustar o entrosamento praticante-amparador, bem como substituir a consciência receptora à frente ou à distância, sempre que necessário. O amparador, nesse período, em geral não perde o controle parapsíquico-mental-energético do processo. As sensações intensas do praticante podem desaparecer nos intervalos entre 1 descarga energética e outra, permanecendo ele na condição de *semipossuído* por parte do amparador durante as transmissões, e *semilivre* nos intervalos.|***16. Imagens.*** Nessa oportunidade, surgem imagens de força, inspiradas pelos amparadores, como, por exemplo, estas 3: **A. Galáxia.** A criação inicial incandescente de um sistema solar. **B. Usina.** A *corrida do aço* de um alto forno de usina. **C. Vulcão.** O mar de lavas vivas de um vulcão em erupção.|**17. Máquina.** Frequentemente, durante as transmissões energéticas, o praticante parece ouvir o pulsar de imensa máquina, como se estivesse com o corpo unificado, ou seja: o todo de seus veículos conscienciais (holossoma), acoplado a potentíssimo dínamo invisível, servindo de peça intermediária *(passe-partout)* a desconhecida máquina extrafísica.|**18. Oitava.** Em geral, uma descarga energética entre as 11, por exemplo, a oitava, pode ser perceptivelmente mais intensa ou mais potente do que as demais, em função dos trabalhos assistenciais em desenvolvimento.|**19. Ondas.** As transmissões, nas práticas da tenepes se fazem por ondas de ECs bem caracterizadas, percebidas pelo praticante, em geral de forma intermitente e não-contínua. As ondas de energias contínuas, quando ocorrem, denunciam uma circunstância terapêutica crítica ou uma injunção desassediadora singular, e tende a serem efêmeras, à semelhança de um pico extraordinário ou esporádico de exteriorização de energias assistenciais.|**20. Projeções.** Projeções conscienciais lúcidas de modalidades e consequências práticas, úteis, para os assistidos e o praticante, as mais diversas.|**21. Pruridos.** Um dos primeiros indícios da manifestação dos fenômenos de efeitos intrafísicos, mas parapsíquicos, ou exteriorização indiscutível de ectoplasma, é o surgimento não habitual de pruridos nas mucosas nasais, ou mais claramente, coceiras inoportunasno interior das fossas nasais, apenas durante as práticas da tenepes. Isso se deve à saída inicial de ectoplasma através das mucosas dos orifícios do corpo humano.|**22. Psicofonia.** O monólogo psicofônico é a fala direta da consciex comunicante (neste caso, o amparador), durante a psicofonia, para a conscin proprietária do soma, temporariamente descoincidida ou projetada (neste caso, o praticante durante as práticas da tenepes). Como se observa, o monólogo psicofônico é uma inversão transcendente e rara de condições, posições de consciências e manifestações interconscienciais.|**23. Pulsações.** Pulsações energéticas cerebrais. Importa observar que fisiologicamente o cérebro não pulsa por si, por exemplo, igual ao coração. Neste caso, as sensações bizarras são mesmo de *pulsações* dentro da cabeça. Relativamente a essas sensações e à maioria das referidas aqui, somente tendo as experiências, pessoalmente, é que o praticante pode aquilatar melhor os seus detalhes e efeitos sadios, com o tempo e a expansão da sua desenvoltura nas práticas assistenciais.|**24. Qualidade.** O tempo não representa fator relevante nas descargas energéticas, importando muito mais a qualidade e a potencialidade das energias conscienciais transmitidas.|**25. Ritmos.** Não raro, o ritmo intenso e variado das descargas energéticas, os movimentos físicos, e as contrações musculares não alteram praticamente em nada o *ritmo cardíaco* do praticante. Tal fato, por si só, constitui fenômeno subjetivo, concomitante, à parte.|***26. Independência.*** A rigor, a frequência – sempre perceptível – das transmissões energéticas do praticante, não se subordina a estas 4 variáveis: **A. Volição.** Nem à sua *vontade* ou à volição, incluindo-se, aqui, a intenção ou intencionalidade. B**. Circulação.** Nem aos seus *batimentos cardíacos* que mantêm a circulação sanguínea, sendo a área mais exigente e importante a correspondente aos dois hemisférios cerebrais. **C. Respiração.** Nem à sua *frequência respiratória* que mantém a sua *alimentação de oxigênio,* em conexão direta com o cardiochacra. **D. Tempo.** Nem ao andamento dos *segundos do relógio* comum que marca o tempo cronológico ou humano.|**27. Ordenações.** Tudo acontece sob a superintendência das ordenações parapsíquicas ou energético-anímico-mediúnico-motrizes da consciex transmissora básica, não obstante todo o conjunto de transmissão parecer estar acoplado a poderosos aparelhos extrafísicos ainda desconhecidos neste estágio de nossos conhecimentos de vanguarda. Podem ocorrer 4 a 5 ritmos de *transmissões energéticas,* bem diferentes uns dos outros, numa só sessão assistencial de 10 transmissões básicas.|**28. Soma.** Mudanças nas posições do soma deitado no leito.|**29. Sons.** Os sons das vibrações geradas pelas energias conscienciais, passando pela cabeça do praticante da tenepes, podem parecer que saem através dos braços e mãos quais tambores batidos com inteligência ou a repetição cadenciada de um *mantra,* palavra única não pronunciada, mas escutada repetidamente, com aceleração menor ou maior.|**30. Torpor.** Entorpecimento notadamente do rosto e dos lábios. **31. Transmissores.** Os transmissores energéticos extrafísicos, ou amparadores, podem se alternar, em serviço, numa só sessão assistencial, e a conscin-praticante-projetor consciente perceberá o revezamento e as mudanças técnicas caracteristicamente individuais, inconfundíveis. O *parassinal* de homem ou de mulher não raro é bem peculiar.|**32. Vivências.** Muitas *sensações inespecíficas* e *vivências* físicas e *parapsíquicas* em um constante crescendo de limites indefinidos ou desconhecidos, até o momento, por todos nós, podem ocorrer durante as práticas da tenepes.|**33. Concomitantes.** Chamam a atenção do praticante 2 fatos como exemplos de fenômenos parapsíquicos concomitantes:|**A. Taquicardia.** A movimentação física, intensiva e extrema dos braços sem o surgimento de taquicardia ou descargas maiores de adrenalina na corrente circulatória. Um fato ainda obscuro, aparentemente antifisiológico.|**B. Digestão.** A aceleração inesperada da digestão em certas circunstâncias emergenciais de assistência.</t>
+    <t>9. VIVÊNCIA</t>
+  </si>
+  <si>
+    <t>***Vivência.*** A tenepes é o *exercício por atacado,* de uma vez, de modo permanente e de tudo o que a consciência sabe, ou especificamente de 7 fatores: | **1. Discernimento.** Possibilita ao praticante alcançar com discernimento a execução da proéxis, do compléxis e até da maximoréxis. | **2. Holochacralidade.** Oferece à consciência humana os meios de instalação do campo energético mais denso e permanente, ou a *névoa* sutil ou densificada, além da aura humana, vista por qualquer pessoa disposta, sobre homens, mulheres, meninos e meninas, nas mais diversas circunstâncias humanas. | **3. Holomaturidade.** Predispõe atingir a maturidade integrada, além da maturidade biológica e maturidade psicológica. | **4. Mentalsomática.** Faculta ao praticante o emprego em nível elevado dos atributos conscienciais, potencialidades individuais e mais de uma inteligência pessoal ao mesmo tempo (todos temos vários módulos de inteligência). | **5. Multidimensionalidade.** Conduz a conscin à desperticidade inevitável. | **6. Parapsiquismo.** Permite ao interessado ou interessada chegar à *pangrafia lúcida.* | **7. Praticidade.** Aponta os meios e os recursos para a execução vivencial mais raciocinada dos atos humanos e manifestações extrafísicas, enquanto na vida física, a fim de a conscin se aproveitar da dinâmica da consciência quanto à sua evolução mais lúcida.</t>
+  </si>
+  <si>
+    <t>**Sensações.** Depois da atuação inconfundível de outra consciência extrafísica sobre os veículos de manifestação – no caso, o soma (corpo humano), o holochacra (corpo energético) e o psicossoma (corpo emocional) – da conscin praticante da tenepes; podem sobrevir, pelo menos, 33 ocorrências de vivência pessoal indiscutível, aqui enumeradas, no período preliminar ou inicial do *praticante-calouro* da tenepes, quando ele *levanta a poeira energética e multidimensional* em torno de si e de seus entes ou realidades mais queridas (homens, mulheres, meninos, meninas, subumanos, plantas e consciexes em multiformes níveis evolutivos): | **1. Assincronizações.** A interferência de assincronizações efêmeras entre os sons e as aspersões energéticas se deve à dificuldade da semipossessão benigna, ou ao entrosamento entre a mente da *conscin praticante* e a *consciex amparadora* responsável pela transmissão. O *amparador-possuidor* comanda, por exemplo, um braço e o *praticante-possuído* comanda o outro braço. | **2. Sincronizações.** Os sons das vibrações rítmicas na cabeça, durante as descargas energéticas, são sincrônicos com os movimentos de aspersões energéticas através dos braços e das mãos. | ***3. Chacras.*** Depois de vários anos, os exercícios regulares, que não são sentidos como sacrifícios, mas diariamente aguardados com alegria íntima ou júbilo sincero, fazem o praticante perceber, no estado da vigília física ordinária, os chacras, notadamente 4 deles, ao mesmo tempo:</t>
+  </si>
+  <si>
+    <t>10. SENSAÇÕES NA TENEPES</t>
+  </si>
+  <si>
+    <t>**A. Sexochacra.** O sexochacra latejante como se o praticante estivesse sentado numa bola de fogo. É a chamada liberação da *kundalini,* muito estudada no Orientalismo. No caso, essa ocorrência é definitivamente sadia ou benigna.</t>
+  </si>
+  <si>
+    <t>**B. Umbilicochacra.** O umbilicochacra ou todo o abdome energizado no sentido para a frente. Não raro, ao contrário, parece que o abdome se amolga ou adelgaça ao modo de uma fina folha de papel.</t>
+  </si>
+  <si>
+    <t>**C. Frontochacra.** O frontochacra que parece pequeno, mas poderoso aparelho incrustado na testa, funcionante, discriminador, até uma certa distância.</t>
+  </si>
+  <si>
+    <t>**D. Coronochacra.** O coronochacra com a impressionante sensação de dissolução da cabeça.</t>
   </si>
   <si>
     <t>OCORRE O APERFEIÇOAMENTO INCESSANTE NAS TRANSMISSÕES ENERGÉTICAS DA TENEPES.</t>
   </si>
   <si>
+    <t>**4. Chama.** Não raro as exteriorizações de energia consciencial podem dar a impressão de que o soma (corpo humano) torna-se enorme chama, língua de fogo de uns 3 metros de altura, quentíssima na periferia e de núcleo gelado, a crepitar para a frente e para cima, e a reverberar como se fosse um foco de luz, expandindo-se e contraindo-se em movimentos para fora e para dentro, alternadamente, sob o comando de uma força intangível, poderosa, inteligente e controlada.</t>
+  </si>
+  <si>
+    <t>**5. Lança-chamas.** Durante a semipossessão benigna, o holochacra que vitaliza mais os braços e as mãos, parece um lança-chamas aspergindo, com aparente violência, as energias conscienciais para a frente através de descargas em ritmo acelerado e constante. Todo o processo aqui assemelha-se ao funcionamento de um centrifugador-consciencial-energético-interdimensional.</t>
+  </si>
+  <si>
+    <t>**6. Clarividências.** Clarividências diversas nas proximidades ou até mesmo clarividência viajora, com alto nível de lucidez.</t>
+  </si>
+  <si>
+    <t>**7. Desmaterializações.** Sensação de desmaterialização dos dedos das mãos e das próprias mãos.</t>
+  </si>
+  <si>
+    <t>**8. Entrosamento.** A primeira descarga energética, mais *receptora* para o conjunto praticante-transmissor extrafísico, do que *doadora* para a consciência receptora (consciex ou conscin projetada), estabelece o *entrosamento parapsíquico.*</t>
+  </si>
+  <si>
+    <t>**A. Experiências.** O acúmulo das experiências diárias com a tenepes, é óbvio, melhora as performances e desempenhos do praticante dedicado e, com o tempo, os amparadores trazem consciexes enfermas mais perturbadas para abordá-lo diretamente no estado da vigília física ordinária ou mesmo quando se projeta com lucidez, fora do horário específico da tenepes. Ele atua, no caso, na condição de *isca assistencial consciente,* intra e extrafisicamente. Nesta altura, o *rapport* físico-extrafísico se intensifica e os resultados das transmissões energéticas melhoram até patamares inimagináveis.</t>
+  </si>
+  <si>
     <t>AS MÃOS DO PRATICANTE DA TENEPES PODEM PARECER ASPERSORES ENERGÉTICOS.</t>
   </si>
   <si>
+    <t>**9. Extras.** Chegando o praticante da tenepes a um grau elevado de afinização com a consciex amparadora, transmissora, *titular,* mais permanente, de ECs, podem sobrevir exteriorizações energéticas extras ou emergenciais, ou seja: antes (principalmente), no período pré-tenepes, ou depois, no período pós-tenepes, diário, das transmissões, em momentos ou circunstâncias inesperadas. Isso acontece sem forçar física ou psiquicamente o praticante, mas de modo agradável, enriquecedor, saudável – que jamais trará qualquer conotação assediadora ou prejudicial – visando a atender consciexes enfermas em uma conjuntura crítica ou emergencial.</t>
+  </si>
+  <si>
+    <t>**10. Fenômenos.** A expansão do holochacra caracteriza os fenômenos sadios do *balonamento* e da *automicroscopia.*</t>
+  </si>
+  <si>
+    <t>**11. Frio.** Sensação de ar frio, mais nas mãos, podendo, no entanto, tomar todo o corpo humano ou mesmo gelar o ambiente do quarto do praticante, independentemente da temperatura ambiental.</t>
+  </si>
+  <si>
+    <t>**12. Holochacra.** Durante as transmissões energéticas, às vezes o soma parece menor ou menos volumoso, devido à expansão do holochacra exteriorizado *(megabalonamento).*</t>
+  </si>
+  <si>
+    <t>**13. Intensidade.** Eis um princípio prático: quanto *mais intensas* sejam as transmissões energéticas, *maior o bem-estar* do praticante no período de minutos ou horas, posterior às transmissões (período pós-tenepes).</t>
+  </si>
+  <si>
+    <t>**14. Intervalos.** O breve intervalo de tempo entre 1 transmissão energética e outra, serve para refazer fisiologicamente o praticante, reajustar o entrosamento praticante-amparador, bem como substituir a consciência receptora à frente ou à distância, sempre que necessário. O amparador, nesse período, em geral não perde o controle parapsíquico-mental-energético do processo. As sensações intensas do praticante podem desaparecer nos intervalos entre 1 descarga energética e outra, permanecendo ele na condição de *semipossuído* por parte do amparador durante as transmissões, e *semilivre* nos intervalos.</t>
+  </si>
+  <si>
+    <t>***15. Imagens.*** Nessa oportunidade, surgem imagens de força, inspiradas pelos amparadores, como, por exemplo, estas 3:</t>
+  </si>
+  <si>
+    <t>**A. Galáxia.** A criação inicial incandescente de um sistema solar</t>
+  </si>
+  <si>
+    <t>**B. Usina.** A *corrida do aço* de um alto forno de usina.</t>
+  </si>
+  <si>
+    <t>**C. Vulcão.** O mar de lavas vivas de um vulcão em erupção.</t>
+  </si>
+  <si>
+    <t>**16. Máquina.** Frequentemente, durante as transmissões energéticas, o praticante parece ouvir o pulsar de imensa máquina, como se estivesse com o corpo unificado, ou seja: o todo de seus veículos conscienciais (holossoma), acoplado a potentíssimo dínamo invisível, servindo de peça intermediária *(passe-partout)* a desconhecida máquina extrafísica.</t>
+  </si>
+  <si>
+    <t>**17. Oitava.** Em geral, uma descarga energética entre as 11, por exemplo, a oitava, pode ser perceptivelmente mais intensa ou mais potente do que as demais, em função dos trabalhos assistenciais em desenvolvimento.</t>
+  </si>
+  <si>
     <t>AS TRANSMISSÕES SE FAZEM POR ONDAS DE ENERGIAS CONSCIENCIAIS EM GERAL INTERMITENTES.</t>
   </si>
   <si>
+    <t>**18. Ondas.** As transmissões, nas práticas da tenepes se fazem por ondas de ECs bem caracterizadas, percebidas pelo praticante, em geral de forma intermitente e não-contínua. As ondas de energias contínuas, quando ocorrem, denunciam uma circunstância terapêutica crítica ou uma injunção desassediadora singular, e tende a serem efêmeras, à semelhança de um pico extraordinário ou esporádico de exteriorização de energias assistenciais.</t>
+  </si>
+  <si>
+    <t>**19. Projeções.** Projeções conscienciais lúcidas de modalidades e consequências práticas, úteis, para os assistidos e o praticante, as mais diversas.</t>
+  </si>
+  <si>
+    <t>**20. Pruridos.** Um dos primeiros indícios da manifestação dos fenômenos de efeitos intrafísicos, mas parapsíquicos, ou exteriorização indiscutível de ectoplasma, é o surgimento não habitual de pruridos nas mucosas nasais, ou mais claramente, coceiras inoportunasno interior das fossas nasais, apenas durante as práticas da tenepes. Isso se deve à saída inicial de ectoplasma através das mucosas dos orifícios do corpo humano.</t>
+  </si>
+  <si>
+    <t>**21. Psicofonia.** O monólogo psicofônico é a fala direta da consciex comunicante (neste caso, o amparador), durante a psicofonia, para a conscin proprietária do soma, temporariamente descoincidida ou projetada (neste caso, o praticante durante as práticas da tenepes). Como se observa, o monólogo psicofônico é uma inversão transcendente e rara de condições, posições de consciências e manifestações interconscienciais.</t>
+  </si>
+  <si>
+    <t>**22. Pulsações.** Pulsações energéticas cerebrais. Importa observar que fisiologicamente o cérebro não pulsa por si, por exemplo, igual ao coração. Neste caso, as sensações bizarras são mesmo de *pulsações* dentro da cabeça. Relativamente a essas sensações e à maioria das referidas aqui, somente tendo as experiências, pessoalmente, é que o praticante pode aquilatar melhor os seus detalhes e efeitos sadios, com o tempo e a expansão da sua desenvoltura nas práticas assistenciais.</t>
+  </si>
+  <si>
+    <t>**23. Qualidade.** O tempo não representa fator relevante nas descargas energéticas, importando muito mais a qualidade e a potencialidade das energias conscienciais transmitidas.</t>
+  </si>
+  <si>
+    <t>**24. Ritmos.** Não raro, o ritmo intenso e variado das descargas energéticas, os movimentos físicos, e as contrações musculares não alteram praticamente em nada o *ritmo cardíaco* do praticante. Tal fato, por si só, constitui fenômeno subjetivo, concomitante, à parte.</t>
+  </si>
+  <si>
+    <t>***25. Independência.*** A rigor, a frequência – sempre perceptível – das transmissões energéticas do praticante, não se subordina a estas 4 variáveis:</t>
+  </si>
+  <si>
+    <t>**A. Volição.** Nem à sua *vontade* ou à volição, incluindo-se, aqui, a intenção ou intencionalidade.</t>
+  </si>
+  <si>
+    <t>**B. Circulação.** Nem aos seus *batimentos cardíacos* que mantêm a circulação sanguínea, sendo a área mais exigente e importante a correspondente aos dois hemisférios cerebrais.</t>
+  </si>
+  <si>
+    <t>**C. Respiração.** Nem à sua *frequência respiratória* que mantém a sua *alimentação de oxigênio,* em conexão direta com o cardiochacra.</t>
+  </si>
+  <si>
+    <t>**D. Tempo.** Nem ao andamento dos *segundos do relógio* comum que marca o tempo cronológico ou humano.</t>
+  </si>
+  <si>
+    <t>**26. Ordenações.** Tudo acontece sob a superintendência das ordenações parapsíquicas ou energético-anímico-mediúnico-motrizes da consciex transmissora básica, não obstante todo o conjunto de transmissão parecer estar acoplado a poderosos aparelhos extrafísicos ainda desconhecidos neste estágio de nossos conhecimentos de vanguarda. Podem ocorrer 4 a 5 ritmos de *transmissões energéticas,* bem diferentes uns dos outros, numa só sessão assistencial de 10 transmissões básicas.</t>
+  </si>
+  <si>
+    <t>**27. Soma.** Mudanças nas posições do soma deitado no leito.</t>
+  </si>
+  <si>
+    <t>**28. Sons.** Os sons das vibrações geradas pelas energias conscienciais, passando pela cabeça do praticante da tenepes, podem parecer que saem através dos braços e mãos quais tambores batidos com inteligência ou a repetição cadenciada de um *mantra,* palavra única não pronunciada, mas escutada repetidamente, com aceleração menor ou maior.</t>
+  </si>
+  <si>
+    <t>**29. Torpor.** Entorpecimento notadamente do rosto e dos lábios.</t>
+  </si>
+  <si>
+    <t>**A. Transmissores.** Os transmissores energéticos extrafísicos, ou amparadores, podem se alternar, em serviço, numa só sessão assistencial, e a conscin-praticante-projetor consciente perceberá o revezamento e as mudanças técnicas caracteristicamente individuais, inconfundíveis. O *parassinal* de homem ou de mulher não raro é bem peculiar.</t>
+  </si>
+  <si>
+    <t>**30. Vivências.** Muitas *sensações inespecíficas* e *vivências* físicas e *parapsíquicas* em um constante crescendo de limites indefinidos ou desconhecidos, até o momento, por todos nós, podem ocorrer durante as práticas da tenepes.</t>
+  </si>
+  <si>
     <t>PODEM OCORRER FENÔMENOS PARAPSÍQUICOS CONCOMITANTES ÀS PRÁTICAS DA TENEPES.</t>
   </si>
   <si>
-    <t>**Energética.** Será sempre melhor o praticante da tenepes não esquecer 4 realidades quanto às energias das consciências:|**1. Vida.** Vida, em qualquer dimensão, é assistencialidade interconsciencial.|**2. Assistencialidade.** Assistencialidade interconsciencial é ou significa energética, *bio*energética e *para*energética.|**3. Embriologia.** A vida é energética e tem seu começo, na Terra, pela Embriologia ou através do ato sexual (energia e adrenalina).|**4. Predomínio.** A vida humana é, portanto, predominantemente holochacral.</t>
+    <t>**31. Concomitantes.** Chamam a atenção do praticante 2 fatos como exemplos de fenômenos parapsíquicos concomitantes:</t>
+  </si>
+  <si>
+    <t>**A. Taquicardia.** A movimentação física, intensiva e extrema dos braços sem o surgimento de taquicardia ou descargas maiores de adrenalina na corrente circulatória. Um fato ainda obscuro, aparentemente antifisiológico.</t>
+  </si>
+  <si>
+    <t>**B. Digestão.** A aceleração inesperada da digestão em certas circunstâncias emergenciais de assistência.</t>
+  </si>
+  <si>
+    <t>**Energética.** Será sempre melhor o praticante da tenepes não esquecer 4 realidades quanto às energias das consciências: | **1. Vida.** Vida, em qualquer dimensão, é assistencialidade interconsciencial. | **2. Assistencialidade.** Assistencialidade interconsciencial é ou significa energética, *bio*energética e *para*energética. | **3. Embriologia.** A vida é energética e tem seu começo, na Terra, pela Embriologia ou através do ato sexual (energia e adrenalina). | **4. Predomínio.** A vida humana é, portanto, predominantemente holochacral.</t>
+  </si>
+  <si>
+    <t>11. CONEXÕES SEXUAIS</t>
   </si>
   <si>
     <t>**Holochacra.** O holochacra é o paracorpo energético ou das energias conscienciais pessoais ou de cada indivíduo macho ou fêmea. O holochacra é o paracorpo da *pré-kundalini,* da *kundalini,* do sexochacra (sexossoma).</t>
   </si>
   <si>
-    <t>**Conexões.** Há 2 conexões do holochacra: |1. **Miniconexão.** A *mini*conexão no soma ou corpo humano.|**2. Maxiconexão.** A *maxi*conexão, mais importante, no psicossoma.</t>
+    <t>**Conexões.** Há 2 conexões do holochacra: | 1. **Miniconexão.** A *mini*conexão no soma ou corpo humano. | **2. Maxiconexão.** A *maxi*conexão, mais importante, no psicossoma.</t>
   </si>
   <si>
     <t>**Trinômio.** As 2 conexões do holochacra constituem o trinômio *soma-holochacra-psicossoma,* dentro do holossoma ou o conjunto dos veículos de manifestação da consciência humana ou conscin.</t>
@@ -380,7 +544,10 @@
     <t>**Meia-força.** A tenepes *sem sexo diário* é uma *tenepes estacionária,* que alcança somente meia-força, por que dificulta um crescimento consciencial evolutivo mais expressivo.</t>
   </si>
   <si>
-    <t>**Advertências.** Eis 5 procedimentos não recomendáveis nas práticas da tenepes: |**1. Companhia.** A mulher *sem companheiro* não consegue dar assistência nem para quem ama, como poderá fazer assistência às outras consciências, conscins e consciexes? A mulher *com companheiro* começa a assistencialidade na alcova sadia ou energeticamente blindada. Esta é uma condição completamente diferente e muito mais eficaz no desenvolvimento da tenepes. O mesmo ocorre ao homem *com* e *sem* companheira.|**2. Masturbação.** A masturbação é uma *conduta-exceção* que não deve ser empregada na condição de conduta-padrão para o resto da vida da conscin, por que não supre as necessidades de alíviosexual com as ECs, ou a acalmia da hiperexcitabilidade sexual gerada naturalmente pelas práticas da tenepes.|**3. Sublimação***.* Toda tentativa inútil de sublimação do sexo, seja qual for a natureza, é castração ou mutilação física, somática, energética, humana. Esta é mais uma condição impraticável para se manter as práticas da tenepes em desenvolvimento sadio, seguro e maduro.|**4. Menopausa.** A menopausa não pode criar a *mulher eunuca* no restante da vida dos exercícios práticos da tenepes. A fim de evitar isso, a Medicina sabe atender com eficácia aos casos de menopausa com o balanço dos hormônios e a indicação de uma vida sexual ativa.|**5. Terceira Idade.** A terceira idade ou a idade dos veteranos da vida, depois dos 65 anos de idade física, não deve criar o *vegetalismo sexual humano,* seja da mulher ou do homem. Esta é outra condição que não funciona com a tenepes, onde a vida energética é a mais intensa, duradoura ou permanente possível.|**Alívio.** O *congressus subtilis* sadio entre o praticante (a praticante) e o amparador (a amparadora) pode ocorrer, com iniciativa do maximecanismo assistencial, a fim de aliviar a conscin em algum período de viagem, separação ou viuvez, de modo efêmero.</t>
+    <t>**Advertências.** Eis 5 procedimentos não recomendáveis nas práticas da tenepes: | **1. Companhia.** A mulher *sem companheiro* não consegue dar assistência nem para quem ama, como poderá fazer assistência às outras consciências, conscins e consciexes? A mulher *com companheiro* começa a assistencialidade na alcova sadia ou energeticamente blindada. Esta é uma condição completamente diferente e muito mais eficaz no desenvolvimento da tenepes. O mesmo ocorre ao homem *com* e *sem* companheira. | **2. Masturbação.** A masturbação é uma *conduta-exceção* que não deve ser empregada na condição de conduta-padrão para o resto da vida da conscin, por que não supre as necessidades de alíviosexual com as ECs, ou a acalmia da hiperexcitabilidade sexual gerada naturalmente pelas práticas da tenepes. | **3. Sublimação. Toda tentativa inútil de sublimação do sexo, seja qual for a natureza, é castração ou mutilação física, somática, energética, humana. Esta é mais uma condição impraticável para se manter as práticas da tenepes em desenvolvimento sadio, seguro e maduro. | **4. Menopausa.** A menopausa não pode criar a *mulher eunuca* no restante da vida dos exercícios práticos da tenepes. A fim de evitar isso, a Medicina sabe atender com eficácia aos casos de menopausa com o balanço dos hormônios e a indicação de uma vida sexual ativa. | **5. Terceira Idade.** A terceira idade ou a idade dos veteranos da vida, depois dos 65 anos de idade física, não deve criar o *vegetalismo sexual humano,* seja da mulher ou do homem. Esta é outra condição que não funciona com a tenepes, onde a vida energética é a mais intensa, duradoura ou permanente possível.</t>
+  </si>
+  <si>
+    <t>**Alívio.** O *congressus subtilis* sadio entre o praticante (a praticante) e o amparador (a amparadora) pode ocorrer, com iniciativa do maximecanismo assistencial, a fim de aliviar a conscin em algum período de viagem, separação ou viuvez, de modo efêmero.</t>
   </si>
   <si>
     <t>**Ciúmes.** A dupla evolutiva há de observar seriamente os processos de ciúmes, possessividade e insegurança psicológica ou afetiva, de um parceiro em relação ao outro, quanto à assistência praticada através da tenepes. Por exemplo, se a mulher começa a manifestar ciúmes em razão dos telefonemas de outras mulheres que solicitam assistência, a ser executada pelo homem através das práticas da tenepes, ela se bandeia inteiramente e *se posiciona* do lado ou *ombro a ombro com os assediadores.* Tais assediadores não são apenas os da consciência a ser assistida, ou de quem telefona solicitando ajuda, mas também os assediadores do praticante que se empenha no desassédio, e os dela própria. O praticante da tenepes, neste caso, ficará encantoado e sentirá isso diretamente, de imediato, na *parapele.* É fácil imaginar o que pode brotar de parapatológico nessa atmosfera de desentendimento da dupla evolutiva.</t>
@@ -389,7 +556,10 @@
     <t>**Intercursos.** As relações sexuais *logo antes* das práticas da tenepes não são recomendáveis em razão dos preparativos assistenciais do praticante por parte dos amparadores. Depois das práticas, as relações sexuais não apresentam quaisquer inconvenientes lógicos.</t>
   </si>
   <si>
-    <t>***Operações.*** Os movimentos sincrônicos, frenéticos, espasmódicos e aspersivos com os braços e as mãos, durante as transmissões energéticas, visam à assistência a conscins e consciexes, através de 3 operações distintas, em geral interligadas:|**1. Doação.** Exteriorização de *energia imanente* e *energia consciencial.|***2. Desmaterialização.** Desmaterialização fugaz de *partes do soma* do praticante da tenepes.|**3. Ectoplasmia.** Extração da EC densa, humana, ou *ectoplasma,* exclusivamente para fins terapêuticos, ou, mais apropriadamente, paraterapêuticos.</t>
+    <t>***Operações.*** Os movimentos sincrônicos, frenéticos, espasmódicos e aspersivos com os braços e as mãos, durante as transmissões energéticas, visam à assistência a conscins e consciexes, através de 3 operações distintas, em geral interligadas: | **1. Doação.** Exteriorização de *energia imanente* e *energia consciencial.* | **2. Desmaterialização.** Desmaterialização fugaz de *partes do soma* do praticante da tenepes. | **3. Ectoplasmia.** Extração da EC densa, humana, ou *ectoplasma,* exclusivamente para fins terapêuticos, ou, mais apropriadamente, paraterapêuticos.</t>
+  </si>
+  <si>
+    <t>12. OPERAÇÕES ASSISTENCIAIS</t>
   </si>
   <si>
     <t>**Aspersores.** Os *para*braços e as *para*mãos do psicossoma do praticante da tenepes são os aspersores energéticos, sob o comando real, perceptível, inconfundível, do amparador, o verdadeiro transmissor da energia consciencial básica.</t>
@@ -410,7 +580,7 @@
     <t>**Reflexões.** Dentre as indicações parapsíquicas do amparador, uma delas levará o praticante da tenepes, quando mais consciente, a refletir, inevitavelmente, em *conceitos,* à primeira vista díspares, porém relacionados por liames lógicos indiscutíveis, entre si, e o serviço assistencial desenvolvido.</t>
   </si>
   <si>
-    <t>***Consciências.*** A tenepes se desenvolve através de 3 consciências entrosadas:|**1. Praticante.** A conscin *praticante* (adulta, homem ou mulher) da tenepes.|**2. Amparador.** A consciex ou o *amparador* (ou amparadores), com paravisuais de homem ou de mulher. Pode ocorrer ser esporadicamente um *superamparador* ou um Orientador Evolutivo do grupocarma.|**3. Assistido.** O *assistido* ou assistidos, consciexes ouconscins.</t>
+    <t>***Consciências.*** A tenepes se desenvolve através de 3 consciências entrosadas: | **1. Praticante.** A conscin *praticante* (adulta, homem ou mulher) da tenepes. | **2. Amparador.** A consciex ou o *amparador* (ou amparadores), com paravisuais de homem ou de mulher. Pode ocorrer ser esporadicamente um *superamparador* ou um Orientador Evolutivo do grupocarma. | **3. Assistido.** O *assistido* ou assistidos, consciexes ouconscins.</t>
   </si>
   <si>
     <t>**Encapsulamento.** O *encapsulamento parassanitário* é o isolamento assistencial e a anulação energética, temporária, das manifestações pensênicas – notadamente energéticas, intrusivas ou assediadoras – de uma ou mais consciências – conscins e/ou consciexes – enfermas, ao modo dos isolamentos sanitários existentes nos hospitais de doenças infectocontagiosas com internados que apresentam alto poder de contaminação doentia, radiativa ou tóxica.</t>
@@ -422,7 +592,7 @@
     <t>**Percepção.** Nem sempre a ocorrência do encapsulamento parassanitário é percebida nitidamente pelo praticante da tenepes, porque o isolamento é patrocinado pelo amparador ou, o mais frequente, por vários amparadores em conjunto, e transcende, não raro, o universo das suas manifestações pensênicas.</t>
   </si>
   <si>
-    <t>**Classificação.** O encapsulamento parassanitário pode ser classificado em 3 tipos ou quanto às consciências, o tempo e as dimensões conscienciais:|**1. Consciências.** Quanto às consciências – conscins e/ou consciexes – o encapsulamento pode ser individual; conjugal ou de dupla; e grupal (coletivo).|**2. Tempo.** Quanto ao tempo, o encapsulamento pode perdurar por minutos, horas ou dias.|**3. Dimensões.** Quanto ao espaço ou às dimensões conscienciais, o isolamento pode abranger as consciências – conscins e/ou consciexes – de uma casa ou apartamento; de todo um edifício de apartamentos ou de toda uma vila de casas; ou até mesmo de todo um bairro ou os limites de uma região administrativa da megacidade.</t>
+    <t>**Classificação.** O encapsulamento parassanitário pode ser classificado em 3 tipos ou quanto às consciências, o tempo e as dimensões conscienciais: | **1. Consciências.** Quanto às consciências – conscins e/ou consciexes – o encapsulamento pode ser individual; conjugal ou de dupla; e grupal (coletivo). | **2. Tempo.** Quanto ao tempo, o encapsulamento pode perdurar por minutos, horas ou dias. | **3. Dimensões.** Quanto ao espaço ou às dimensões conscienciais, o isolamento pode abranger as consciências – conscins e/ou consciexes – de uma casa ou apartamento; de todo um edifício de apartamentos ou de toda uma vila de casas; ou até mesmo de todo um bairro ou os limites de uma região administrativa da megacidade.</t>
   </si>
   <si>
     <t>**Filosofia.** A filosofia da assistencialidade interconsciencial, antientrópica, do encapsulamento parassanitário se baseia na premissa prática de que *muito ajuda quem não atrapalha*.</t>
@@ -437,6 +607,9 @@
     <t>**Primário.** O praticante humano, primário, da tenepes, seja homem ou mulher, é o que não evolui e nem muda de amparadores.</t>
   </si>
   <si>
+    <t>13. AMPARADORES</t>
+  </si>
+  <si>
     <t>O AMPARADOR É O COPRATICANTE EXTRAFÍSICO NAS PRÁTICAS DA TENEPES.</t>
   </si>
   <si>
@@ -455,7 +628,7 @@
     <t>**Intimidades.** *Comunicação é convivência.* A intimidade com o amparador é superior – em função do holossoma – à intimidade com o *consorte* na condição do casamento convencional ou o *parceiro* da dupla evolutiva.</t>
   </si>
   <si>
-    <t>**Parcerias.** Existem 2 tipos de parcerias bem definidas quanto às intimidades interconscienciais:|**1. Simples.** A parceria, *mais simples,* dos 2 parceiros da dupla evolutiva, ou em um casamento convencional, que se faz basicamente através do *soma.|***2. Complexa.** A parceria, *mais complexa,* do praticante da tenepes com o amparador, que se faz basicamente através do *holossoma.*</t>
+    <t>**Parcerias.** Existem 2 tipos de parcerias bem definidas quanto às intimidades interconscienciais: | **1. Simples.** A parceria, *mais simples,* dos 2 parceiros da dupla evolutiva, ou em um casamento convencional, que se faz basicamente através do *soma.* | **2. Complexa.** A parceria, *mais complexa,* do praticante da tenepes com o amparador, que se faz basicamente através do *holossoma.*</t>
   </si>
   <si>
     <t>**Potencialização.** Assim, o praticante veterano da tenepes tem as suas energias conscienciais cada vez mais potencializadas pelo amparador que atua através do holossoma.</t>
@@ -464,12 +637,18 @@
     <t>**Sabedoria.** A sabedoria dos amparadores se expressa na dosagem cosmoética justa em tudo o que fazem. Jamais *deixam faltar* o útil necessário e jamais *deixam passar* da conta, seja quanto à assistência interconsciencial, ao uso das energias conscienciais, ou quanto ao emprego dos talentos do praticante da tenepes na condição de instrumento assistencial sensível.</t>
   </si>
   <si>
-    <t>***Conceitos.*** Eis 13 exemplos de *ideias complexas* (Mentalsomática, o *pen* do pensene) que virão à cabeça do praticante da tenepes, conforme as suas *motivações intelectuais* mais frequentes, seus arquétipos, a qualidade e extensão do seu *dicionário cerebral:|***1. Autogestão.** A autossuficiência da conscin.|**2. Buraco negro.** O buraco negro é o estado que a matéria atinge ao sofrer um colapso gravitacional do qual nem a luz, a matéria ou qualquer outro tipo de sinal podem escapar.|***3. Criador incriado.*** A chamada *causa primeira.|***4. Enésima potência.|5. Eternidade**. A eternidade, aqui, significa a vida que evidencia prosseguir sempre, para nós, numa sucessão alternada e constante de renascimentos intrafísicos e dessomas.|**6. Fênix.** O que é o mito do renascimento da fênix.|**7. Implosão.** A condição do *oneness,* a consciência una com o Universo.|**8. Infinito do futuro.** Após a condição da consciência livre (CL), o que acontece?|**9. Infinito do passado.** O começo de tudo.|**10. Moto-contínuo.** O moto-contínuo físico, uma roda de aço, mecânica, caricatura sem eletricidade, bateria ou qualquer outro recurso, que gira incessantemente tão-só impulsionada pela gravitação.|**11. Onipotência.** A onipotência é a autoridade ou a soberania absoluta.|***12. Poço sem fundo*** (o abismo, a voragem, o *void*)**.|13. Superinfovia.** A *super-rodovia da informação* significa, aqui, o máximo da vanguarda, hoje, do universalismo intrafísico prático.</t>
+    <t>***Conceitos.*** Eis 13 exemplos de *ideias complexas* (Mentalsomática, o *pen* do pensene) que virão à cabeça do praticante da tenepes, conforme as suas *motivações intelectuais* mais frequentes, seus arquétipos, a qualidade e extensão do seu *dicionário cerebral:* | **1. Autogestão.** A autossuficiência da conscin. | **2. Buraco negro.** O buraco negro é o estado que a matéria atinge ao sofrer um colapso gravitacional do qual nem a luz, a matéria ou qualquer outro tipo de sinal podem escapar. | ***3. Criador incriado.*** A chamada *causa primeira.* | **4. Enésima potência.** | **5. Eternidade**. A eternidade, aqui, significa a vida que evidencia prosseguir sempre, para nós, numa sucessão alternada e constante de renascimentos intrafísicos e dessomas. | **6. Fênix.** O que é o mito do renascimento da fênix. | **7. Implosão.** A condição do *oneness,* a consciência una com o Universo. | **8. Infinito do futuro.** Após a condição da consciência livre (CL), o que acontece? | **9. Infinito do passado.** O começo de tudo. | **10. Moto-contínuo.** O moto-contínuo físico, uma roda de aço, mecânica, caricatura sem eletricidade, bateria ou qualquer outro recurso, que gira incessantemente tão-só impulsionada pela gravitação. | **11. Onipotência.** A onipotência é a autoridade ou a soberania absoluta. | ***12. Poço sem fundo*** (o abismo, a voragem, o *void*). | **13. Superinfovia.** A *super-rodovia da informação* significa, aqui, o máximo da vanguarda, hoje, do universalismo intrafísico prático.</t>
+  </si>
+  <si>
+    <t>14. MENTALSOMÁTICA</t>
   </si>
   <si>
     <t>**Desenvolvimento.** Quanto mais evoluída seja a consciência, mais intensidade terá em sua potência energética, e menos esforço consciencial e tempo precisará para a sua completa *reposição energética* (assins e desassins).</t>
   </si>
   <si>
+    <t>15. HOLOCHACRALIDADE</t>
+  </si>
+  <si>
     <t>**EC.** A energia consciencial, ou EC, é inesgotável ou inexaurível.</t>
   </si>
   <si>
@@ -500,12 +679,15 @@
     <t>**Isolamento.** A ofiex é uma espécie de isolamento sanitário de hospital extrafísico destinado a receber as consciexes enfermas temporariamente, dentro de um *bolsão interdimensional* de transição.</t>
   </si>
   <si>
-    <t>**Períodos.** Há 2 períodos bem característicos nas práticas da tenepes (veja página 31):|1. O período *pré-tenepes,* antes da instalação dos serviços assistenciais, a cada dia.|2. O período *pós-tenepes,* após a realização diária dos serviços assistenciais.</t>
+    <t>**Períodos.** Há 2 períodos bem característicos nas práticas da tenepes (veja página 31): | 1. O período *pré-tenepes,* antes da instalação dos serviços assistenciais, a cada dia. | 2. O período *pós-tenepes,* após a realização diária dos serviços assistenciais.</t>
   </si>
   <si>
     <t>**Instrumentos.** Não se recomenda deixar quaisquer tipos de instrumentos ou aparelhos ligados ou funcionando dentro do cômodo ou peça onde se pratica a tenepes, durante os exercícios, em razão dos efeitos físicos de origem parapsíquica ou ectoplasmática, por exemplo: microcomputador pessoal, telefone, interfone, TV, *bip,* vídeo com relógio digital e luzes acesas, relógio de funcionamento barulhento, e outros.</t>
   </si>
   <si>
+    <t>16. OBJETOS</t>
+  </si>
+  <si>
     <t>**Armas.** O recinto – o quarto-laboratório de dormir, *alcova energeticamente blindada,* a base física, o *projetarium,* ou a *antecâmara intrafísica da ofiex* – do praticante da tenepes, *não deve, é óbvio,* ser local para guardar armas de qualquer natureza, por exemplo, uma arma de fogo.</t>
   </si>
   <si>
@@ -524,7 +706,7 @@
     <t>**Gaveta.** O ideal é o praticante veterano da tenepes manter uma gaveta reservada onde possa colocar exclusivamente os papéis com *pedidos, cartas, telegramas e faxes de assistência interconsciencial* à distância que, inevitavelmente, receberá, ao ficar mais conhecida a sua tarefa assistencial permanente.</t>
   </si>
   <si>
-    <t>**Vias.** Com o desenvolvimento das práticas assistenciais da tenepes, o praticante pode parecer uma *pessoa jurídica,* pois receberá solicitações por 4 vias diversas de comunicação:|**1. Correios:** o praticante recebe carta ou telegrama endereçados à sua ofiex, com solicitação de assistência à distância.|**2. CI:** Comunicação Interna dentro de uma empresa conscienciológica solicitando assistência.|**3. Fax:** solicitação de assistência através de fax.</t>
+    <t>**Vias.** Com o desenvolvimento das práticas assistenciais da tenepes, o praticante pode parecer uma *pessoa jurídica,* pois receberá solicitações por 4 vias diversas de comunicação: | **1. Correios:** o praticante recebe carta ou telegrama endereçados à sua ofiex, com solicitação de assistência à distância. | **2. CI:** Comunicação Interna dentro de uma empresa conscienciológica solicitando assistência. | **3. Fax:** solicitação de assistência através de fax.</t>
   </si>
   <si>
     <t>**Computadores:** pedido de assistência via rede de computadores.</t>
@@ -557,7 +739,7 @@
     <t>**Hotel.** Obviamente, a conscin que vive em um hotel, faz do seu apartamento, ali, a sua base física. Contudo, nas práticas da tenepes, a base física, definitiva e permanente, em hotel *não é a ideal* em razão da vida tumultuada, própria do local, com gente saindo e entrando, em geral em períodos existenciais críticos, fora do seu domicílio natural.</t>
   </si>
   <si>
-    <t>**Paradoxos.** Fazer do hotel a base física gera 3 reflexos sobre os *paradoxos* da vida do praticante da tenepes:|**1. Provisoriedade.** Ele não se apega à vida humana por que, não vive com a sensação de provisoriedade do residente-hóspede do hotel.|**2. Responsabilidade.** Sabe muito bem que está em trânsito pela existência intrafísica, sem medo da morte do corpo físico, contudo, mantém responsabilidade quanto às obrigações humanas.|**3. Proéxis.** Não está *amarrado a nada,* igual ao residente-hóspede, mas se sente *amarrado a tudo* no cumprimento de sua proéxis.</t>
+    <t>**Paradoxos.** Fazer do hotel a base física gera 3 reflexos sobre os *paradoxos* da vida do praticante da tenepes: | **1. Provisoriedade.** Ele não se apega à vida humana por que, não vive com a sensação de provisoriedade do residente-hóspede do hotel. | **2. Responsabilidade.** Sabe muito bem que está em trânsito pela existência intrafísica, sem medo da morte do corpo físico, contudo, mantém responsabilidade quanto às obrigações humanas. | **3. Proéxis.** Não está *amarrado a nada,* igual ao residente-hóspede, mas se sente *amarrado a tudo* no cumprimento de sua proéxis.</t>
   </si>
   <si>
     <t>**Euforia.** Um dos maiores males das práticas da tenepes é justamente um dos seus benefícios: a produção da euforia no praticante. Essa euforia precisa ser contida, sem recalcamentos, a fim de não prejudicar a própria passividade autolúcida do praticante da tenepes.</t>
@@ -566,7 +748,10 @@
     <t>**Grupalidade.** A tenepes não funciona em grupo de conscins porque é compromisso individual. A grupalidade em suas práticas é multidimensional, seguindo as diretrizes de um maximecanismo assistencial.</t>
   </si>
   <si>
-    <t>**Práticas.** Não apresentam os mesmos êxitos da tenepes 5 práticas assemelhadas, enumeradas aqui como exemplos de muitas outras práticas parecidas, contudo não idênticas:|**1. Culto do evangelho** no lar 1 vez por semana, prática comum no movimento espírita do Brasil**.|2. Sessão mediúnica** em grupo, privativa ou pública (desobsessão), 1 vez por semana, de várias seitas mediúnicas**.|3. Gira da Umbanda.|4. Irradiação** da Comunhão **do Pensamento** às 18 horas, em geral 5 minutos diários, sem compromissos rígidos maiores**.|5. Terço** (reza) da Igreja Católica**.**</t>
+    <t>17. GRUPALIDADE</t>
+  </si>
+  <si>
+    <t>**Práticas.** Não apresentam os mesmos êxitos da tenepes 5 práticas assemelhadas, enumeradas aqui como exemplos de muitas outras práticas parecidas, contudo não idênticas: | **1. Culto do evangelho** no lar 1 vez por semana, prática comum no movimento espírita do Brasil. | **2. Sessão mediúnica** em grupo, privativa ou pública (desobsessão), 1 vez por semana, de várias seitas mediúnicas. | **3. Gira da Umbanda.** | **4. Irradiação** da Comunhão **do Pensamento** às 18 horas, em geral 5 minutos diários, sem compromissos rígidos maiores. | **5. Terço** (reza) da Igreja Católica.</t>
   </si>
   <si>
     <t>ASSIM COMO NÃO EXISTE MEIA-GRAVIDEZ, NÃO EXISTE TAMBÉM MEIA-TENEPES.</t>
@@ -575,7 +760,10 @@
     <t>**Estacionária.** A tenepes estacionária só alcança *meia-força,* (Veja página 37), o que é diferente da *meia-tenepes.*</t>
   </si>
   <si>
-    <t>***Contraindicações.*** A prática da tenepes *não é recomendável* a 6 tipos de pessoas ou conscins:|**1. Apedeutas.** A quem *nunca sentiu manifestações parapsíquicas,* intraconscienciais, ostensivas, que não admite nem a discussão do assunto, ignorante quanto ao tema, ou que se perfila entre os *apedeutas parapsíquicos.|***2. Principiantes.** Aos principiantes ou calouros quanto ao parapsiquismo (bioenergética, animismo e mediunidade), ainda não desenvolvidos até a um nível prático, individual, razoável.|**3. Miniassediados.** Às vítimas dos miniassédios inconscientes eventuais, ou seja: à *maioria absoluta* da população planetária. Uma pessoa já *super*possuída doentiamente pelo *assediador,* não pode ser *semi*possuída sadiamente pelo *amparador.* Tal fato chancela um princípio da Física, da Fisiologia, da Parafisiologia e da Conscienciologia: “2 corpos não podem ocupar, ao mesmo tempo, o mesmo espaço, na mesma dimensão”.|**4. Descontrolados.** Às conscins parapsiquicamente deseducadas, que não conseguem controlar os processos parapsíquicos dos intercâmbios conscienciais de modo autossuficiente, confortável e sadio que sofrem à aproximação de consciexes, por exemplo, mioclonias incessantes incontroláveis.|**5. Ávidos.** Às conscins que ainda respiram ansiosas por sensações instintivas; de existência ainda não assentada quanto às suas pretensões e aspirações humanas; em geral até os 35 anos de idade física, ou na *fase preparatória* para a execução da proéxis. Quem deseja praticar a tenepes só depois que alcançar 2 milhões de dólares na conta bancária, está perdendo o tempo por que jamais vai conseguir bons resultados assistenciais com as práticas.|**6. Crianças.** Evidentemente, as práticas da tenepes não são recomendadas para crianças de ambos os sexos, em qualquer idade infantil, mesmo se superdotadas parapsiquicamente.</t>
+    <t>***Contraindicações.*** A prática da tenepes *não é recomendável* a 6 tipos de pessoas ou conscins: | **1. Apedeutas.** A quem *nunca sentiu manifestações parapsíquicas,* intraconscienciais, ostensivas, que não admite nem a discussão do assunto, ignorante quanto ao tema, ou que se perfila entre os *apedeutas parapsíquicos.* | **2. Principiantes.** Aos principiantes ou calouros quanto ao parapsiquismo (bioenergética, animismo e mediunidade), ainda não desenvolvidos até a um nível prático, individual, razoável. | **3. Miniassediados.** Às vítimas dos miniassédios inconscientes eventuais, ou seja: à *maioria absoluta* da população planetária. Uma pessoa já *super*possuída doentiamente pelo *assediador,* não pode ser *semi*possuída sadiamente pelo *amparador.* Tal fato chancela um princípio da Física, da Fisiologia, da Parafisiologia e da Conscienciologia: “2 corpos não podem ocupar, ao mesmo tempo, o mesmo espaço, na mesma dimensão”. | **4. Descontrolados.** Às conscins parapsiquicamente deseducadas, que não conseguem controlar os processos parapsíquicos dos intercâmbios conscienciais de modo autossuficiente, confortável e sadio que sofrem à aproximação de consciexes, por exemplo, mioclonias incessantes incontroláveis. | **5. Ávidos.** Às conscins que ainda respiram ansiosas por sensações instintivas; de existência ainda não assentada quanto às suas pretensões e aspirações humanas; em geral até os 35 anos de idade física, ou na *fase preparatória* para a execução da proéxis. Quem deseja praticar a tenepes só depois que alcançar 2 milhões de dólares na conta bancária, está perdendo o tempo por que jamais vai conseguir bons resultados assistenciais com as práticas. | **6. Crianças.** Evidentemente, as práticas da tenepes não são recomendadas para crianças de ambos os sexos, em qualquer idade infantil, mesmo se superdotadas parapsiquicamente.</t>
+  </si>
+  <si>
+    <t>18. CONTRAINDICAÇÕES DA TENEPES</t>
   </si>
   <si>
     <t>QUEM VIVE ÁVIDO POR SENSAÇÕES TROPOSFÉRICAS AINDA NÃO ESTÁ APTO PARA A TENEPES.</t>
@@ -584,16 +772,22 @@
     <t>**Teste.** O Capítulo 345 do livro *“700 Experimentos da Conscienciologia”,* traz um teste sobre a tenepes aqui reproduzido, em suas linhas gerais, a fim de clarear mais os assuntos.</t>
   </si>
   <si>
+    <t>19. TESTE DA TENEPES</t>
+  </si>
+  <si>
     <t>**Evolução.** A consciência somente evolui mais depressa quando *ajuda* as outras consciências a evoluírem. Isto resume a dinâmica evolutiva que atinge a todos nós.</t>
   </si>
   <si>
-    <t>**Consciencioterapia.** A prática diária da tenepes implica na renovação íntima inevitável da conscin. Torna-se incompatível ao praticante da tenepes, manter estes 30 hábitos ou posturas anticosmoéticas:|1. Apelar sempre para mancias e adivinhações em suas decisões no dia-a-dia.|2. Bater na madeira quantas vezes sejam, escravo de uma superstição irracional.|3. Carregar um badulaque ou patuá dependurado no pescoço ou na camisa.|4. Chorar habitualmente uma vez por semana, sob alta insegurança e insatisfação.|5. Colecionar, ingenuamente, armas de fogo: uma autoimprudência primária.|6. Cultivar a gurulatria de qualquer tipo ou uma autossujeição consciencial.|7. Cultivar um posicionamento pessimista e cronicificado perante o Universo.|8. Fazer promessas irracionais, ou seja: não confiar na Multidimensionalidade.|9. Fumar: um vício primitivo e bloqueador irreparável das energias conscienciais (ECs) do cardiochacra.|10. Funcionar profissionalmente a serviço de matadouro de animais, ou abatedouro de aves.|11. Manter capela, altar ou congá dentro de casa, sob o jugo de misticismos infantis.|12. Manter o peso corporal excessivo (obesidade psicológica), aumentado por bulimia ou vida sedentária.|13. Passar por noitadas promíscuas várias vezes a cada mês (assedialidade).|14. Pensar e se preocupar tão-somente com a sua família nuclear *(megaegocarma).|*15. Praticar, por exemplo, o *tiro aos pombos* ou a condição da zooconvivialidade patológica.|16. Seguir com uma vida intrafísica desregrada ou essencialmente desorganizada.|17. Sentir insegurança, manifesta ou transparente em seus atos, na vida cotidiana.|18. Ser motociclista, sob o alto risco energético da vida locomotora do motoqueiro.|19. Ser partidário ou apologista, mesmo sincero, da legalização da pena de morte.|20. Ser usuário, doente, de álcool ou drogas em geral, tanto leves quanto pesadas.|21. Sofrer miniassédios inconscientes e habituais, contudo evidentes para os outros.|22. Ter e usar porte de arma, em uma evocação autoconsciente da matança subumana.|23. Ter existência o tempo todo improdutiva, sem nenhuma autocriatividade.|24. Ter ocupação que implique, de algum modo, em repressão de consciências.|25. Trabalhar, ainda mesmo *no pesado*, com motosserra, em qualquer zona rural (fitoconvivialidade patológica).|26. Viver em um estado de permanente insociabilidade ou em um eremitismo conventual.|27. Viver preso a uma doutrina sectária, no antiuniversalismo medíocre e medieval.|28. Viver submisso ao hábito depressivo da ingestão de *bolinhas* ou estupefacientes.|29. Viver todo o tempo sem domicílio intrafísico fixo ou em um nomadismo impulsivo.|30. Voar de asa delta: o voo livre é um esporte de alto risco, mortífero ou suicida.</t>
+    <t>**Consciencioterapia.** A prática diária da tenepes implica na renovação íntima inevitável da conscin. Torna-se incompatível ao praticante da tenepes, manter estes 30 hábitos ou posturas anticosmoéticas: | 1. Apelar sempre para mancias e adivinhações em suas decisões no dia-a-dia. | 2. Bater na madeira quantas vezes sejam, escravo de uma superstição irracional. | 3. Carregar um badulaque ou patuá dependurado no pescoço ou na camisa. | 4. Chorar habitualmente uma vez por semana, sob alta insegurança e insatisfação. | 5. Colecionar, ingenuamente, armas de fogo: uma autoimprudência primária. | 6. Cultivar a gurulatria de qualquer tipo ou uma autossujeição consciencial. | 7. Cultivar um posicionamento pessimista e cronicificado perante o Universo. | 8. Fazer promessas irracionais, ou seja: não confiar na Multidimensionalidade. | 9. Fumar: um vício primitivo e bloqueador irreparável das energias conscienciais (ECs) do cardiochacra. | 10. Funcionar profissionalmente a serviço de matadouro de animais, ou abatedouro de aves. | 11. Manter capela, altar ou congá dentro de casa, sob o jugo de misticismos infantis. | 12. Manter o peso corporal excessivo (obesidade psicológica), aumentado por bulimia ou vida sedentária. | 13. Passar por noitadas promíscuas várias vezes a cada mês (assedialidade). | 14. Pensar e se preocupar tão-somente com a sua família nuclear *(megaegocarma).* | 15. Praticar, por exemplo, o *tiro aos pombos* ou a condição da zooconvivialidade patológica. | 16. Seguir com uma vida intrafísica desregrada ou essencialmente desorganizada. | 17. Sentir insegurança, manifesta ou transparente em seus atos, na vida cotidiana. | 18. Ser motociclista, sob o alto risco energético da vida locomotora do motoqueiro. | 19. Ser partidário ou apologista, mesmo sincero, da legalização da pena de morte. | 20. Ser usuário, doente, de álcool ou drogas em geral, tanto leves quanto pesadas. | 21. Sofrer miniassédios inconscientes e habituais, contudo evidentes para os outros. | 22. Ter e usar porte de arma, em uma evocação autoconsciente da matança subumana. | 23. Ter existência o tempo todo improdutiva, sem nenhuma autocriatividade. | 24. Ter ocupação que implique, de algum modo, em repressão de consciências. | 25. Trabalhar, ainda mesmo *no pesado*, com motosserra, em qualquer zona rural (fitoconvivialidade patológica). | 26. Viver em um estado de permanente insociabilidade ou em um eremitismo conventual. | 27. Viver preso a uma doutrina sectária, no antiuniversalismo medíocre e medieval. | 28. Viver submisso ao hábito depressivo da ingestão de *bolinhas* ou estupefacientes. | 29. Viver todo o tempo sem domicílio intrafísico fixo ou em um nomadismo impulsivo. | 30. Voar de asa delta: o voo livre é um esporte de alto risco, mortífero ou suicida.</t>
   </si>
   <si>
     <t>**Hábitos.** Se você ainda mantém apenas 3 destes 30 hábitos pessoais, pode estar certo: a tenepes sadia e eficaz, ainda *passa longe* de você.</t>
   </si>
   <si>
-    <t>***Indicações.*** É recomendável a prática diária da tenepes, com horário marcado, tão-somente a 4 tipos de pessoas ou conscins:|**1. Veteranos.** Às conscins mais ou menos desenvolvidas parapsiquicamente ou veteranas quanto às *autodefesas energéticas e parapsíquicas.|***2. Desassediados.** Às conscins sem problemas de assedialidade interconsciencial *de monta,* inteiramente seguras do que fazem. Não precisa, contudo, a conscin ser ou viver qual um *desperto* ou desassediado permanente total. Muito pelo contrário. A condução da conscin à desperticidade, através da tenepes, acontece pelo *auto*desassédio consciencial gradativo, executado através do *hetero*desassédio interconsciencial diário em pacientes – consciexes e conscins enfermas – situados à distância. A tenepes é a técnica ideal de *autodefesa antiassediadora,* de caráter multidimensional.|**3. Flexíveis.** Às conscins conscientes da flexibilidade holochacral, EV, recepção e absorção de ECs, e as dezenas de manobras e desempenhos bioenergéticos já existentes, aplicáveis e exercidos na cotidianidade.|**4. Presidiários.** A tenepes, assim como as projeções conscienciais lúcidas, são especialmente indicadas para serem praticadas pelos presidiários em geral que desejarem mudar para melhor o rumo do próprio destino, incapacitados que se acham de se deslocarem fisicamente pelas próprias circunstâncias humanas restringidoras; e que atendam às especificações, traf*o*res ou traços pessoais indicados anteriormente. Em razão das próprias circunstâncias da vida, a tenepes do presidiário será de meia-força tendo em vista as características de sua vida afetivo-sexual e outras repressões.</t>
+    <t>***Indicações.*** É recomendável a prática diária da tenepes, com horário marcado, tão-somente a 4 tipos de pessoas ou conscins: | **1. Veteranos.** Às conscins mais ou menos desenvolvidas parapsiquicamente ou veteranas quanto às *autodefesas energéticas e parapsíquicas.* | **2. Desassediados.** Às conscins sem problemas de assedialidade interconsciencial *de monta,* inteiramente seguras do que fazem. Não precisa, contudo, a conscin ser ou viver qual um *desperto* ou desassediado permanente total. Muito pelo contrário. A condução da conscin à desperticidade, através da tenepes, acontece pelo *auto*desassédio consciencial gradativo, executado através do *hetero*desassédio interconsciencial diário em pacientes – consciexes e conscins enfermas – situados à distância. A tenepes é a técnica ideal de *autodefesa antiassediadora,* de caráter multidimensional. | **3. Flexíveis.** Às conscins conscientes da flexibilidade holochacral, EV, recepção e absorção de ECs, e as dezenas de manobras e desempenhos bioenergéticos já existentes, aplicáveis e exercidos na cotidianidade. | **4. Presidiários.** A tenepes, assim como as projeções conscienciais lúcidas, são especialmente indicadas para serem praticadas pelos presidiários em geral que desejarem mudar para melhor o rumo do próprio destino, incapacitados que se acham de se deslocarem fisicamente pelas próprias circunstâncias humanas restringidoras; e que atendam às especificações, traf*o*res ou traços pessoais indicados anteriormente. Em razão das próprias circunstâncias da vida, a tenepes do presidiário será de meia-força tendo em vista as características de sua vida afetivo-sexual e outras repressões.</t>
+  </si>
+  <si>
+    <t>20. INDICAÇÕES DA TENEPES</t>
   </si>
   <si>
     <t>UMA DAS FINALIDADES DA TENEPES É CONDUZIR A CONSCIÊNCIA HUMANA À DESPERTICIDADE.</t>
@@ -614,15 +808,21 @@
     <t>**Conteúdo.** O melhor conteúdo prático nas aplicações dos fenômenos das energias conscienciais da pessoa ou conscin é a vivência da tenepes.</t>
   </si>
   <si>
-    <t>***Utilidades.*** Existem inúmeras utilidades e aplicações holocarmicamente evolutivas da tenepes, dentre as quais estas 7:|**1. Cobertura.** A tenepes mantém a cobertura extrafísica positiva, a *concha protetora,* ou a *boa assistência* permanente, multidimensional, para a vida humana do projetor ou projetora consciente, a obtenção da *condição da supersaúde.|**2. Continuum.*** Os hábitos de exteriorização de ECs assistenciais podem conduzir o praticante da tenepes à centralização ou fundamentação do ego, o mais elevado estado de equilíbrio que o ser humano, ou conscin, consegue atingir. Nesse ponto, quase sempre se instala o acoplamento do seu mentalsoma ao mentalsoma de uma consciência desperta ou orientador evolutivo, na serena condição evoluída do *continuum* de tomada da consciencialidade.|**3. Hiperpensenes.** O estado ou o período de tempo das transmissões energéticas, durante a prática da tenepes, mostra-se altamente propício à assimilação de ideias novas, originais ou hiperpensenes, ao praticante atento, homem ou mulher.|**4. Parapatologias.** Uma das utilidades básicas da tenepes é sanar os distúrbios do âmbito da parapatologia do psicossoma, dentre eles as sequelas do restringimento intrafísico da consciex que passou recentemente pela dessoma. Por exemplo: a recuperação mais rápida da maturidade extrafísica para aquelas consciências que sofreram a dessoma em tenra idade física ou no período da adolescência, e que se tornam crianças extrafísicas que merecem ou precisam retornar a ser consciencialmente adultas mais depressa ou em pouco tempo. Nesses casos, as ECs troposféricas da conscin, praticante da tenepes, atuam de modo positivo com possibilidade de *rapport* maior na extração das energias ainda muito humanas, afins, remanescentes, vinculadas à consciex.|**5. Primener.** A tenepes permite ao praticante aferir a sua condição energética do dia, da semana, ou do período atual da suaexistência humana, inclusive os períodos evoluídos de primener, ou primavera energética pessoal.|**6. Recessos.** Na exteriorização assistencial de ECs com horário marcado, pré-fixado, mantido com disciplina e perseverança, está a melhor técnica para o projetor consciente veterano evitar o recesso prolongado na produção desenvolta das projeções conscientes. Por outro lado, podem sobrevir recessos na tenepes, quanto à intensidade e qualidade dos serviços assistenciais prestados, à semelhança dos que ocorrem no desenvolvimento das projeções conscientes.|**7. Proéxis.** A execução regular da assistência a outras consciências desestabilizadas, através da tenepes, faz a conscin observar, inevitavelmente, com atenção e cuidado maior, o emprego do seu *holossoma* e a manutenção do próprio *soma,* em particular, e tudo o que diz respeito à sua higiene, saúde, utilização da bioenergética pessoal, autodisciplina, e à realização crescente das obrigações da proéxis.</t>
-  </si>
-  <si>
-    <t>**Dimensões.** As energias conscienciais atuam além do espaço e do tempo. Dentre as dimensões mais afins às possibilidades de nossas manifestações pensênicas, nas práticas da tenepes, de acordo com as consciências que se manifestam em cada uma, destacam-se 3:|**1. Troposfera** (Intrafisicalidade)**:** pré-serenão ou desperto praticantes da tenepes; minipeças assistenciais; conscins assistidas; assediadores humanos conscientes e inconscientes**.|2. Paratroposfera** (Extrafisicalidade)**:** consciexes assistidas; assediadores extrafísicos conscientes e inconscientes; comunidades extrafísicas não-evoluídas; maximecanismo assistencial**.|3. Comunidades extrafísicas evoluídas** (Extrafisicalidade)**:** amparadores; orientadores evolutivos; maximecanismo assistencial; Serenões; Consciências Livres.</t>
+    <t>21. UTILIDADES DA TENEPES</t>
+  </si>
+  <si>
+    <t>***Utilidades.*** Existem inúmeras utilidades e aplicações holocarmicamente evolutivas da tenepes, dentre as quais estas 7: | **1. Cobertura.** A tenepes mantém a cobertura extrafísica positiva, a *concha protetora,* ou a *boa assistência* permanente, multidimensional, para a vida humana do projetor ou projetora consciente, a obtenção da *condição da supersaúde.* | ***2. Continuum.*** Os hábitos de exteriorização de ECs assistenciais podem conduzir o praticante da tenepes à centralização ou fundamentação do ego, o mais elevado estado de equilíbrio que o ser humano, ou conscin, consegue atingir. Nesse ponto, quase sempre se instala o acoplamento do seu mentalsoma ao mentalsoma de uma consciência desperta ou orientador evolutivo, na serena condição evoluída do *continuum* de tomada da consciencialidade. | **3. Hiperpensenes.** O estado ou o período de tempo das transmissões energéticas, durante a prática da tenepes, mostra-se altamente propício à assimilação de ideias novas, originais ou hiperpensenes, ao praticante atento, homem ou mulher. | **4. Parapatologias.** Uma das utilidades básicas da tenepes é sanar os distúrbios do âmbito da parapatologia do psicossoma, dentre eles as sequelas do restringimento intrafísico da consciex que passou recentemente pela dessoma. Por exemplo: a recuperação mais rápida da maturidade extrafísica para aquelas consciências que sofreram a dessoma em tenra idade física ou no período da adolescência, e que se tornam crianças extrafísicas que merecem ou precisam retornar a ser consciencialmente adultas mais depressa ou em pouco tempo. Nesses casos, as ECs troposféricas da conscin, praticante da tenepes, atuam de modo positivo com possibilidade de *rapport* maior na extração das energias ainda muito humanas, afins, remanescentes, vinculadas à consciex. | **5. Primener.** A tenepes permite ao praticante aferir a sua condição energética do dia, da semana, ou do período atual da suaexistência humana, inclusive os períodos evoluídos de primener, ou primavera energética pessoal. | **6. Recessos.** Na exteriorização assistencial de ECs com horário marcado, pré-fixado, mantido com disciplina e perseverança, está a melhor técnica para o projetor consciente veterano evitar o recesso prolongado na produção desenvolta das projeções conscientes. Por outro lado, podem sobrevir recessos na tenepes, quanto à intensidade e qualidade dos serviços assistenciais prestados, à semelhança dos que ocorrem no desenvolvimento das projeções conscientes. | **7. Proéxis.** A execução regular da assistência a outras consciências desestabilizadas, através da tenepes, faz a conscin observar, inevitavelmente, com atenção e cuidado maior, o emprego do seu *holossoma* e a manutenção do próprio *soma,* em particular, e tudo o que diz respeito à sua higiene, saúde, utilização da bioenergética pessoal, autodisciplina, e à realização crescente das obrigações da proéxis.</t>
+  </si>
+  <si>
+    <t>**Dimensões.** As energias conscienciais atuam além do espaço e do tempo. Dentre as dimensões mais afins às possibilidades de nossas manifestações pensênicas, nas práticas da tenepes, de acordo com as consciências que se manifestam em cada uma, destacam-se 3: | **1. Troposfera** (Intrafisicalidade): pré-serenão ou desperto praticantes da tenepes; minipeças assistenciais; conscins assistidas; assediadores humanos conscientes e inconscientes. | **2. Paratroposfera** (Extrafisicalidade): consciexes assistidas; assediadores extrafísicos conscientes e inconscientes; comunidades extrafísicas não-evoluídas; maximecanismo assistencial. | **3. Comunidades extrafísicas evoluídas** (Extrafisicalidade): amparadores; orientadores evolutivos; maximecanismo assistencial; Serenões; Consciências Livres.</t>
   </si>
   <si>
     <t>**Grupo.** É sobejamente conhecido, em qualquer empreendimento humano, que a EC positiva, grupal, coletiva, ou melhor, nascida de 1 grupo homogêneo e coeso de consciências transmissoras, que apresentam efetivo senso de união e afinidade marcante, quando reunidas, manifesta-se mais forte, intensa, vigorosa e curativamente, beneficiando a maior número de consciências receptoras do que a EC individual, isolada, derivada de 1 consciência apenas.</t>
   </si>
   <si>
+    <t>22. SINTONIA</t>
+  </si>
+  <si>
     <t>**Audiência.** O artista na ribalta, o orador na tribuna, o advogado no tribunal (corte), o professor na cátedra, e as conscins parapsíquicas nos estados alterados da consciência, têm conhecimento da energia emanada da *audiência viva.* Daí nasceu a prática da sessão mediúnica ou parapsíquica.</t>
   </si>
   <si>
@@ -647,7 +847,7 @@
     <t>**Singularidade.** Quem experimenta uma condição singular, *top* ou ímpar, de responsabilidade maior quanto ao autoconhecimento no meio da população terrestre atual, abraçará, inevitavelmente, no tempo certo ou oportuno, as práticas da tenepes.</t>
   </si>
   <si>
-    <t>**Condições.** Eis 9 condições intraconscienciais que podem servir de unidades de medida para a classificação da singularidade referida:|1. Reconhecer os *autotraf**a**res e autotraf**o**res.|*2. Procurar sair do *porão consciencial.|*3. Acatar a *cosmoética.|*4. Admitir o imperativo da *maxifraternidade.|*5. Ter feito *curso intermissivo.|*6. Dispor de um *macrossoma.|*7. Praticar a *invéxis ou recéxis.|*8. Querer ampliar a sua *tares.|*9. Viver autoconsciente da sua *proéxis.*</t>
+    <t>**Condições.** Eis 9 condições intraconscienciais que podem servir de unidades de medida para a classificação da singularidade referida: | 1. Reconhecer os *autotraf**a**res e autotraf**o**res.* | 2. Procurar sair do *porão consciencial.* | 3. Acatar a *cosmoética.* | 4. Admitir o imperativo da *maxifraternidade.* | 5. Ter feito *curso intermissivo.* | 6. Dispor de um *macrossoma.* | 7. Praticar a *invéxis ou recéxis.* | 8. Querer ampliar a sua *tares.* | 9. Viver autoconsciente da sua *proéxis.*</t>
   </si>
   <si>
     <t>A TENEPES É O CURSO PRÁTICO PERMANENTE DE PÓS-GRADUAÇÃO DO CONSCIENCIÓLOGO.</t>
@@ -662,7 +862,10 @@
     <t>**Período.** É sempre inteligente atentar-se para o período existencial que se vive ou o patamar evolutivo do praticante com a tenepes.</t>
   </si>
   <si>
-    <t>***Estágios.*** Observa-se bem claramente que existem, pelo menos, 3 estágios ou períodos bem distintos quanto às práticas da tenepes:|**1. Inicial.** O estágio da instalação das práticas da tenepes para o resto da vida intrafísica, mais difícil, perdura, em média, por *6 meses.|***2. Manutenção.** A consolidação das práticas energético-assistenciais da tenepes ocorre dentro de um período médio de *3 anos.|***3. Evolução.** As práticas da tenepes evoluída, *a qualquer hora,* permanentemente, sem misticismos, com *os pés na rocha* e o mentalsoma no Cosmos, em geral somente acontece após *1 década* de exercícios diários.</t>
+    <t>23. ESTÁGIOS NA TENEPES</t>
+  </si>
+  <si>
+    <t>***Estágios.*** Observa-se bem claramente que existem, pelo menos, 3 estágios ou períodos bem distintos quanto às práticas da tenepes: | **1. Inicial.** O estágio da instalação das práticas da tenepes para o resto da vida intrafísica, mais difícil, perdura, em média, por *6 meses.* | **2. Manutenção.** A consolidação das práticas energético-assistenciais da tenepes ocorre dentro de um período médio de *3 anos.* | **3. Evolução.** As práticas da tenepes evoluída, *a qualquer hora,* permanentemente, sem misticismos, com *os pés na rocha* e o mentalsoma no Cosmos, em geral somente acontece após *1 década* de exercícios diários.</t>
   </si>
   <si>
     <t>**Especialização.** No estágio evoluído das práticas da tenepes, o praticante pode apresentar desempenhos especializados, por exemplo: ocorrência sadia e mais frequente de determinado fenômeno parapsíquico; atendimento com amparador de consciexes com carências específicas; e outros.</t>
@@ -674,19 +877,22 @@
     <t>**Sinapses.** A tenepes exige a criação de sinapses específicas (neopensenes), de alta qualidade em função da multidimensionalidade ou do caráter holossomático do processo, no cérebro *do* (ou *da*) praticante, o que é obtido somente em um período médio de cerca de 2 anos.</t>
   </si>
   <si>
-    <t>**Atributos.** Na autoanálise magna na condição de consciência, o praticante da tenepes há de pesquisar se consegue viver sabendo e se utilizando destes 6 atributos seus:|**1. Atemporalidade.|2. Imaterialidade.|3. Imortalidade.|4. Inalienabilidade**.|**5. Objetividade.|6. Racionalidade.**</t>
+    <t>24. ESTÁGIO AVANÇADO</t>
+  </si>
+  <si>
+    <t>**Atributos.** Na autoanálise magna na condição de consciência, o praticante da tenepes há de pesquisar se consegue viver sabendo e se utilizando destes 6 atributos seus: | **1. Atemporalidade.** | **2. Imaterialidade.** | **3. Imortalidade.** | **4. Inalienabilidade**. | **5. Objetividade.** | **6. Racionalidade.**</t>
   </si>
   <si>
     <t>**Autoconhecimentos.** A evolução da tenepes exige esses autoconhecimentos listados atrás.</t>
   </si>
   <si>
-    <t>***Avançado.*** Em um estágio mais avançado, as práticas da tenepes podem ser extrafisicamente orientadas para efeitos intrafísicos ou ectoplásmicos, com estas 10 características nas manifestações:|**1. Decúbito.** Emprego da posição corporal em decúbito dorsal do praticante.|**2. Temperatura.** Queda da temperatura corporal e ambiental (ectoplasmia).|**3. Efeitos.** Fenômenos amenos de efeitos parapsíquicos ou bioenergéticos, mas intrafísicos (macro-PK).|**4. Soma.** Modificação das exteriorizações energéticas quanto ao soma, ou seja: *mais* através do tronco e da cabeça, e *menos* através dos braços e mãos.|***5.* Respiração.** Mudança da frequência respiratória durante as transmissões energéticas.|**6. Umbilicochacra.** Predominância evidente da atuação do umbilicochacra nas transmissões energéticas.|**7. Abdome.** Sensação de puxamento para cima, através do abdome, a cada exteriorização energética.|**8. Musculatura.** Fortalecimento da musculatura abdominal (massa muscular enrijecida e aumentada).|**9. Metabolismo.** Podem ocorrer alterações do metabolismo do praticante que sentirá maior necessidade de ingerir *glúcidos* (açúcar), em certos casos; aumento da *diurese;* ou ocorrência de *sede,* com ingestão maior de líquidos.|**10. Hipertrofia.** Cessação da hipertrofia da musculatura dos braços e ombros gerada pelos movimentos intensos e diários das transmissões energéticas anteriores.</t>
+    <t>***Avançado.*** Em um estágio mais avançado, as práticas da tenepes podem ser extrafisicamente orientadas para efeitos intrafísicos ou ectoplásmicos, com estas 10 características nas manifestações: | **1. Decúbito.** Emprego da posição corporal em decúbito dorsal do praticante. | **2. Temperatura.** Queda da temperatura corporal e ambiental (ectoplasmia). | **3. Efeitos.** Fenômenos amenos de efeitos parapsíquicos ou bioenergéticos, mas intrafísicos (macro-PK). | **4. Soma.** Modificação das exteriorizações energéticas quanto ao soma, ou seja: *mais* através do tronco e da cabeça, e *menos* através dos braços e mãos. | ***5.* Respiração.** Mudança da frequência respiratória durante as transmissões energéticas. | **6. Umbilicochacra.** Predominância evidente da atuação do umbilicochacra nas transmissões energéticas. | **7. Abdome.** Sensação de puxamento para cima, através do abdome, a cada exteriorização energética. | **8. Musculatura.** Fortalecimento da musculatura abdominal (massa muscular enrijecida e aumentada). | **9. Metabolismo.** Podem ocorrer alterações do metabolismo do praticante que sentirá maior necessidade de ingerir *glúcidos* (açúcar), em certos casos; aumento da *diurese;* ou ocorrência de *sede,* com ingestão maior de líquidos. | **10. Hipertrofia.** Cessação da hipertrofia da musculatura dos braços e ombros gerada pelos movimentos intensos e diários das transmissões energéticas anteriores.</t>
   </si>
   <si>
     <t>AS PRÁTICAS DA TENEPES DEPENDEM SEMPRE DO SOMA SADIO DO PRATICANTE.</t>
   </si>
   <si>
-    <t>**Duração.** Quanto à duração das práticas diárias da tenepes, importa considerar se as transmissões energéticas são *primárias,* assentadas nos braços, ou *evoluídas,* assentadas no tórax. Neste sentido são relevantes 2 variáveis:|**1. Braços.** As transmissões de ECs nas práticas da tenepes, estando o praticante sentado, e com o emprego preponderante da cabeça, braços e mãos, ou seja: predominando a atuação do coronochacra, frontochacra e laringochacra; se fazem com exercícios físicos maiores, mais rapidamente e a sessão da tenepes *demora menos.|***2. Tórax.** As transmissões de ECs nas práticas da tenepes, estando o praticante deitado, e com o emprego preponderante da cabeça, tórax e abdome, ou seja: todos os 7 chacras essenciais ou primários em ação; se fazem com exercícios físicos menos intensos, mais lentamente, e a sessão da tenepes *demora mais,* ocorrendo efeitos ectoplásmicos com frequência maior. Contudo, tudo isso é relativo pois depende das reações psicológicas do praticante em seu relacionamento holossomático com o amparador ou amparadores.</t>
+    <t>**Duração.** Quanto à duração das práticas diárias da tenepes, importa considerar se as transmissões energéticas são *primárias,* assentadas nos braços, ou *evoluídas,* assentadas no tórax. Neste sentido são relevantes 2 variáveis: | **1. Braços.** As transmissões de ECs nas práticas da tenepes, estando o praticante sentado, e com o emprego preponderante da cabeça, braços e mãos, ou seja: predominando a atuação do coronochacra, frontochacra e laringochacra; se fazem com exercícios físicos maiores, mais rapidamente e a sessão da tenepes *demora menos.* | **2. Tórax.** As transmissões de ECs nas práticas da tenepes, estando o praticante deitado, e com o emprego preponderante da cabeça, tórax e abdome, ou seja: todos os 7 chacras essenciais ou primários em ação; se fazem com exercícios físicos menos intensos, mais lentamente, e a sessão da tenepes *demora mais,* ocorrendo efeitos ectoplásmicos com frequência maior. Contudo, tudo isso é relativo pois depende das reações psicológicas do praticante em seu relacionamento holossomático com o amparador ou amparadores.</t>
   </si>
   <si>
     <t>**Semipossessão.** Como se observa, a tenepes é uma semipossessão consciente, maior, sadia, onipresente e permanente por parte do amparador no período desenvolvido das práticas assistenciais.</t>
@@ -695,7 +901,7 @@
     <t>**Camelo.** Nesse estágio avançado das práticas da tenepes, o praticante já dispõe de reservas ectoplásmicas para assistência energética maior – *parametabolismo energético* – a toda hora, ao modo da condição do camelo e seu *metabolismo hídrico* no deserto.</t>
   </si>
   <si>
-    <t>**Desenvolvimentos.** Há 2 tipos de desenvolvimentos das práticas da tenepes quanto ao emprego específico, mais predominante, dos chacras básicos:|**1. Palmochacras.** A prática da *tenepes primária* é desenvolvida através dos 2 *palmochacras* do praticante, estando, atrás, o cardiochacra. Ocorre, aqui, obviamente, antes de tudo, o *circuito holochacral clássico,* o mais comum na existência da conscin: absorvemos *energia imanente* pelos plantochacras e doamos *energia consciencial* pelos palmochacras.|**2. Frontochacra.** A prática da *tenepes avançada* é desenvolvida através do *frontochacra* do praticante, estando, acima, o coronochacra.</t>
+    <t>**Desenvolvimentos.** Há 2 tipos de desenvolvimentos das práticas da tenepes quanto ao emprego específico, mais predominante, dos chacras básicos: | **1. Palmochacras.** A prática da *tenepes primária* é desenvolvida através dos 2 *palmochacras* do praticante, estando, atrás, o cardiochacra. Ocorre, aqui, obviamente, antes de tudo, o *circuito holochacral clássico,* o mais comum na existência da conscin: absorvemos *energia imanente* pelos plantochacras e doamos *energia consciencial* pelos palmochacras. | **2. Frontochacra.** A prática da *tenepes avançada* é desenvolvida através do *frontochacra* do praticante, estando, acima, o coronochacra.</t>
   </si>
   <si>
     <t>**Superestimações.** O praticante da tenepes, *ao se tornar veterano,* não mais superestima, qual ocorre com largo percentual dos componentes da Humanidade, as religiões, as ciências convencionais, as artes, as ideologias humanas em geral e os envolvimentos intrafísicos transitórios, em função das próprias realidades multidimensionais que já identificou, aceitou e, agora, procura vivenciar.</t>
@@ -716,24 +922,30 @@
     <t>**Praticidade.** Os exercícios diários da tenepes são extremamente práticos quanto à vida intrafísica.</t>
   </si>
   <si>
-    <t>***Vantagens.*** Até a conscin que pelos seus compromissos individuais, sociais, *não consegue* exercer o parapsiquismo *nem 2* vezes por semana em um grupo de estudos práticos especializados, pode praticar a tenepes, entre outras, com 14 vantagens evidentes:|**1. Periodicidade.** As práticas podem ser desenvolvidas todo dia.|**2. Isolamento.** As tarefas do praticante da tenepes podemser alcançadas sempre estando ele sozinho do ponto de vista espacial ou intrafísico.|**3. Discrição.** As tarefas podem ser mantidas sigilosamente porque não há a presença testemunhal nem a participação de outras conscins ou animais subumanos no *laboratório* do praticante.|**4. Desinibição.** As excessivas autocensuras são eliminadas porque o praticante se vê isolado, com a sua pensenidade, em suas vivências ou manifestações.|**5. Horário.** Todos os trabalhos podem ocorrer fora do horário comercial, do calendário dos dias úteis ou feriados, e dos esquemas dos compromissos humanos, profissionais ou sociais.|**6. Local.** Tudo se passa na intimidade do domicílio, casa ou apartamento do interessado ou interessada, em um só local acolhedor – o *próprio campo* – escolhido pela dupla praticante-amparador de modo permanente.|**7. Domicílio.** O desenrolar das tarefas da tenepes acontecem sem quaisquer problemas de condução, translado ou trânsito, o que evita naturalmente os *acidentes de percurso parapsíquicos* nos períodos de tempo anteriores às práticas diárias.|**8. Informalidade.** As convenções, etiquetas, cerimônias e leis condicionadas pela Socin, ainda patológica, não raro, excessivas, componentes do *rolo compressor das inutilidades intrafísicas,* são completamente eliminadas.|**9. Independência.** A assistência interconsciencial é executada independente da presença e do juízo heterocrítico de outras conscins do grupo evolutivo, o que evita naturalmente as intrusõesegoicas, interconscins, indesejáveis no caso. O praticante da tenepes há de ser autossuficiente em sua vida.|**10. Autocomprovações.** Os fundamentos da Conscienciologia recomendam que tudo que uma consciência afirmar teoricamente já deve ter comprovado na sua vida prática, em si mesma. Só é lógico aceitar as coisas e os fatos baseado na teoria e na vivência em conjunto, experimentada, dos fenômenos universais reagindo na pessoa. A holomaturidade começa por essa providência essencial. A vivência da tenepes permite as autocomprovações em um nível ímpar.As práticas da tenepes através dos exercícios oferecem, além de outras, para o próprio praticante, 7 provas definitivas:|1. Existência do **psicossoma.|**2. Existência do **holochacra.|**3. Vivência da **multidimensionalidade** da consciência.|4. Vivência da **projetabilidade lúcida** (PL) da conscin.|**5. Sobrevivência** da consciência à dessoma.|6. Vivência do **parapsiquismo** mais evoluído.|7. Existência e coexistência assistencial com o **amparador.|11. Gratificação.** A gratificação que a tenepes traz é indireta, multidimensional, evolutiva.</t>
+    <t>25. VANTAGENS DA TENEPES</t>
+  </si>
+  <si>
+    <t>***Vantagens.*** Até a conscin que pelos seus compromissos individuais, sociais, *não consegue* exercer o parapsiquismo *nem 2* vezes por semana em um grupo de estudos práticos especializados, pode praticar a tenepes, entre outras, com 14 vantagens evidentes: | **1. Periodicidade.** As práticas podem ser desenvolvidas todo dia. | **2. Isolamento.** As tarefas do praticante da tenepes podemser alcançadas sempre estando ele sozinho do ponto de vista espacial ou intrafísico. | **3. Discrição.** As tarefas podem ser mantidas sigilosamente porque não há a presença testemunhal nem a participação de outras conscins ou animais subumanos no *laboratório* do praticante. | **4. Desinibição.** As excessivas autocensuras são eliminadas porque o praticante se vê isolado, com a sua pensenidade, em suas vivências ou manifestações. | **5. Horário.** Todos os trabalhos podem ocorrer fora do horário comercial, do calendário dos dias úteis ou feriados, e dos esquemas dos compromissos humanos, profissionais ou sociais. | **6. Local.** Tudo se passa na intimidade do domicílio, casa ou apartamento do interessado ou interessada, em um só local acolhedor – o *próprio campo* – escolhido pela dupla praticante-amparador de modo permanente. | **7. Domicílio.** O desenrolar das tarefas da tenepes acontecem sem quaisquer problemas de condução, translado ou trânsito, o que evita naturalmente os *acidentes de percurso parapsíquicos* nos períodos de tempo anteriores às práticas diárias. | **8. Informalidade.** As convenções, etiquetas, cerimônias e leis condicionadas pela Socin, ainda patológica, não raro, excessivas, componentes do *rolo compressor das inutilidades intrafísicas,* são completamente eliminadas. | **9. Independência.** A assistência interconsciencial é executada independente da presença e do juízo heterocrítico de outras conscins do grupo evolutivo, o que evita naturalmente as intrusõesegoicas, interconscins, indesejáveis no caso. O praticante da tenepes há de ser autossuficiente em sua vida. | **10. Autocomprovações.** Os fundamentos da Conscienciologia recomendam que tudo que uma consciência afirmar teoricamente já deve ter comprovado na sua vida prática, em si mesma. Só é lógico aceitar as coisas e os fatos baseado na teoria e na vivência em conjunto, experimentada, dos fenômenos universais reagindo na pessoa. A holomaturidade começa por essa providência essencial. A vivência da tenepes permite as autocomprovações em um nível ímpar.As práticas da tenepes através dos exercícios oferecem, além de outras, para o próprio praticante, 7 provas definitivas: | 1. Existência do **psicossoma.** | 2. Existência do **holochacra.** | 3. Vivência da **multidimensionalidade** da consciência. | 4. Vivência da **projetabilidade lúcida** (PL) da conscin. | **5. Sobrevivência** da consciência à dessoma. | 6. Vivência do **parapsiquismo** mais evoluído. | 7. Existência e coexistência assistencial com o **amparador.** | **11. Gratificação.** A gratificação que a tenepes traz é indireta, multidimensional, evolutiva.</t>
   </si>
   <si>
     <t>A TENEPES É UMA EMPREITADA ASSISTENCIAL COM RENDIMENTO EVOLUTIVO DE EXCEÇÃO.</t>
   </si>
   <si>
-    <t>&gt; **12. Negócio.** A tenepes, se tomada na condição de *negócio assistencial,* é obviamente o melhor tipo de *franchising* (franquia) evolutivo com a multidimensionalidade para a consciência intrafísica. Você dá 1 hora, a cada dia, de assistência aos necessitados extrafísicos e intrafísicos, e recebe 23 horas de assistência energética, intra e extrafísica, dos amparadores, durante o resto da sua existência humana, ou segundo a *fórmula:* 23 X 1 ou 100% = 23 ou 2.300 %</t>
+    <t>**12. Negócio.** A tenepes, se tomada na condição de *negócio assistencial,* é obviamente o melhor tipo de *franchising* (franquia) evolutivo com a multidimensionalidade para a consciência intrafísica. Você dá 1 hora, a cada dia, de assistência aos necessitados extrafísicos e intrafísicos, e recebe 23 horas de assistência energética, intra e extrafísica, dos amparadores, durante o resto da sua existência humana, ou segundo a *fórmula:* 23 X 1 ou 100% = 23 ou 2.300 %</t>
   </si>
   <si>
     <t>A TENEPES É O DIVISOR DE ÁGUAS NA VIDA DO PRATICANTE: ANTES E DEPOIS DA TENEPES.</t>
   </si>
   <si>
-    <t>**13. Divisor.** A tenepes funciona por divisor de águas na existência do praticante, que a dividirá em 2 períodos – *antes* da tenepes e *depois* da tenepes – em razão da mudança para melhor do holopensene pessoal, incluindo aí 3 realidades geográficas e parageográficas que sustentam as práticas multidimensionais:|**1. Base física,** especificamente geográfica.|**2. Alcova energeticamente blindada,** geográfica e *para*geográfica.|**3. Ofiex** ou oficina extrafísica, especificamente *para*geográfica.|**  **</t>
+    <t>**13. Divisor.** A tenepes funciona por divisor de águas na existência do praticante, que a dividirá em 2 períodos – *antes* da tenepes e *depois* da tenepes – em razão da mudança para melhor do holopensene pessoal, incluindo aí 3 realidades geográficas e parageográficas que sustentam as práticas multidimensionais: | **1. Base física,** especificamente geográfica. | **2. Alcova energeticamente blindada,** geográfica e *para*geográfica. | **3. Ofiex** ou oficina extrafísica, especificamente *para*geográfica.</t>
   </si>
   <si>
     <t>**Sutilezas.** A tenepes permanente apresenta o *paradoxo das sutilezas e ostentações* da *assistencialidade* interconsciencial sadia. Isso é percebido através de inúmeros indicadores personalíssimos, vivenciados, difíceis de serem explicados, por exemplo. Também apresenta, ao mesmo tempo, as sutilezas e ostentações da *assedialidade* doentia percebida através de objetos singelos, por exemplo: blusa com desenhos de escafandros da conscin assistida bitolada; plantas em vasos, sensoriados a distância, carregados de energias conscienciais doentias.</t>
   </si>
   <si>
+    <t>26. SUTILEZAS</t>
+  </si>
+  <si>
     <t>**Complexidades.** Evidentemente, tais fatos *singelos* ou mensagens silenciosas, porém com imenso conteúdo significativo tão-somente para quem vivencia, são muito *complexos* nas análises de sua transcendência a maior. Só *o* (ou *a*) praticante veterano*(a)* da tenepes poderá compreender tais particularidades personalíssimas.</t>
   </si>
   <si>
@@ -743,18 +955,27 @@
     <t>**Variáveis.** Nas práticas da tenepes interessam sobremaneira, dentre muitas outras, 21 variáveis: acoplamento áurico; base física; campo energético instalado; cérebro; cosmoconsciência; cosmoética vivenciada; desperticidade lúcida; dimener; energizador lúcido; epicon; homeostase holossomática; homeostase orgânica; multidimensionalidade; ofiex; paracérebro; parapsiquismo em geral; sinalética bioenergética; soltura holochacral; troposfera terrestre; vida alternante lúcida; vida energética.</t>
   </si>
   <si>
-    <t>**Hábitos.** Eis 5 hábitos assemelhados, ou 5 sessões diárias ou de *todo dia,* recomendadas com lógica na administração das práticas da tenepes, bem como a fim de se desenvolver o autoconhecimento através da Conscienciologia:|**1. Roupas.** Mudar as *roupas pessoais* (trajes) todo dia (sessão social ou sociabilidade).|**2. Banho.** Tomar *banho* todo dia (sessão *higiência* diária dosoma).|**3. Refeições.** Ter *refeições* – uma *quente,* pelo menos – todo dia (sessão gastronômica ou sobrevivência do soma).|**3. Sexo.** Fazer *sexo* todo dia (sessão *sexual* diária), o que implica na existência e no *contato energético* mais íntimo e intrafísico com outra conscin.|**4. Tenepes.** Praticar a *tenepes* todo dia (sessão *assistencial* diária), o que implica no *contato energético* mais íntimo e multidimensional com outra consciex – o amparador – e outras consciências eventuais, assistidas.</t>
+    <t>**Hábitos.** Eis 5 hábitos assemelhados, ou 5 sessões diárias ou de *todo dia,* recomendadas com lógica na administração das práticas da tenepes, bem como a fim de se desenvolver o autoconhecimento através da Conscienciologia: | **1. Roupas.** Mudar as *roupas pessoais* (trajes) todo dia (sessão social ou sociabilidade). | **2. Banho.** Tomar *banho* todo dia (sessão *higiência* diária dosoma). | **3. Refeições.** Ter *refeições* – uma *quente,* pelo menos – todo dia (sessão gastronômica ou sobrevivência do soma). | **3. Sexo.** Fazer *sexo* todo dia (sessão *sexual* diária), o que implica na existência e no *contato energético* mais íntimo e intrafísico com outra conscin. | **4. Tenepes.** Praticar a *tenepes* todo dia (sessão *assistencial* diária), o que implica no *contato energético* mais íntimo e multidimensional com outra consciex – o amparador – e outras consciências eventuais, assistidas.</t>
+  </si>
+  <si>
+    <t>27. HÁBITOS DIÁRIOS</t>
   </si>
   <si>
     <t>**Vício.** Quanto à prática do sexo diário que, segundo as estatísticas, atinge a 10% da população da cidade de São Paulo, é bom lembrar a afirmação do escritor patrício, *Érico Veríssimo*: ***“O pior dos vícios sexuais é a abstinência”.***</t>
   </si>
   <si>
-    <t>**Nudez.** Partindo do princípio de que a prática da tenepes se desenvolve com a conscin, na qualidade de praticante sozinho e isolado, da exteriorização de ECs; e, desde que observe a ausência de *correntes de ar* no local, a *temperatura* ambiente adequada, e a utilização correta no momento do *condicionador de ar,* a fim de não contrair um resfriado; ele pode se apassivar parapsiquicamente para os amparadores assistenciais permanecendo inteiramente nu, com toda a naturalidade, sobrevindo daí 2 fatos:|**1. Amparadores.** Os amparadores têm autoconsciencialidade evoluída, analisando a vida através da óptica da multidimensionalidade, empregando o psicossoma, e não se importam com a nudez do praticante.|**2. Assistidos.** Contudo, a nudez do praticante pode afetar as reações das consciexes assistidas, de visual masculino ou feminino – não vem ao caso – doentias, troposféricas, *parapsicóticos pós-dessomáticos* ou que se despertam extrafisicamente em função das próprias transmissões energéticas da tenepes, cujas consciências ainda se acham profundamente envolvidas pelos condicionamentos, repressões, *lavagens cerebrais,* bitolamentos e sacralizações intrafísicas.</t>
+    <t>**Nudez.** Partindo do princípio de que a prática da tenepes se desenvolve com a conscin, na qualidade de praticante sozinho e isolado, da exteriorização de ECs; e, desde que observe a ausência de *correntes de ar* no local, a *temperatura* ambiente adequada, e a utilização correta no momento do *condicionador de ar,* a fim de não contrair um resfriado; ele pode se apassivar parapsiquicamente para os amparadores assistenciais permanecendo inteiramente nu, com toda a naturalidade, sobrevindo daí 2 fatos: | **1. Amparadores.** Os amparadores têm autoconsciencialidade evoluída, analisando a vida através da óptica da multidimensionalidade, empregando o psicossoma, e não se importam com a nudez do praticante. | **2. Assistidos.** Contudo, a nudez do praticante pode afetar as reações das consciexes assistidas, de visual masculino ou feminino – não vem ao caso – doentias, troposféricas, *parapsicóticos pós-dessomáticos* ou que se despertam extrafisicamente em função das próprias transmissões energéticas da tenepes, cujas consciências ainda se acham profundamente envolvidas pelos condicionamentos, repressões, *lavagens cerebrais,* bitolamentos e sacralizações intrafísicas.</t>
+  </si>
+  <si>
+    <t>28. NUDEZ</t>
   </si>
   <si>
     <t>**Assins.** As assins, ou assimilações simpáticas por afinidade, boa intenção, e ascendência energética de doenças, distúrbios ou afecções de certas conscins-pacientes, podem ocorrer nas transmissões energéticas da tenepes, seja de modo consciente ou inconsciente por parte de ambos: o *praticante-assimilador* e o *paciente-assimilado.*</t>
   </si>
   <si>
+    <t>29. ASSINS</t>
+  </si>
+  <si>
     <t>**Remissão.** A remissão definitiva dos sintomas e sinais da conscin-paciente, após algum período de horas, dias, ou até semanas, das transmissões energéticas, é que revela, em muitos casos, a ocorrência das assins.</t>
   </si>
   <si>
@@ -770,7 +991,7 @@
     <t>**Distúrbios.** Exemplos típicos de assim, ou assimilação energética das condições patológicas do soma-holochacra-psicossoma de um enfermo é o da conscin acometida por alterações em 1 membro, seja uma perna que vem apresentando já por longo tempo, dores, edemas, dificuldades de locomoção, e outros distúrbios, sobre os quais já se tentou todos os exames, diagnósticos e terapêuticas convencionais inutilmente, distúrbios esses que desaparecem com as transmissões energéticas da tenepes, inclusive tão-somente à distância.</t>
   </si>
   <si>
-    <t>**Isca.** A *assim* é o efeito mais avançado da condição de isca consciencial assistencial anímico-parapsíquica, com 3 fundamentos:|1. Estado de *rapport* ou de afinização.|2. Existência das *energias conscienciais* (ECs)*.|*3. Fenômeno do *acoplamento áurico.*</t>
+    <t>**Isca.** A *assim* é o efeito mais avançado da condição de isca consciencial assistencial anímico-parapsíquica, com 3 fundamentos: | 1. Estado de *rapport* ou de afinização. | 2. Existência das *energias conscienciais* (ECs). | 3. Fenômeno do *acoplamento áurico.*</t>
   </si>
   <si>
     <t>**Terapêutica.** A assedialidade, neste caso, não é um episódio de assédio interconsciencial como entendemos. A ocorrência é, antes de tudo, terapêutica e não-patológica, embora derive – em número expressivo de casos – de assedialidade crônica e práticas sincréticas de muitas seitas.</t>
@@ -782,7 +1003,10 @@
     <t>**Incêndio.** O praticante da tenepes não precisa ter medo de estar trancado em seu quarto escuro e ocorrer um sinistro, por exemplo, um incêndio no edifício ou casa onde está. Os amparadores estão atentos para quaisquer irregularidades junto ou externas ao local das práticas da tenepes e avisam a tempo, antecipadamente, ao praticante. A vivência da tenepes traz autocomprovações desses fatos de evitação de acidentes de percurso naturalmente para o praticante.</t>
   </si>
   <si>
-    <t>**Escala.** Eis a escala da evolução da *consciência assistencial* da personalidade humana, em 10 estágios, segundo a Conscienciometria:|**1. Pré-serenão.** Conscin vulgar pré-serenona de proéxis medíocre, sem domicílio fixo.|**2. Miniassediado.** Miniassediado eventual comum quanto à assistencialidade interconsciencial.|**3. Praticante.** *Praticante da tenepes auto-organizado.|***4. Isca.** Isca assistencial autoconsciente.|**5. Sensitivo.** Sensitivo parapsíquico de alto nível.|**6. Ofiex.** Responsável por ofiex com domicílio fixo.|**7. Epicon.** Epicon autoconsciente com instalação permanente de campo energético visível da minipeça dentro do maximecanismo assistencial.|**8. Desperto.** Desassediado permanente total ou o desperto.|**9. Completista.** Completista em relação à execução da proéxis a maior (maxiproéxis).|**10. Moratorista.** Recebedor autoconsciente de moréxis ou moratória existencial a maior (maximoréxis).</t>
+    <t>**Escala.** Eis a escala da evolução da *consciência assistencial* da personalidade humana, em 10 estágios, segundo a Conscienciometria: | **1. Pré-serenão.** Conscin vulgar pré-serenona de proéxis medíocre, sem domicílio fixo. | **2. Miniassediado.** Miniassediado eventual comum quanto à assistencialidade interconsciencial. | **3. Praticante.** *Praticante da tenepes auto-organizado.* | **4. Isca.** Isca assistencial autoconsciente. | **5. Sensitivo.** Sensitivo parapsíquico de alto nível. | **6. Ofiex.** Responsável por ofiex com domicílio fixo. | **7. Epicon.** Epicon autoconsciente com instalação permanente de campo energético visível da minipeça dentro do maximecanismo assistencial. | **8. Desperto.** Desassediado permanente total ou o desperto. | **9. Completista.** Completista em relação à execução da proéxis a maior (maxiproéxis). | **10. Moratorista.** Recebedor autoconsciente de moréxis ou moratória existencial a maior (maximoréxis).</t>
+  </si>
+  <si>
+    <t>30. EVOLUÇÃO DA CONSCIÊNCIA</t>
   </si>
   <si>
     <t>**Vontade.** A tenepes não é cura-tudo nem panaceia universal. Por exemplo, a tenepes não vacina o praticante contra a corrupção. Quem vacina o praticante da tenepes contra a corrupção é a vontade e a intencionalidade dele mesmo.</t>
@@ -791,6 +1015,9 @@
     <t>**Síntese.** Fazendo uma síntese de todas as considerações deste texto, até aqui, alcançamos algumas reflexões e conclusões.</t>
   </si>
   <si>
+    <t>31. SALDO CONSCIENCIAL</t>
+  </si>
+  <si>
     <t>**Evolução.** Evoluir é domar completamente e empregar com inteligência maior a energia imanente.</t>
   </si>
   <si>
@@ -806,7 +1033,7 @@
     <t>**Compromissos.** Sendo um caminho sem volta, a tenepes é um compromisso mais forte e rigoroso do que o compromisso do *casamento tradicional,* e mais forte e rigoroso do que o compromisso da *dupla evolutiva.* A tenepes não admite divórcio. Por exemplo: é mais fácil ser campeão de boxe – um esporte radical, violento e condenado do que praticar a tenepes em alto nível.</t>
   </si>
   <si>
-    <t>**Consciencioterapia.** A tenepes põe os *pontos nos **ii**,* vai *até o osso,* e anatomiza a consciência do praticante. A tenepes é uma *enciclopédia de autoconhecimento,* uma *auto* e *hetero*consciencioterapia.</t>
+    <t>**Consciencioterapia.** A tenepes põe os *pontos nos **ii, vai *até o osso,* e anatomiza a consciência do praticante. A tenepes é uma *enciclopédia de autoconhecimento,* uma *auto* e *hetero*consciencioterapia.</t>
   </si>
   <si>
     <t>**Imagística.** A tenepes extrapola a imaginação, ou a imagística, as fabulações, os sonhos e as perspectivas mais transcendentes ansiadas pela consciência humana.</t>
@@ -833,6 +1060,9 @@
     <t>**Questão.** Uma questão pertinente cabe muito bem aqui: por que as práticas da tenepes são possíveis hoje e não foram comuns, ou mais exequíveis, no passado da Humanidade? A Conscienciologia tem uma resposta racional para esta questão, baseada nos fatos intrafísicos e multidimensionais.</t>
   </si>
   <si>
+    <t>32. TEORIA DA FARTURA DA EC</t>
+  </si>
+  <si>
     <t>**Fartura.** Vivemos hoje, na Terra, dentro de uma condição ímpar, ainda não detectada fora da Conscienciologia, ou a comprovação na própria vida da *teoria da fartura de energia consciencial,* proposta por este autor.</t>
   </si>
   <si>
@@ -848,16 +1078,34 @@
     <t>**Matéria.** Além do exposto, o aumento do número das miniconexões dos holochacras nos somas ampliou o volume existente, na vida física da Terra, da *matéria energizada* pelas consciências. Neste ponto, a teoria da fartura de energia consciencial explica uma série de ocorrências.</t>
   </si>
   <si>
-    <t>**Holopensene.** A matéria energizada em volume maior e melhor qualidade, vem aperfeiçoando o *holopensene planetário* da Terra e a vida intrafísica, bem como predispondo, cada vez mais, o surgimento de fenômenos parapsíquicos, cosmoéticos e mais avançados, inclusive estes 10:|1. Superdotações intelectuais as mais diversas de homens e mulheres (precocidades e crianças prodígios).|2. Superdotações das parapercepções (bioenergética, animismo e parapsiquismo) de sensitivos.|3. Incidência de fenômenos de ectoplasmias, sadios, em alto nível, sem exibições espetaculares.|4. Fenômenos terapêuticos e paraclínicos.|5. Intervenções heterodoxas ou paracirurgias.|6. Para-anestesias.|7. Para-assepsias.|8. Para-hemostasias.|9. Paracicatrizações.|10. Emergência e desaparecimento de pequenos e grandes objetos no espaço-tempo-matéria.</t>
-  </si>
-  <si>
-    <t>**Teoria.** Pelas exposições feitas aqui, mesmo de modo sucinto, pode-se concluir, com lógica, que a teoria da fartura de energia consciencial é capaz de preencher e atender perfeitamente aos 7 objetivos ou desideratos básicos exigidos pelo rigor da Ciência como papéis de uma teoria, ou seja:|**1. Metodologia:** sistematiza o conhecimento humano quanto às energias da consciência.|**2. Conceitos:** serve como fonte para a estruturação analítica de conceitos e classificação conceitual (sistema de referência).|**3. Fatos:** explica, generaliza e sintetiza os conhecimentos de problemas e fenômenos (fatos).|**4. Conhecimento:** incrementa o conhecimento do homem e descobre lacunas indicando áreas que ainda não foram exploradas nesse mesmo conhecimento do homem (bioenergética).|**5. Contrastabilidade:** reforça a contrastabilidade ou contribui para a verificação real de valores veritativos factuais.|**6. Pesquisa:** orienta a pesquisa conscienciológica.|**7. Roteiro:** oferece um roteiro de um setor da realidade consciencial e torna-se um meio de fazer previsões de fatos.</t>
+    <t>**Holopensene.** A matéria energizada em volume maior e melhor qualidade, vem aperfeiçoando o *holopensene planetário* da Terra e a vida intrafísica, bem como predispondo, cada vez mais, o surgimento de fenômenos parapsíquicos, cosmoéticos e mais avançados, inclusive estes 10: | 1. Superdotações intelectuais as mais diversas de homens e mulheres (precocidades e crianças prodígios). | 2. Superdotações das parapercepções (bioenergética, animismo e parapsiquismo) de sensitivos. | 3. Incidência de fenômenos de ectoplasmias, sadios, em alto nível, sem exibições espetaculares. | 4. Fenômenos terapêuticos e paraclínicos. | 5. Intervenções heterodoxas ou paracirurgias. | 6. Para-anestesias. | 7. Para-assepsias. | 8. Para-hemostasias. | 9. Paracicatrizações. | 10. Emergência e desaparecimento de pequenos e grandes objetos no espaço-tempo-matéria.</t>
+  </si>
+  <si>
+    <t>**Teoria.** Pelas exposições feitas aqui, mesmo de modo sucinto, pode-se concluir, com lógica, que a teoria da fartura de energia consciencial é capaz de preencher e atender perfeitamente aos 7 objetivos ou desideratos básicos exigidos pelo rigor da Ciência como papéis de uma teoria, ou seja: | **1. Metodologia:** sistematiza o conhecimento humano quanto às energias da consciência. | **2. Conceitos:** serve como fonte para a estruturação analítica de conceitos e classificação conceitual (sistema de referência). | **3. Fatos:** explica, generaliza e sintetiza os conhecimentos de problemas e fenômenos (fatos). | **4. Conhecimento:** incrementa o conhecimento do homem e descobre lacunas indicando áreas que ainda não foram exploradas nesse mesmo conhecimento do homem (bioenergética). | **5. Contrastabilidade:** reforça a contrastabilidade ou contribui para a verificação real de valores veritativos factuais. | **6. Pesquisa:** orienta a pesquisa conscienciológica. | **7. Roteiro:** oferece um roteiro de um setor da realidade consciencial e torna-se um meio de fazer previsões de fatos.</t>
   </si>
   <si>
     <t>**Efeitos.** A esta altura das considerações, cabe uma pergunta óbvia: quais os efeitos sadios da prática da tenepes depois de 1 década?</t>
   </si>
   <si>
-    <t>**Avaliação.** É fácil avaliar o saldo desse esforço por uma conta aritmética. Se colocarmos, por baixo, temos: **50** min em **300** dias (1 ano com 65 dias descontados) ; **15.000** min em **1** ano (300 dias) ; **150.000** min em **10** anos (1 década ou 3.000 dias) ; **2.500** horas em **1** década **104** dias em **1** década ; **3,5** meses em **1** década **1/40** vida em **4** décadas.</t>
+    <t>33. EFEITOS DA TENEPES</t>
+  </si>
+  <si>
+    <t>**Avaliação.** É fácil avaliar o saldo desse esforço por uma conta aritmética. Se colocarmos, por baixo, temos:</t>
+  </si>
+  <si>
+    <t>- **50** min em **300** dias (1 ano com 65 dias descontados)</t>
+  </si>
+  <si>
+    <t>- **15.000** min em **1** ano (300 dias)</t>
+  </si>
+  <si>
+    <t>- **150.000** min em **10** anos (1 década ou 3.000 dias)</t>
+  </si>
+  <si>
+    <t>- **2.500** horas em **1** década **104** dias em **1** década</t>
+  </si>
+  <si>
+    <t>- **3,5** meses em **1** década **1/40** vida em **4** décadas.</t>
   </si>
   <si>
     <t>**Desconto.** O desconto (obviamente exagerado, como hipótese para o arredondamento das cifras) dos 65 dias, diz respeito às doenças eventuais, praticamente inevitáveis, e aos impedimentos naturais – a doença de alguém mais íntimo, por exemplo – à prática dos exercícios da tenepes, durante os 12 meses do ano. Exemplos de impedimentos naturais: a doença de alguém mais íntimo; um problema doméstico; a viagem imprevista, de fato, inadiável; a exigência profissional inesperada; fatos que, racionalmente, não podem ser atribuídos ou interpretados dentro da condição de acidentes de percurso parapsíquicos.</t>
@@ -872,13 +1120,16 @@
     <t>**Extras.** E os períodos extras, diários, do tempo *anterior –* preparação, *aquecimento holossomático,* e *ligamento mental,* somático, à vida *extra*física *–* e *posterior – re*fazimento e *re*entrosamento à vida *intra*física – exigidos pelas práticas diárias da tenepes que não foram incluídos?</t>
   </si>
   <si>
-    <t>**Veterano.** No entanto, é mais do que isso, porque o *praticante, quando veterano,* atende às exteriorizações das energias conscienciais assistenciais a qualquer hora e em qualquer lugar.</t>
+    <t>**Veterano.** No entanto, é mais do que isso, por que o *praticante, quando veterano,* atende às exteriorizações das energias conscienciais assistenciais a qualquer hora e em qualquer lugar.</t>
   </si>
   <si>
     <t>**Líder.** Calcular o número de consciências atendidas durante os exercícios diários da tenepes é impraticável. Basta considerar a hipótese do atendimento de uma só *consciex-enferma-líder* que influa sobre 1.200 consciências carentes, como às vezes acontece, em comunidades extrafísicas doentias. Como saber os resultados dessa assistência? Só depois da dessoma, talvez, com o Orientador Evolutivo.</t>
   </si>
   <si>
-    <t>**Forças.** Eis as 8 forças *mais potentes* de manifestação pensênica da consciência, na vida intrafísica, em ordem decrescente:|**1. Vontade.** *Vontade* pessoal inquebrantável (volição).|**2. Intencionalidade.** Governo da *intencionalidade cosmoética maxifraterna* (intenção).|**3. Auto-organização.** *Auto-organização multidimensional* relativa à intrafisicalidade, bioenergética, mentalsomática e ao parapsiquismo (autodomínio consciencial).|**4. Tenepes.** *Tenepes* praticada através da bioenergética assistencial em alto nível de maturidade.|**5. Ofiex.** *Ofiex* em funcionamento franco, predispondo até a *moréxis* do epicon, se for o caso.|**6. Dupla evolutiva.** Participação atuante numa *dupla evolutiva* íntima.|**7. Megagestações.** *Megagestações conscienciais* executadas individualmente, através da dupla evolutiva íntima ou em equipe.|**8. Proéxis.** *Proéxis* em desenvolvimento seguro no rumo do *. compléxis.*</t>
+    <t>**Forças.** Eis as 8 forças *mais potentes* de manifestação pensênica da consciência, na vida intrafísica, em ordem decrescente: | **1. Vontade.** *Vontade* pessoal inquebrantável (volição). | **2. Intencionalidade.** Governo da *intencionalidade cosmoética maxifraterna* (intenção). | **3. Auto-organização.** *Auto-organização multidimensional* relativa à intrafisicalidade, bioenergética, mentalsomática e ao parapsiquismo (autodomínio consciencial). | **4. Tenepes.** *Tenepes* praticada através da bioenergética assistencial em alto nível de maturidade. | **5. Ofiex.** *Ofiex* em funcionamento franco, predispondo até a *moréxis* do epicon, se for o caso. | **6. Dupla evolutiva.** Participação atuante numa *dupla evolutiva* íntima. | **7. Megagestações.** *Megagestações conscienciais* executadas individualmente, através da dupla evolutiva íntima ou em equipe. | **8. Proéxis.** *Proéxis* em desenvolvimento seguro no rumo do *. compléxis.*</t>
+  </si>
+  <si>
+    <t>34. FORÇAS PRIORITÁRIAS</t>
   </si>
   <si>
     <t>**Poderes.** Estas 8 forças são os verdadeiros e mais relevantes poderes de que a conscin dispõe.</t>
@@ -902,125 +1153,14 @@
     <t>**Pessoal.** Estou, pessoalmente, sempre às ordens para assistir especificamente a cada candidato ou candidata às práticas da tenepes, dentro de minhas possibilidades intrafísicas limitadas e na condição confessa, explícita, de *mercador de minha própria ignorância alfabetizada* quanto aos temas da consciência, prioritários e mais importantes do que todos os outros, dentro de nosso atual estágio evolutivo.</t>
   </si>
   <si>
-    <t>Introdução</t>
-  </si>
-  <si>
-    <t>1. Definições</t>
-  </si>
-  <si>
-    <t>3. Conscins</t>
-  </si>
-  <si>
-    <t>4. Paradoxos</t>
-  </si>
-  <si>
-    <t>5. Comparações</t>
-  </si>
-  <si>
-    <t>8. Contatos Diários</t>
-  </si>
-  <si>
-    <t>9. Vivência</t>
-  </si>
-  <si>
-    <t>11. Conexões Sexuais</t>
-  </si>
-  <si>
-    <t>12. Operações Assistenciais</t>
-  </si>
-  <si>
-    <t>13. Amparadores</t>
-  </si>
-  <si>
-    <t>14. Mentalsomática</t>
-  </si>
-  <si>
-    <t>15. Holochacralidade</t>
-  </si>
-  <si>
-    <t>16. Objetos</t>
-  </si>
-  <si>
-    <t>17. Grupalidade</t>
-  </si>
-  <si>
-    <t>22. Sintonia</t>
-  </si>
-  <si>
-    <t>24. Estágio Avançado</t>
-  </si>
-  <si>
-    <t>26. Sutilezas</t>
-  </si>
-  <si>
-    <t>27. Hábitos Diários</t>
-  </si>
-  <si>
-    <t>28. Nudez</t>
-  </si>
-  <si>
-    <t>29. Assins</t>
-  </si>
-  <si>
-    <t>31. Saldo Consciencial</t>
-  </si>
-  <si>
-    <t>34. Forças Prioritárias</t>
-  </si>
-  <si>
-    <t>2. Histórico da Tenepes</t>
-  </si>
-  <si>
-    <t>6. Técnica da Tenepes</t>
-  </si>
-  <si>
-    <t>7. Antecipação da Tenepes</t>
-  </si>
-  <si>
-    <t>18. Contraindicações da Tenepes</t>
-  </si>
-  <si>
-    <t>19. Teste da Tenepes</t>
-  </si>
-  <si>
-    <t>20. Indicações da Tenepes</t>
-  </si>
-  <si>
-    <t>21. Utilidades da Tenepes</t>
-  </si>
-  <si>
-    <t>25. Vantagens da Tenepes</t>
-  </si>
-  <si>
-    <t>30. Evolução da Consciência</t>
-  </si>
-  <si>
-    <t>33. Efeitos da Tenepes</t>
-  </si>
-  <si>
-    <t>10. Sensações na Tenepes</t>
-  </si>
-  <si>
-    <t>23. Estágios na Tenepes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32. Teoria da Fartura da EC </t>
-  </si>
-  <si>
     <t>number</t>
-  </si>
-  <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>title</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1029,34 +1169,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1086,18 +1215,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1400,31 +1525,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C290"/>
+  <dimension ref="A1:C341"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="88.33203125" customWidth="1"/>
-    <col min="2" max="2" width="49.5546875" customWidth="1"/>
-    <col min="3" max="3" width="25.44140625" customWidth="1"/>
+    <col min="1" max="1" width="77.77734375" customWidth="1"/>
+    <col min="2" max="2" width="29.109375" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>324</v>
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>289</v>
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -1432,10 +1557,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>289</v>
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -1443,10 +1568,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>289</v>
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
@@ -1454,10 +1579,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
         <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -1465,10 +1590,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>289</v>
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
       </c>
       <c r="C6" s="1">
         <v>5</v>
@@ -1476,10 +1601,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>289</v>
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
       </c>
       <c r="C7" s="1">
         <v>6</v>
@@ -1487,10 +1612,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>289</v>
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
       </c>
       <c r="C8" s="1">
         <v>7</v>
@@ -1498,10 +1623,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>289</v>
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
       </c>
       <c r="C9" s="1">
         <v>8</v>
@@ -1509,10 +1634,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>289</v>
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
       </c>
       <c r="C10" s="1">
         <v>9</v>
@@ -1520,10 +1645,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>289</v>
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
       </c>
       <c r="C11" s="1">
         <v>10</v>
@@ -1531,10 +1656,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>289</v>
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
       </c>
       <c r="C12" s="1">
         <v>11</v>
@@ -1542,10 +1667,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>289</v>
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
       </c>
       <c r="C13" s="1">
         <v>12</v>
@@ -1553,10 +1678,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>289</v>
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
       </c>
       <c r="C14" s="1">
         <v>13</v>
@@ -1564,10 +1689,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>289</v>
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
       </c>
       <c r="C15" s="1">
         <v>14</v>
@@ -1575,10 +1700,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>290</v>
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
       </c>
       <c r="C16" s="1">
         <v>15</v>
@@ -1586,10 +1711,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>290</v>
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
       </c>
       <c r="C17" s="1">
         <v>16</v>
@@ -1597,10 +1722,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>290</v>
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
       </c>
       <c r="C18" s="1">
         <v>17</v>
@@ -1608,10 +1733,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>290</v>
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
       </c>
       <c r="C19" s="1">
         <v>18</v>
@@ -1619,10 +1744,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
         <v>18</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="C20" s="1">
         <v>19</v>
@@ -1630,10 +1755,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>290</v>
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
       </c>
       <c r="C21" s="1">
         <v>20</v>
@@ -1641,10 +1766,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>290</v>
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
       </c>
       <c r="C22" s="1">
         <v>21</v>
@@ -1652,10 +1777,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>311</v>
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
       </c>
       <c r="C23" s="1">
         <v>22</v>
@@ -1663,10 +1788,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>311</v>
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
       </c>
       <c r="C24" s="1">
         <v>23</v>
@@ -1674,10 +1799,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>311</v>
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
       </c>
       <c r="C25" s="1">
         <v>24</v>
@@ -1685,10 +1810,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>311</v>
+        <v>29</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
       </c>
       <c r="C26" s="1">
         <v>25</v>
@@ -1696,10 +1821,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>311</v>
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
       </c>
       <c r="C27" s="1">
         <v>26</v>
@@ -1707,10 +1832,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" t="s">
         <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>311</v>
       </c>
       <c r="C28" s="1">
         <v>27</v>
@@ -1718,10 +1843,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>311</v>
+        <v>32</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1729,10 +1854,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>311</v>
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
       </c>
       <c r="C30" s="1">
         <v>29</v>
@@ -1740,10 +1865,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>311</v>
+        <v>34</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
       </c>
       <c r="C31" s="1">
         <v>30</v>
@@ -1751,10 +1876,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>311</v>
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
       </c>
       <c r="C32" s="1">
         <v>31</v>
@@ -1762,10 +1887,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>311</v>
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
       </c>
       <c r="C33" s="1">
         <v>32</v>
@@ -1773,10 +1898,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>311</v>
+        <v>37</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
       </c>
       <c r="C34" s="1">
         <v>33</v>
@@ -1784,10 +1909,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>311</v>
+        <v>38</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
       </c>
       <c r="C35" s="1">
         <v>34</v>
@@ -1795,10 +1920,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>291</v>
+        <v>39</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
       </c>
       <c r="C36" s="1">
         <v>35</v>
@@ -1806,10 +1931,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>291</v>
+        <v>41</v>
+      </c>
+      <c r="B37" t="s">
+        <v>40</v>
       </c>
       <c r="C37" s="1">
         <v>36</v>
@@ -1817,10 +1942,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>292</v>
+        <v>42</v>
+      </c>
+      <c r="B38" t="s">
+        <v>40</v>
       </c>
       <c r="C38" s="1">
         <v>37</v>
@@ -1828,10 +1953,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>292</v>
+        <v>43</v>
+      </c>
+      <c r="B39" t="s">
+        <v>40</v>
       </c>
       <c r="C39" s="1">
         <v>38</v>
@@ -1839,10 +1964,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>293</v>
+        <v>44</v>
+      </c>
+      <c r="B40" t="s">
+        <v>45</v>
       </c>
       <c r="C40" s="1">
         <v>39</v>
@@ -1850,10 +1975,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>293</v>
+        <v>46</v>
+      </c>
+      <c r="B41" t="s">
+        <v>45</v>
       </c>
       <c r="C41" s="1">
         <v>40</v>
@@ -1861,10 +1986,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>293</v>
+        <v>47</v>
+      </c>
+      <c r="B42" t="s">
+        <v>48</v>
       </c>
       <c r="C42" s="1">
         <v>41</v>
@@ -1872,10 +1997,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>293</v>
+        <v>49</v>
+      </c>
+      <c r="B43" t="s">
+        <v>48</v>
       </c>
       <c r="C43" s="1">
         <v>42</v>
@@ -1883,10 +2008,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>293</v>
+        <v>50</v>
+      </c>
+      <c r="B44" t="s">
+        <v>48</v>
       </c>
       <c r="C44" s="1">
         <v>43</v>
@@ -1894,10 +2019,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>293</v>
+        <v>51</v>
+      </c>
+      <c r="B45" t="s">
+        <v>48</v>
       </c>
       <c r="C45" s="1">
         <v>44</v>
@@ -1905,10 +2030,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>293</v>
+        <v>52</v>
+      </c>
+      <c r="B46" t="s">
+        <v>48</v>
       </c>
       <c r="C46" s="1">
         <v>45</v>
@@ -1916,10 +2041,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>293</v>
+        <v>53</v>
+      </c>
+      <c r="B47" t="s">
+        <v>48</v>
       </c>
       <c r="C47" s="1">
         <v>46</v>
@@ -1927,10 +2052,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>293</v>
+        <v>54</v>
+      </c>
+      <c r="B48" t="s">
+        <v>48</v>
       </c>
       <c r="C48" s="1">
         <v>47</v>
@@ -1938,10 +2063,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>293</v>
+        <v>55</v>
+      </c>
+      <c r="B49" t="s">
+        <v>48</v>
       </c>
       <c r="C49" s="1">
         <v>48</v>
@@ -1949,10 +2074,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" t="s">
         <v>48</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>293</v>
       </c>
       <c r="C50" s="1">
         <v>49</v>
@@ -1960,10 +2085,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>49</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>293</v>
+        <v>57</v>
+      </c>
+      <c r="B51" t="s">
+        <v>48</v>
       </c>
       <c r="C51" s="1">
         <v>50</v>
@@ -1971,10 +2096,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>50</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>293</v>
+        <v>58</v>
+      </c>
+      <c r="B52" t="s">
+        <v>48</v>
       </c>
       <c r="C52" s="1">
         <v>51</v>
@@ -1982,10 +2107,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>51</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>293</v>
+        <v>59</v>
+      </c>
+      <c r="B53" t="s">
+        <v>48</v>
       </c>
       <c r="C53" s="1">
         <v>52</v>
@@ -1993,10 +2118,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>52</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>293</v>
+        <v>60</v>
+      </c>
+      <c r="B54" t="s">
+        <v>48</v>
       </c>
       <c r="C54" s="1">
         <v>53</v>
@@ -2004,10 +2129,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>53</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>293</v>
+        <v>61</v>
+      </c>
+      <c r="B55" t="s">
+        <v>48</v>
       </c>
       <c r="C55" s="1">
         <v>54</v>
@@ -2015,10 +2140,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>54</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>293</v>
+        <v>62</v>
+      </c>
+      <c r="B56" t="s">
+        <v>48</v>
       </c>
       <c r="C56" s="1">
         <v>55</v>
@@ -2026,10 +2151,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>55</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>293</v>
+        <v>63</v>
+      </c>
+      <c r="B57" t="s">
+        <v>48</v>
       </c>
       <c r="C57" s="1">
         <v>56</v>
@@ -2037,10 +2162,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>56</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>293</v>
+        <v>64</v>
+      </c>
+      <c r="B58" t="s">
+        <v>48</v>
       </c>
       <c r="C58" s="1">
         <v>57</v>
@@ -2048,10 +2173,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>57</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>312</v>
+        <v>65</v>
+      </c>
+      <c r="B59" t="s">
+        <v>48</v>
       </c>
       <c r="C59" s="1">
         <v>58</v>
@@ -2059,10 +2184,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>58</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>312</v>
+        <v>66</v>
+      </c>
+      <c r="B60" t="s">
+        <v>48</v>
       </c>
       <c r="C60" s="1">
         <v>59</v>
@@ -2070,10 +2195,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>59</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>312</v>
+        <v>67</v>
+      </c>
+      <c r="B61" t="s">
+        <v>68</v>
       </c>
       <c r="C61" s="1">
         <v>60</v>
@@ -2081,10 +2206,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>60</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>312</v>
+        <v>69</v>
+      </c>
+      <c r="B62" t="s">
+        <v>68</v>
       </c>
       <c r="C62" s="1">
         <v>61</v>
@@ -2092,10 +2217,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>61</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>312</v>
+        <v>70</v>
+      </c>
+      <c r="B63" t="s">
+        <v>68</v>
       </c>
       <c r="C63" s="1">
         <v>62</v>
@@ -2103,10 +2228,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>62</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>312</v>
+        <v>71</v>
+      </c>
+      <c r="B64" t="s">
+        <v>68</v>
       </c>
       <c r="C64" s="1">
         <v>63</v>
@@ -2114,10 +2239,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>63</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>312</v>
+        <v>72</v>
+      </c>
+      <c r="B65" t="s">
+        <v>68</v>
       </c>
       <c r="C65" s="1">
         <v>64</v>
@@ -2125,10 +2250,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>64</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>312</v>
+        <v>73</v>
+      </c>
+      <c r="B66" t="s">
+        <v>68</v>
       </c>
       <c r="C66" s="1">
         <v>65</v>
@@ -2136,10 +2261,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>312</v>
+        <v>74</v>
+      </c>
+      <c r="B67" t="s">
+        <v>68</v>
       </c>
       <c r="C67" s="1">
         <v>66</v>
@@ -2147,10 +2272,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>66</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>312</v>
+        <v>75</v>
+      </c>
+      <c r="B68" t="s">
+        <v>68</v>
       </c>
       <c r="C68" s="1">
         <v>67</v>
@@ -2158,10 +2283,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>67</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>312</v>
+        <v>76</v>
+      </c>
+      <c r="B69" t="s">
+        <v>68</v>
       </c>
       <c r="C69" s="1">
         <v>68</v>
@@ -2169,10 +2294,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" t="s">
         <v>68</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="C70" s="1">
         <v>69</v>
@@ -2180,10 +2305,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>69</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>312</v>
+        <v>78</v>
+      </c>
+      <c r="B71" t="s">
+        <v>68</v>
       </c>
       <c r="C71" s="1">
         <v>70</v>
@@ -2191,10 +2316,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>70</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>312</v>
+        <v>79</v>
+      </c>
+      <c r="B72" t="s">
+        <v>68</v>
       </c>
       <c r="C72" s="1">
         <v>71</v>
@@ -2202,10 +2327,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>71</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>312</v>
+        <v>80</v>
+      </c>
+      <c r="B73" t="s">
+        <v>68</v>
       </c>
       <c r="C73" s="1">
         <v>72</v>
@@ -2213,10 +2338,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>72</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>312</v>
+        <v>81</v>
+      </c>
+      <c r="B74" t="s">
+        <v>68</v>
       </c>
       <c r="C74" s="1">
         <v>73</v>
@@ -2224,10 +2349,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>73</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>312</v>
+        <v>82</v>
+      </c>
+      <c r="B75" t="s">
+        <v>68</v>
       </c>
       <c r="C75" s="1">
         <v>74</v>
@@ -2235,10 +2360,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>74</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>312</v>
+        <v>83</v>
+      </c>
+      <c r="B76" t="s">
+        <v>68</v>
       </c>
       <c r="C76" s="1">
         <v>75</v>
@@ -2246,10 +2371,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>75</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>312</v>
+        <v>84</v>
+      </c>
+      <c r="B77" t="s">
+        <v>68</v>
       </c>
       <c r="C77" s="1">
         <v>76</v>
@@ -2257,10 +2382,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>76</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>312</v>
+        <v>85</v>
+      </c>
+      <c r="B78" t="s">
+        <v>68</v>
       </c>
       <c r="C78" s="1">
         <v>77</v>
@@ -2268,10 +2393,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>77</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>312</v>
+        <v>86</v>
+      </c>
+      <c r="B79" t="s">
+        <v>68</v>
       </c>
       <c r="C79" s="1">
         <v>78</v>
@@ -2279,10 +2404,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>78</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>312</v>
+        <v>87</v>
+      </c>
+      <c r="B80" t="s">
+        <v>68</v>
       </c>
       <c r="C80" s="1">
         <v>79</v>
@@ -2290,10 +2415,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>79</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>312</v>
+        <v>88</v>
+      </c>
+      <c r="B81" t="s">
+        <v>68</v>
       </c>
       <c r="C81" s="1">
         <v>80</v>
@@ -2301,10 +2426,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>80</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>312</v>
+        <v>89</v>
+      </c>
+      <c r="B82" t="s">
+        <v>68</v>
       </c>
       <c r="C82" s="1">
         <v>81</v>
@@ -2312,10 +2437,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>81</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>312</v>
+        <v>90</v>
+      </c>
+      <c r="B83" t="s">
+        <v>68</v>
       </c>
       <c r="C83" s="1">
         <v>82</v>
@@ -2323,10 +2448,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>82</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>312</v>
+        <v>91</v>
+      </c>
+      <c r="B84" t="s">
+        <v>68</v>
       </c>
       <c r="C84" s="1">
         <v>83</v>
@@ -2334,10 +2459,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>83</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>312</v>
+        <v>92</v>
+      </c>
+      <c r="B85" t="s">
+        <v>68</v>
       </c>
       <c r="C85" s="1">
         <v>84</v>
@@ -2345,10 +2470,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>84</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>312</v>
+        <v>93</v>
+      </c>
+      <c r="B86" t="s">
+        <v>68</v>
       </c>
       <c r="C86" s="1">
         <v>85</v>
@@ -2356,10 +2481,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>85</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>312</v>
+        <v>94</v>
+      </c>
+      <c r="B87" t="s">
+        <v>68</v>
       </c>
       <c r="C87" s="1">
         <v>86</v>
@@ -2367,10 +2492,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>86</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>312</v>
+        <v>95</v>
+      </c>
+      <c r="B88" t="s">
+        <v>68</v>
       </c>
       <c r="C88" s="1">
         <v>87</v>
@@ -2378,10 +2503,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>87</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>312</v>
+        <v>96</v>
+      </c>
+      <c r="B89" t="s">
+        <v>68</v>
       </c>
       <c r="C89" s="1">
         <v>88</v>
@@ -2389,10 +2514,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>88</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>312</v>
+        <v>97</v>
+      </c>
+      <c r="B90" t="s">
+        <v>68</v>
       </c>
       <c r="C90" s="1">
         <v>89</v>
@@ -2400,10 +2525,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>89</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>312</v>
+        <v>98</v>
+      </c>
+      <c r="B91" t="s">
+        <v>68</v>
       </c>
       <c r="C91" s="1">
         <v>90</v>
@@ -2411,10 +2536,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>90</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>313</v>
+        <v>99</v>
+      </c>
+      <c r="B92" t="s">
+        <v>68</v>
       </c>
       <c r="C92" s="1">
         <v>91</v>
@@ -2422,10 +2547,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>91</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>294</v>
+        <v>100</v>
+      </c>
+      <c r="B93" t="s">
+        <v>68</v>
       </c>
       <c r="C93" s="1">
         <v>92</v>
@@ -2433,10 +2558,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>92</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>294</v>
+        <v>101</v>
+      </c>
+      <c r="B94" t="s">
+        <v>102</v>
       </c>
       <c r="C94" s="1">
         <v>93</v>
@@ -2444,10 +2569,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>93</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>294</v>
+        <v>103</v>
+      </c>
+      <c r="B95" t="s">
+        <v>104</v>
       </c>
       <c r="C95" s="1">
         <v>94</v>
@@ -2455,10 +2580,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>94</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>294</v>
+        <v>105</v>
+      </c>
+      <c r="B96" t="s">
+        <v>104</v>
       </c>
       <c r="C96" s="1">
         <v>95</v>
@@ -2466,10 +2591,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>95</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>295</v>
+        <v>106</v>
+      </c>
+      <c r="B97" t="s">
+        <v>104</v>
       </c>
       <c r="C97" s="1">
         <v>96</v>
@@ -2477,10 +2602,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>96</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>295</v>
+        <v>107</v>
+      </c>
+      <c r="B98" t="s">
+        <v>104</v>
       </c>
       <c r="C98" s="1">
         <v>97</v>
@@ -2488,10 +2613,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>97</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>321</v>
+        <v>108</v>
+      </c>
+      <c r="B99" t="s">
+        <v>109</v>
       </c>
       <c r="C99" s="1">
         <v>98</v>
@@ -2499,10 +2624,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>98</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>321</v>
+        <v>110</v>
+      </c>
+      <c r="B100" t="s">
+        <v>109</v>
       </c>
       <c r="C100" s="1">
         <v>99</v>
@@ -2510,10 +2635,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>99</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>321</v>
+        <v>111</v>
+      </c>
+      <c r="B101" t="s">
+        <v>112</v>
       </c>
       <c r="C101" s="1">
         <v>100</v>
@@ -2521,10 +2646,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>100</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>321</v>
+        <v>113</v>
+      </c>
+      <c r="B102" t="s">
+        <v>112</v>
       </c>
       <c r="C102" s="1">
         <v>101</v>
@@ -2532,10 +2657,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>101</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>321</v>
+        <v>114</v>
+      </c>
+      <c r="B103" t="s">
+        <v>112</v>
       </c>
       <c r="C103" s="1">
         <v>102</v>
@@ -2543,10 +2668,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>102</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>296</v>
+        <v>115</v>
+      </c>
+      <c r="B104" t="s">
+        <v>112</v>
       </c>
       <c r="C104" s="1">
         <v>103</v>
@@ -2554,10 +2679,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>103</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>296</v>
+        <v>116</v>
+      </c>
+      <c r="B105" t="s">
+        <v>112</v>
       </c>
       <c r="C105" s="1">
         <v>104</v>
@@ -2565,10 +2690,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>104</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>296</v>
+        <v>117</v>
+      </c>
+      <c r="B106" t="s">
+        <v>112</v>
       </c>
       <c r="C106" s="1">
         <v>105</v>
@@ -2576,10 +2701,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>105</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>296</v>
+        <v>118</v>
+      </c>
+      <c r="B107" t="s">
+        <v>112</v>
       </c>
       <c r="C107" s="1">
         <v>106</v>
@@ -2587,10 +2712,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>106</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>296</v>
+        <v>119</v>
+      </c>
+      <c r="B108" t="s">
+        <v>112</v>
       </c>
       <c r="C108" s="1">
         <v>107</v>
@@ -2598,10 +2723,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>107</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>296</v>
+        <v>120</v>
+      </c>
+      <c r="B109" t="s">
+        <v>112</v>
       </c>
       <c r="C109" s="1">
         <v>108</v>
@@ -2609,10 +2734,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>108</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>296</v>
+        <v>121</v>
+      </c>
+      <c r="B110" t="s">
+        <v>112</v>
       </c>
       <c r="C110" s="1">
         <v>109</v>
@@ -2620,10 +2745,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>109</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>296</v>
+        <v>122</v>
+      </c>
+      <c r="B111" t="s">
+        <v>112</v>
       </c>
       <c r="C111" s="1">
         <v>110</v>
@@ -2631,10 +2756,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>110</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>296</v>
+        <v>123</v>
+      </c>
+      <c r="B112" t="s">
+        <v>112</v>
       </c>
       <c r="C112" s="1">
         <v>111</v>
@@ -2642,10 +2767,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>111</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>296</v>
+        <v>124</v>
+      </c>
+      <c r="B113" t="s">
+        <v>112</v>
       </c>
       <c r="C113" s="1">
         <v>112</v>
@@ -2653,10 +2778,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
+        <v>125</v>
+      </c>
+      <c r="B114" t="s">
         <v>112</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>296</v>
       </c>
       <c r="C114" s="1">
         <v>113</v>
@@ -2664,10 +2789,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>113</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>296</v>
+        <v>126</v>
+      </c>
+      <c r="B115" t="s">
+        <v>112</v>
       </c>
       <c r="C115" s="1">
         <v>114</v>
@@ -2675,10 +2800,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>114</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>296</v>
+        <v>127</v>
+      </c>
+      <c r="B116" t="s">
+        <v>112</v>
       </c>
       <c r="C116" s="1">
         <v>115</v>
@@ -2686,10 +2811,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>115</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>296</v>
+        <v>128</v>
+      </c>
+      <c r="B117" t="s">
+        <v>112</v>
       </c>
       <c r="C117" s="1">
         <v>116</v>
@@ -2697,10 +2822,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>116</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>296</v>
+        <v>129</v>
+      </c>
+      <c r="B118" t="s">
+        <v>112</v>
       </c>
       <c r="C118" s="1">
         <v>117</v>
@@ -2708,10 +2833,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>117</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>296</v>
+        <v>130</v>
+      </c>
+      <c r="B119" t="s">
+        <v>112</v>
       </c>
       <c r="C119" s="1">
         <v>118</v>
@@ -2719,10 +2844,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>118</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>297</v>
+        <v>131</v>
+      </c>
+      <c r="B120" t="s">
+        <v>112</v>
       </c>
       <c r="C120" s="1">
         <v>119</v>
@@ -2730,10 +2855,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>119</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>297</v>
+        <v>132</v>
+      </c>
+      <c r="B121" t="s">
+        <v>112</v>
       </c>
       <c r="C121" s="1">
         <v>120</v>
@@ -2741,10 +2866,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>120</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>297</v>
+        <v>133</v>
+      </c>
+      <c r="B122" t="s">
+        <v>112</v>
       </c>
       <c r="C122" s="1">
         <v>121</v>
@@ -2752,10 +2877,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>121</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>297</v>
+        <v>134</v>
+      </c>
+      <c r="B123" t="s">
+        <v>112</v>
       </c>
       <c r="C123" s="1">
         <v>122</v>
@@ -2763,10 +2888,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>122</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>297</v>
+        <v>135</v>
+      </c>
+      <c r="B124" t="s">
+        <v>112</v>
       </c>
       <c r="C124" s="1">
         <v>123</v>
@@ -2774,10 +2899,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>123</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>297</v>
+        <v>136</v>
+      </c>
+      <c r="B125" t="s">
+        <v>112</v>
       </c>
       <c r="C125" s="1">
         <v>124</v>
@@ -2785,10 +2910,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>124</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>297</v>
+        <v>137</v>
+      </c>
+      <c r="B126" t="s">
+        <v>112</v>
       </c>
       <c r="C126" s="1">
         <v>125</v>
@@ -2796,10 +2921,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>125</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>297</v>
+        <v>138</v>
+      </c>
+      <c r="B127" t="s">
+        <v>112</v>
       </c>
       <c r="C127" s="1">
         <v>126</v>
@@ -2807,10 +2932,10 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>126</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>297</v>
+        <v>139</v>
+      </c>
+      <c r="B128" t="s">
+        <v>112</v>
       </c>
       <c r="C128" s="1">
         <v>127</v>
@@ -2818,10 +2943,10 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>127</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>297</v>
+        <v>140</v>
+      </c>
+      <c r="B129" t="s">
+        <v>112</v>
       </c>
       <c r="C129" s="1">
         <v>128</v>
@@ -2829,10 +2954,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>128</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>297</v>
+        <v>141</v>
+      </c>
+      <c r="B130" t="s">
+        <v>112</v>
       </c>
       <c r="C130" s="1">
         <v>129</v>
@@ -2840,10 +2965,10 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>129</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>297</v>
+        <v>142</v>
+      </c>
+      <c r="B131" t="s">
+        <v>112</v>
       </c>
       <c r="C131" s="1">
         <v>130</v>
@@ -2851,10 +2976,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>130</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>297</v>
+        <v>143</v>
+      </c>
+      <c r="B132" t="s">
+        <v>112</v>
       </c>
       <c r="C132" s="1">
         <v>131</v>
@@ -2862,10 +2987,10 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>131</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>297</v>
+        <v>144</v>
+      </c>
+      <c r="B133" t="s">
+        <v>112</v>
       </c>
       <c r="C133" s="1">
         <v>132</v>
@@ -2873,10 +2998,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>132</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>297</v>
+        <v>145</v>
+      </c>
+      <c r="B134" t="s">
+        <v>112</v>
       </c>
       <c r="C134" s="1">
         <v>133</v>
@@ -2884,10 +3009,10 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>133</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>298</v>
+        <v>146</v>
+      </c>
+      <c r="B135" t="s">
+        <v>112</v>
       </c>
       <c r="C135" s="1">
         <v>134</v>
@@ -2895,10 +3020,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>134</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>298</v>
+        <v>147</v>
+      </c>
+      <c r="B136" t="s">
+        <v>112</v>
       </c>
       <c r="C136" s="1">
         <v>135</v>
@@ -2906,10 +3031,10 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>135</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>298</v>
+        <v>148</v>
+      </c>
+      <c r="B137" t="s">
+        <v>112</v>
       </c>
       <c r="C137" s="1">
         <v>136</v>
@@ -2917,10 +3042,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>136</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>298</v>
+        <v>149</v>
+      </c>
+      <c r="B138" t="s">
+        <v>112</v>
       </c>
       <c r="C138" s="1">
         <v>137</v>
@@ -2928,10 +3053,10 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>137</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>298</v>
+        <v>150</v>
+      </c>
+      <c r="B139" t="s">
+        <v>112</v>
       </c>
       <c r="C139" s="1">
         <v>138</v>
@@ -2939,10 +3064,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>138</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>298</v>
+        <v>151</v>
+      </c>
+      <c r="B140" t="s">
+        <v>112</v>
       </c>
       <c r="C140" s="1">
         <v>139</v>
@@ -2950,10 +3075,10 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>139</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>298</v>
+        <v>152</v>
+      </c>
+      <c r="B141" t="s">
+        <v>112</v>
       </c>
       <c r="C141" s="1">
         <v>140</v>
@@ -2961,10 +3086,10 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>140</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>298</v>
+        <v>153</v>
+      </c>
+      <c r="B142" t="s">
+        <v>112</v>
       </c>
       <c r="C142" s="1">
         <v>141</v>
@@ -2972,10 +3097,10 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>141</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>298</v>
+        <v>154</v>
+      </c>
+      <c r="B143" t="s">
+        <v>112</v>
       </c>
       <c r="C143" s="1">
         <v>142</v>
@@ -2983,10 +3108,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>142</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>298</v>
+        <v>155</v>
+      </c>
+      <c r="B144" t="s">
+        <v>112</v>
       </c>
       <c r="C144" s="1">
         <v>143</v>
@@ -2994,10 +3119,10 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>143</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>299</v>
+        <v>156</v>
+      </c>
+      <c r="B145" t="s">
+        <v>112</v>
       </c>
       <c r="C145" s="1">
         <v>144</v>
@@ -3005,10 +3130,10 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>144</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>300</v>
+        <v>157</v>
+      </c>
+      <c r="B146" t="s">
+        <v>112</v>
       </c>
       <c r="C146" s="1">
         <v>145</v>
@@ -3016,10 +3141,10 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>145</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>300</v>
+        <v>158</v>
+      </c>
+      <c r="B147" t="s">
+        <v>112</v>
       </c>
       <c r="C147" s="1">
         <v>146</v>
@@ -3027,10 +3152,10 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>146</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>300</v>
+        <v>159</v>
+      </c>
+      <c r="B148" t="s">
+        <v>112</v>
       </c>
       <c r="C148" s="1">
         <v>147</v>
@@ -3038,10 +3163,10 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>147</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>300</v>
+        <v>160</v>
+      </c>
+      <c r="B149" t="s">
+        <v>161</v>
       </c>
       <c r="C149" s="1">
         <v>148</v>
@@ -3049,10 +3174,10 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>148</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>300</v>
+        <v>162</v>
+      </c>
+      <c r="B150" t="s">
+        <v>161</v>
       </c>
       <c r="C150" s="1">
         <v>149</v>
@@ -3060,10 +3185,10 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>149</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>300</v>
+        <v>163</v>
+      </c>
+      <c r="B151" t="s">
+        <v>161</v>
       </c>
       <c r="C151" s="1">
         <v>150</v>
@@ -3071,10 +3196,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>150</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>300</v>
+        <v>164</v>
+      </c>
+      <c r="B152" t="s">
+        <v>161</v>
       </c>
       <c r="C152" s="1">
         <v>151</v>
@@ -3082,10 +3207,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>151</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>300</v>
+        <v>165</v>
+      </c>
+      <c r="B153" t="s">
+        <v>161</v>
       </c>
       <c r="C153" s="1">
         <v>152</v>
@@ -3093,10 +3218,10 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>152</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>300</v>
+        <v>166</v>
+      </c>
+      <c r="B154" t="s">
+        <v>161</v>
       </c>
       <c r="C154" s="1">
         <v>153</v>
@@ -3104,10 +3229,10 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>153</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>300</v>
+        <v>167</v>
+      </c>
+      <c r="B155" t="s">
+        <v>161</v>
       </c>
       <c r="C155" s="1">
         <v>154</v>
@@ -3115,10 +3240,10 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>154</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>300</v>
+        <v>168</v>
+      </c>
+      <c r="B156" t="s">
+        <v>161</v>
       </c>
       <c r="C156" s="1">
         <v>155</v>
@@ -3126,10 +3251,10 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>155</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>300</v>
+        <v>169</v>
+      </c>
+      <c r="B157" t="s">
+        <v>161</v>
       </c>
       <c r="C157" s="1">
         <v>156</v>
@@ -3137,10 +3262,10 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>156</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>301</v>
+        <v>170</v>
+      </c>
+      <c r="B158" t="s">
+        <v>161</v>
       </c>
       <c r="C158" s="1">
         <v>157</v>
@@ -3148,10 +3273,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>157</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>301</v>
+        <v>171</v>
+      </c>
+      <c r="B159" t="s">
+        <v>161</v>
       </c>
       <c r="C159" s="1">
         <v>158</v>
@@ -3159,10 +3284,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>158</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>301</v>
+        <v>172</v>
+      </c>
+      <c r="B160" t="s">
+        <v>161</v>
       </c>
       <c r="C160" s="1">
         <v>159</v>
@@ -3170,10 +3295,10 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>159</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>301</v>
+        <v>173</v>
+      </c>
+      <c r="B161" t="s">
+        <v>161</v>
       </c>
       <c r="C161" s="1">
         <v>160</v>
@@ -3181,10 +3306,10 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>160</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>301</v>
+        <v>174</v>
+      </c>
+      <c r="B162" t="s">
+        <v>161</v>
       </c>
       <c r="C162" s="1">
         <v>161</v>
@@ -3192,10 +3317,10 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
+        <v>175</v>
+      </c>
+      <c r="B163" t="s">
         <v>161</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="C163" s="1">
         <v>162</v>
@@ -3203,10 +3328,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>162</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>301</v>
+        <v>176</v>
+      </c>
+      <c r="B164" t="s">
+        <v>161</v>
       </c>
       <c r="C164" s="1">
         <v>163</v>
@@ -3214,10 +3339,10 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>163</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>301</v>
+        <v>177</v>
+      </c>
+      <c r="B165" t="s">
+        <v>161</v>
       </c>
       <c r="C165" s="1">
         <v>164</v>
@@ -3225,10 +3350,10 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>164</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>301</v>
+        <v>178</v>
+      </c>
+      <c r="B166" t="s">
+        <v>179</v>
       </c>
       <c r="C166" s="1">
         <v>165</v>
@@ -3236,10 +3361,10 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>165</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>301</v>
+        <v>180</v>
+      </c>
+      <c r="B167" t="s">
+        <v>179</v>
       </c>
       <c r="C167" s="1">
         <v>166</v>
@@ -3247,10 +3372,10 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>166</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>301</v>
+        <v>181</v>
+      </c>
+      <c r="B168" t="s">
+        <v>179</v>
       </c>
       <c r="C168" s="1">
         <v>167</v>
@@ -3258,10 +3383,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>167</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>301</v>
+        <v>182</v>
+      </c>
+      <c r="B169" t="s">
+        <v>179</v>
       </c>
       <c r="C169" s="1">
         <v>168</v>
@@ -3269,10 +3394,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>168</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>301</v>
+        <v>183</v>
+      </c>
+      <c r="B170" t="s">
+        <v>179</v>
       </c>
       <c r="C170" s="1">
         <v>169</v>
@@ -3280,10 +3405,10 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>169</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>301</v>
+        <v>184</v>
+      </c>
+      <c r="B171" t="s">
+        <v>179</v>
       </c>
       <c r="C171" s="1">
         <v>170</v>
@@ -3291,10 +3416,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>170</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>301</v>
+        <v>185</v>
+      </c>
+      <c r="B172" t="s">
+        <v>179</v>
       </c>
       <c r="C172" s="1">
         <v>171</v>
@@ -3302,10 +3427,10 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>171</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>301</v>
+        <v>186</v>
+      </c>
+      <c r="B173" t="s">
+        <v>179</v>
       </c>
       <c r="C173" s="1">
         <v>172</v>
@@ -3313,10 +3438,10 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>172</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>301</v>
+        <v>187</v>
+      </c>
+      <c r="B174" t="s">
+        <v>179</v>
       </c>
       <c r="C174" s="1">
         <v>173</v>
@@ -3324,10 +3449,10 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>173</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>301</v>
+        <v>188</v>
+      </c>
+      <c r="B175" t="s">
+        <v>179</v>
       </c>
       <c r="C175" s="1">
         <v>174</v>
@@ -3335,10 +3460,10 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>174</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>301</v>
+        <v>189</v>
+      </c>
+      <c r="B176" t="s">
+        <v>179</v>
       </c>
       <c r="C176" s="1">
         <v>175</v>
@@ -3346,10 +3471,10 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>175</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>301</v>
+        <v>190</v>
+      </c>
+      <c r="B177" t="s">
+        <v>179</v>
       </c>
       <c r="C177" s="1">
         <v>176</v>
@@ -3357,10 +3482,10 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>176</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>302</v>
+        <v>191</v>
+      </c>
+      <c r="B178" t="s">
+        <v>179</v>
       </c>
       <c r="C178" s="1">
         <v>177</v>
@@ -3368,10 +3493,10 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>177</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>302</v>
+        <v>192</v>
+      </c>
+      <c r="B179" t="s">
+        <v>179</v>
       </c>
       <c r="C179" s="1">
         <v>178</v>
@@ -3379,10 +3504,10 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>178</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>302</v>
+        <v>193</v>
+      </c>
+      <c r="B180" t="s">
+        <v>179</v>
       </c>
       <c r="C180" s="1">
         <v>179</v>
@@ -3390,10 +3515,10 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>179</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>302</v>
+        <v>194</v>
+      </c>
+      <c r="B181" t="s">
+        <v>195</v>
       </c>
       <c r="C181" s="1">
         <v>180</v>
@@ -3401,10 +3526,10 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>180</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>314</v>
+        <v>196</v>
+      </c>
+      <c r="B182" t="s">
+        <v>195</v>
       </c>
       <c r="C182" s="1">
         <v>181</v>
@@ -3412,10 +3537,10 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>181</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>314</v>
+        <v>197</v>
+      </c>
+      <c r="B183" t="s">
+        <v>195</v>
       </c>
       <c r="C183" s="1">
         <v>182</v>
@@ -3423,10 +3548,10 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>182</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>315</v>
+        <v>198</v>
+      </c>
+      <c r="B184" t="s">
+        <v>195</v>
       </c>
       <c r="C184" s="1">
         <v>183</v>
@@ -3434,10 +3559,10 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>183</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>315</v>
+        <v>199</v>
+      </c>
+      <c r="B185" t="s">
+        <v>195</v>
       </c>
       <c r="C185" s="1">
         <v>184</v>
@@ -3445,10 +3570,10 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>184</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>315</v>
+        <v>200</v>
+      </c>
+      <c r="B186" t="s">
+        <v>195</v>
       </c>
       <c r="C186" s="1">
         <v>185</v>
@@ -3456,10 +3581,10 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>185</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>315</v>
+        <v>201</v>
+      </c>
+      <c r="B187" t="s">
+        <v>195</v>
       </c>
       <c r="C187" s="1">
         <v>186</v>
@@ -3467,10 +3592,10 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>186</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>316</v>
+        <v>202</v>
+      </c>
+      <c r="B188" t="s">
+        <v>195</v>
       </c>
       <c r="C188" s="1">
         <v>187</v>
@@ -3478,10 +3603,10 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>187</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>316</v>
+        <v>203</v>
+      </c>
+      <c r="B189" t="s">
+        <v>195</v>
       </c>
       <c r="C189" s="1">
         <v>188</v>
@@ -3489,10 +3614,10 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>188</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>316</v>
+        <v>204</v>
+      </c>
+      <c r="B190" t="s">
+        <v>195</v>
       </c>
       <c r="C190" s="1">
         <v>189</v>
@@ -3500,10 +3625,10 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>189</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>316</v>
+        <v>205</v>
+      </c>
+      <c r="B191" t="s">
+        <v>206</v>
       </c>
       <c r="C191" s="1">
         <v>190</v>
@@ -3511,10 +3636,10 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>190</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>316</v>
+        <v>207</v>
+      </c>
+      <c r="B192" t="s">
+        <v>208</v>
       </c>
       <c r="C192" s="1">
         <v>191</v>
@@ -3522,10 +3647,10 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>191</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>316</v>
+        <v>209</v>
+      </c>
+      <c r="B193" t="s">
+        <v>208</v>
       </c>
       <c r="C193" s="1">
         <v>192</v>
@@ -3533,10 +3658,10 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>192</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>317</v>
+        <v>210</v>
+      </c>
+      <c r="B194" t="s">
+        <v>208</v>
       </c>
       <c r="C194" s="1">
         <v>193</v>
@@ -3544,10 +3669,10 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>193</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>317</v>
+        <v>211</v>
+      </c>
+      <c r="B195" t="s">
+        <v>208</v>
       </c>
       <c r="C195" s="1">
         <v>194</v>
@@ -3555,10 +3680,10 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>194</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>317</v>
+        <v>212</v>
+      </c>
+      <c r="B196" t="s">
+        <v>208</v>
       </c>
       <c r="C196" s="1">
         <v>195</v>
@@ -3566,10 +3691,10 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>195</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>303</v>
+        <v>213</v>
+      </c>
+      <c r="B197" t="s">
+        <v>208</v>
       </c>
       <c r="C197" s="1">
         <v>196</v>
@@ -3577,10 +3702,10 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>196</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>303</v>
+        <v>214</v>
+      </c>
+      <c r="B198" t="s">
+        <v>208</v>
       </c>
       <c r="C198" s="1">
         <v>197</v>
@@ -3588,10 +3713,10 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>197</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>303</v>
+        <v>215</v>
+      </c>
+      <c r="B199" t="s">
+        <v>208</v>
       </c>
       <c r="C199" s="1">
         <v>198</v>
@@ -3599,10 +3724,10 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>198</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>303</v>
+        <v>216</v>
+      </c>
+      <c r="B200" t="s">
+        <v>208</v>
       </c>
       <c r="C200" s="1">
         <v>199</v>
@@ -3610,10 +3735,10 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>199</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>303</v>
+        <v>217</v>
+      </c>
+      <c r="B201" t="s">
+        <v>208</v>
       </c>
       <c r="C201" s="1">
         <v>200</v>
@@ -3621,10 +3746,10 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>200</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>303</v>
+        <v>218</v>
+      </c>
+      <c r="B202" t="s">
+        <v>208</v>
       </c>
       <c r="C202" s="1">
         <v>201</v>
@@ -3632,10 +3757,10 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>201</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>303</v>
+        <v>219</v>
+      </c>
+      <c r="B203" t="s">
+        <v>208</v>
       </c>
       <c r="C203" s="1">
         <v>202</v>
@@ -3643,10 +3768,10 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>202</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>303</v>
+        <v>220</v>
+      </c>
+      <c r="B204" t="s">
+        <v>221</v>
       </c>
       <c r="C204" s="1">
         <v>203</v>
@@ -3654,10 +3779,10 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>203</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>303</v>
+        <v>222</v>
+      </c>
+      <c r="B205" t="s">
+        <v>221</v>
       </c>
       <c r="C205" s="1">
         <v>204</v>
@@ -3665,10 +3790,10 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>204</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>303</v>
+        <v>223</v>
+      </c>
+      <c r="B206" t="s">
+        <v>221</v>
       </c>
       <c r="C206" s="1">
         <v>205</v>
@@ -3676,10 +3801,10 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>205</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>303</v>
+        <v>224</v>
+      </c>
+      <c r="B207" t="s">
+        <v>221</v>
       </c>
       <c r="C207" s="1">
         <v>206</v>
@@ -3687,10 +3812,10 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>206</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>303</v>
+        <v>225</v>
+      </c>
+      <c r="B208" t="s">
+        <v>221</v>
       </c>
       <c r="C208" s="1">
         <v>207</v>
@@ -3698,10 +3823,10 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>207</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>303</v>
+        <v>226</v>
+      </c>
+      <c r="B209" t="s">
+        <v>221</v>
       </c>
       <c r="C209" s="1">
         <v>208</v>
@@ -3709,10 +3834,10 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>208</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>322</v>
+        <v>227</v>
+      </c>
+      <c r="B210" t="s">
+        <v>221</v>
       </c>
       <c r="C210" s="1">
         <v>209</v>
@@ -3720,10 +3845,10 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>209</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>322</v>
+        <v>228</v>
+      </c>
+      <c r="B211" t="s">
+        <v>221</v>
       </c>
       <c r="C211" s="1">
         <v>210</v>
@@ -3731,10 +3856,10 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>210</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>322</v>
+        <v>229</v>
+      </c>
+      <c r="B212" t="s">
+        <v>221</v>
       </c>
       <c r="C212" s="1">
         <v>211</v>
@@ -3742,10 +3867,10 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>211</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>322</v>
+        <v>230</v>
+      </c>
+      <c r="B213" t="s">
+        <v>221</v>
       </c>
       <c r="C213" s="1">
         <v>212</v>
@@ -3753,10 +3878,10 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>212</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>304</v>
+        <v>231</v>
+      </c>
+      <c r="B214" t="s">
+        <v>221</v>
       </c>
       <c r="C214" s="1">
         <v>213</v>
@@ -3764,10 +3889,10 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>213</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>304</v>
+        <v>232</v>
+      </c>
+      <c r="B215" t="s">
+        <v>221</v>
       </c>
       <c r="C215" s="1">
         <v>214</v>
@@ -3775,10 +3900,10 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>214</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>304</v>
+        <v>233</v>
+      </c>
+      <c r="B216" t="s">
+        <v>221</v>
       </c>
       <c r="C216" s="1">
         <v>215</v>
@@ -3786,10 +3911,10 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>215</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>304</v>
+        <v>234</v>
+      </c>
+      <c r="B217" t="s">
+        <v>221</v>
       </c>
       <c r="C217" s="1">
         <v>216</v>
@@ -3797,10 +3922,10 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>216</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>304</v>
+        <v>235</v>
+      </c>
+      <c r="B218" t="s">
+        <v>221</v>
       </c>
       <c r="C218" s="1">
         <v>217</v>
@@ -3808,10 +3933,10 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>217</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>304</v>
+        <v>236</v>
+      </c>
+      <c r="B219" t="s">
+        <v>221</v>
       </c>
       <c r="C219" s="1">
         <v>218</v>
@@ -3819,10 +3944,10 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>218</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>304</v>
+        <v>237</v>
+      </c>
+      <c r="B220" t="s">
+        <v>221</v>
       </c>
       <c r="C220" s="1">
         <v>219</v>
@@ -3830,10 +3955,10 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>219</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>304</v>
+        <v>238</v>
+      </c>
+      <c r="B221" t="s">
+        <v>221</v>
       </c>
       <c r="C221" s="1">
         <v>220</v>
@@ -3841,10 +3966,10 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>220</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>304</v>
+        <v>239</v>
+      </c>
+      <c r="B222" t="s">
+        <v>221</v>
       </c>
       <c r="C222" s="1">
         <v>221</v>
@@ -3852,10 +3977,10 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
+        <v>240</v>
+      </c>
+      <c r="B223" t="s">
         <v>221</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>304</v>
       </c>
       <c r="C223" s="1">
         <v>222</v>
@@ -3863,10 +3988,10 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>222</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>304</v>
+        <v>241</v>
+      </c>
+      <c r="B224" t="s">
+        <v>242</v>
       </c>
       <c r="C224" s="1">
         <v>223</v>
@@ -3874,10 +3999,10 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>223</v>
-      </c>
-      <c r="B225" s="1" t="s">
-        <v>304</v>
+        <v>243</v>
+      </c>
+      <c r="B225" t="s">
+        <v>242</v>
       </c>
       <c r="C225" s="1">
         <v>224</v>
@@ -3885,10 +4010,10 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>224</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>304</v>
+        <v>244</v>
+      </c>
+      <c r="B226" t="s">
+        <v>242</v>
       </c>
       <c r="C226" s="1">
         <v>225</v>
@@ -3896,10 +4021,10 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>225</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>304</v>
+        <v>245</v>
+      </c>
+      <c r="B227" t="s">
+        <v>242</v>
       </c>
       <c r="C227" s="1">
         <v>226</v>
@@ -3907,10 +4032,10 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>226</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>318</v>
+        <v>246</v>
+      </c>
+      <c r="B228" t="s">
+        <v>247</v>
       </c>
       <c r="C228" s="1">
         <v>227</v>
@@ -3918,10 +4043,10 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>227</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>318</v>
+        <v>248</v>
+      </c>
+      <c r="B229" t="s">
+        <v>247</v>
       </c>
       <c r="C229" s="1">
         <v>228</v>
@@ -3929,10 +4054,10 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>228</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>318</v>
+        <v>249</v>
+      </c>
+      <c r="B230" t="s">
+        <v>250</v>
       </c>
       <c r="C230" s="1">
         <v>229</v>
@@ -3940,10 +4065,10 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>229</v>
-      </c>
-      <c r="B231" s="1" t="s">
-        <v>318</v>
+        <v>251</v>
+      </c>
+      <c r="B231" t="s">
+        <v>250</v>
       </c>
       <c r="C231" s="1">
         <v>230</v>
@@ -3951,10 +4076,10 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>230</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>318</v>
+        <v>252</v>
+      </c>
+      <c r="B232" t="s">
+        <v>250</v>
       </c>
       <c r="C232" s="1">
         <v>231</v>
@@ -3962,10 +4087,10 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>231</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>318</v>
+        <v>253</v>
+      </c>
+      <c r="B233" t="s">
+        <v>250</v>
       </c>
       <c r="C233" s="1">
         <v>232</v>
@@ -3973,10 +4098,10 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>232</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>305</v>
+        <v>254</v>
+      </c>
+      <c r="B234" t="s">
+        <v>255</v>
       </c>
       <c r="C234" s="1">
         <v>233</v>
@@ -3984,10 +4109,10 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>233</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>305</v>
+        <v>256</v>
+      </c>
+      <c r="B235" t="s">
+        <v>255</v>
       </c>
       <c r="C235" s="1">
         <v>234</v>
@@ -3995,10 +4120,10 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>234</v>
-      </c>
-      <c r="B236" s="1" t="s">
-        <v>305</v>
+        <v>257</v>
+      </c>
+      <c r="B236" t="s">
+        <v>255</v>
       </c>
       <c r="C236" s="1">
         <v>235</v>
@@ -4006,10 +4131,10 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>235</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>305</v>
+        <v>258</v>
+      </c>
+      <c r="B237" t="s">
+        <v>255</v>
       </c>
       <c r="C237" s="1">
         <v>236</v>
@@ -4017,10 +4142,10 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>236</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>306</v>
+        <v>259</v>
+      </c>
+      <c r="B238" t="s">
+        <v>255</v>
       </c>
       <c r="C238" s="1">
         <v>237</v>
@@ -4028,10 +4153,10 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>237</v>
-      </c>
-      <c r="B239" s="1" t="s">
-        <v>306</v>
+        <v>260</v>
+      </c>
+      <c r="B239" t="s">
+        <v>255</v>
       </c>
       <c r="C239" s="1">
         <v>238</v>
@@ -4039,10 +4164,10 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>238</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>307</v>
+        <v>261</v>
+      </c>
+      <c r="B240" t="s">
+        <v>262</v>
       </c>
       <c r="C240" s="1">
         <v>239</v>
@@ -4050,10 +4175,10 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>239</v>
-      </c>
-      <c r="B241" s="1" t="s">
-        <v>308</v>
+        <v>263</v>
+      </c>
+      <c r="B241" t="s">
+        <v>262</v>
       </c>
       <c r="C241" s="1">
         <v>240</v>
@@ -4061,10 +4186,10 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>240</v>
-      </c>
-      <c r="B242" s="1" t="s">
-        <v>308</v>
+        <v>264</v>
+      </c>
+      <c r="B242" t="s">
+        <v>262</v>
       </c>
       <c r="C242" s="1">
         <v>241</v>
@@ -4072,10 +4197,10 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>241</v>
-      </c>
-      <c r="B243" s="1" t="s">
-        <v>308</v>
+        <v>265</v>
+      </c>
+      <c r="B243" t="s">
+        <v>266</v>
       </c>
       <c r="C243" s="1">
         <v>242</v>
@@ -4083,10 +4208,10 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>242</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>308</v>
+        <v>267</v>
+      </c>
+      <c r="B244" t="s">
+        <v>266</v>
       </c>
       <c r="C244" s="1">
         <v>243</v>
@@ -4094,10 +4219,10 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>243</v>
-      </c>
-      <c r="B245" s="1" t="s">
-        <v>308</v>
+        <v>268</v>
+      </c>
+      <c r="B245" t="s">
+        <v>266</v>
       </c>
       <c r="C245" s="1">
         <v>244</v>
@@ -4105,10 +4230,10 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>244</v>
-      </c>
-      <c r="B246" s="1" t="s">
-        <v>308</v>
+        <v>269</v>
+      </c>
+      <c r="B246" t="s">
+        <v>266</v>
       </c>
       <c r="C246" s="1">
         <v>245</v>
@@ -4116,10 +4241,10 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>245</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>308</v>
+        <v>270</v>
+      </c>
+      <c r="B247" t="s">
+        <v>266</v>
       </c>
       <c r="C247" s="1">
         <v>246</v>
@@ -4127,10 +4252,10 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>246</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>308</v>
+        <v>271</v>
+      </c>
+      <c r="B248" t="s">
+        <v>266</v>
       </c>
       <c r="C248" s="1">
         <v>247</v>
@@ -4138,10 +4263,10 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>247</v>
-      </c>
-      <c r="B249" s="1" t="s">
-        <v>308</v>
+        <v>272</v>
+      </c>
+      <c r="B249" t="s">
+        <v>266</v>
       </c>
       <c r="C249" s="1">
         <v>248</v>
@@ -4149,10 +4274,10 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>248</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>308</v>
+        <v>273</v>
+      </c>
+      <c r="B250" t="s">
+        <v>266</v>
       </c>
       <c r="C250" s="1">
         <v>249</v>
@@ -4160,10 +4285,10 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>249</v>
-      </c>
-      <c r="B251" s="1" t="s">
-        <v>319</v>
+        <v>274</v>
+      </c>
+      <c r="B251" t="s">
+        <v>266</v>
       </c>
       <c r="C251" s="1">
         <v>250</v>
@@ -4171,10 +4296,10 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>250</v>
-      </c>
-      <c r="B252" s="1" t="s">
-        <v>319</v>
+        <v>275</v>
+      </c>
+      <c r="B252" t="s">
+        <v>266</v>
       </c>
       <c r="C252" s="1">
         <v>251</v>
@@ -4182,10 +4307,10 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>251</v>
-      </c>
-      <c r="B253" s="1" t="s">
-        <v>309</v>
+        <v>276</v>
+      </c>
+      <c r="B253" t="s">
+        <v>266</v>
       </c>
       <c r="C253" s="1">
         <v>252</v>
@@ -4193,10 +4318,10 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>252</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>309</v>
+        <v>277</v>
+      </c>
+      <c r="B254" t="s">
+        <v>266</v>
       </c>
       <c r="C254" s="1">
         <v>253</v>
@@ -4204,10 +4329,10 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>253</v>
-      </c>
-      <c r="B255" s="1" t="s">
-        <v>309</v>
+        <v>278</v>
+      </c>
+      <c r="B255" t="s">
+        <v>266</v>
       </c>
       <c r="C255" s="1">
         <v>254</v>
@@ -4215,10 +4340,10 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>254</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>309</v>
+        <v>279</v>
+      </c>
+      <c r="B256" t="s">
+        <v>280</v>
       </c>
       <c r="C256" s="1">
         <v>255</v>
@@ -4226,10 +4351,10 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>255</v>
-      </c>
-      <c r="B257" s="1" t="s">
-        <v>309</v>
+        <v>281</v>
+      </c>
+      <c r="B257" t="s">
+        <v>280</v>
       </c>
       <c r="C257" s="1">
         <v>256</v>
@@ -4237,10 +4362,10 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>256</v>
-      </c>
-      <c r="B258" s="1" t="s">
-        <v>309</v>
+        <v>282</v>
+      </c>
+      <c r="B258" t="s">
+        <v>280</v>
       </c>
       <c r="C258" s="1">
         <v>257</v>
@@ -4248,10 +4373,10 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>257</v>
-      </c>
-      <c r="B259" s="1" t="s">
-        <v>309</v>
+        <v>283</v>
+      </c>
+      <c r="B259" t="s">
+        <v>280</v>
       </c>
       <c r="C259" s="1">
         <v>258</v>
@@ -4259,10 +4384,10 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>258</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>309</v>
+        <v>284</v>
+      </c>
+      <c r="B260" t="s">
+        <v>285</v>
       </c>
       <c r="C260" s="1">
         <v>259</v>
@@ -4270,10 +4395,10 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>259</v>
-      </c>
-      <c r="B261" s="1" t="s">
-        <v>309</v>
+        <v>286</v>
+      </c>
+      <c r="B261" t="s">
+        <v>285</v>
       </c>
       <c r="C261" s="1">
         <v>260</v>
@@ -4281,10 +4406,10 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>260</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>309</v>
+        <v>287</v>
+      </c>
+      <c r="B262" t="s">
+        <v>285</v>
       </c>
       <c r="C262" s="1">
         <v>261</v>
@@ -4292,10 +4417,10 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>261</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>309</v>
+        <v>288</v>
+      </c>
+      <c r="B263" t="s">
+        <v>285</v>
       </c>
       <c r="C263" s="1">
         <v>262</v>
@@ -4303,10 +4428,10 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>262</v>
-      </c>
-      <c r="B264" s="1" t="s">
-        <v>309</v>
+        <v>289</v>
+      </c>
+      <c r="B264" t="s">
+        <v>285</v>
       </c>
       <c r="C264" s="1">
         <v>263</v>
@@ -4314,10 +4439,10 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>263</v>
-      </c>
-      <c r="B265" s="1" t="s">
-        <v>309</v>
+        <v>290</v>
+      </c>
+      <c r="B265" t="s">
+        <v>285</v>
       </c>
       <c r="C265" s="1">
         <v>264</v>
@@ -4325,10 +4450,10 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>264</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>309</v>
+        <v>291</v>
+      </c>
+      <c r="B266" t="s">
+        <v>285</v>
       </c>
       <c r="C266" s="1">
         <v>265</v>
@@ -4336,10 +4461,10 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>265</v>
-      </c>
-      <c r="B267" s="1" t="s">
-        <v>323</v>
+        <v>292</v>
+      </c>
+      <c r="B267" t="s">
+        <v>285</v>
       </c>
       <c r="C267" s="1">
         <v>266</v>
@@ -4347,10 +4472,10 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>266</v>
-      </c>
-      <c r="B268" s="1" t="s">
-        <v>323</v>
+        <v>293</v>
+      </c>
+      <c r="B268" t="s">
+        <v>285</v>
       </c>
       <c r="C268" s="1">
         <v>267</v>
@@ -4358,10 +4483,10 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>267</v>
-      </c>
-      <c r="B269" s="1" t="s">
-        <v>323</v>
+        <v>294</v>
+      </c>
+      <c r="B269" t="s">
+        <v>285</v>
       </c>
       <c r="C269" s="1">
         <v>268</v>
@@ -4369,10 +4494,10 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>268</v>
-      </c>
-      <c r="B270" s="1" t="s">
-        <v>323</v>
+        <v>295</v>
+      </c>
+      <c r="B270" t="s">
+        <v>285</v>
       </c>
       <c r="C270" s="1">
         <v>269</v>
@@ -4380,10 +4505,10 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>269</v>
-      </c>
-      <c r="B271" s="1" t="s">
-        <v>323</v>
+        <v>296</v>
+      </c>
+      <c r="B271" t="s">
+        <v>285</v>
       </c>
       <c r="C271" s="1">
         <v>270</v>
@@ -4391,10 +4516,10 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>270</v>
-      </c>
-      <c r="B272" s="1" t="s">
-        <v>323</v>
+        <v>297</v>
+      </c>
+      <c r="B272" t="s">
+        <v>285</v>
       </c>
       <c r="C272" s="1">
         <v>271</v>
@@ -4402,10 +4527,10 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>271</v>
-      </c>
-      <c r="B273" s="1" t="s">
-        <v>323</v>
+        <v>298</v>
+      </c>
+      <c r="B273" t="s">
+        <v>285</v>
       </c>
       <c r="C273" s="1">
         <v>272</v>
@@ -4413,10 +4538,10 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>272</v>
-      </c>
-      <c r="B274" s="1" t="s">
-        <v>323</v>
+        <v>299</v>
+      </c>
+      <c r="B274" t="s">
+        <v>300</v>
       </c>
       <c r="C274" s="1">
         <v>273</v>
@@ -4424,10 +4549,10 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>273</v>
-      </c>
-      <c r="B275" s="1" t="s">
-        <v>320</v>
+        <v>301</v>
+      </c>
+      <c r="B275" t="s">
+        <v>300</v>
       </c>
       <c r="C275" s="1">
         <v>274</v>
@@ -4435,10 +4560,10 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>274</v>
-      </c>
-      <c r="B276" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
+      </c>
+      <c r="B276" t="s">
+        <v>300</v>
       </c>
       <c r="C276" s="1">
         <v>275</v>
@@ -4446,10 +4571,10 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>275</v>
-      </c>
-      <c r="B277" s="1" t="s">
-        <v>320</v>
+        <v>303</v>
+      </c>
+      <c r="B277" t="s">
+        <v>300</v>
       </c>
       <c r="C277" s="1">
         <v>276</v>
@@ -4457,10 +4582,10 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>276</v>
-      </c>
-      <c r="B278" s="1" t="s">
-        <v>320</v>
+        <v>304</v>
+      </c>
+      <c r="B278" t="s">
+        <v>300</v>
       </c>
       <c r="C278" s="1">
         <v>277</v>
@@ -4468,10 +4593,10 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>277</v>
-      </c>
-      <c r="B279" s="1" t="s">
-        <v>320</v>
+        <v>305</v>
+      </c>
+      <c r="B279" t="s">
+        <v>300</v>
       </c>
       <c r="C279" s="1">
         <v>278</v>
@@ -4479,10 +4604,10 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>278</v>
-      </c>
-      <c r="B280" s="1" t="s">
-        <v>320</v>
+        <v>306</v>
+      </c>
+      <c r="B280" t="s">
+        <v>307</v>
       </c>
       <c r="C280" s="1">
         <v>279</v>
@@ -4490,10 +4615,10 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>279</v>
-      </c>
-      <c r="B281" s="1" t="s">
-        <v>320</v>
+        <v>308</v>
+      </c>
+      <c r="B281" t="s">
+        <v>307</v>
       </c>
       <c r="C281" s="1">
         <v>280</v>
@@ -4501,10 +4626,10 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>280</v>
-      </c>
-      <c r="B282" s="1" t="s">
-        <v>320</v>
+        <v>309</v>
+      </c>
+      <c r="B282" t="s">
+        <v>307</v>
       </c>
       <c r="C282" s="1">
         <v>281</v>
@@ -4512,10 +4637,10 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>281</v>
-      </c>
-      <c r="B283" s="1" t="s">
         <v>310</v>
+      </c>
+      <c r="B283" t="s">
+        <v>307</v>
       </c>
       <c r="C283" s="1">
         <v>282</v>
@@ -4523,10 +4648,10 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>282</v>
-      </c>
-      <c r="B284" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
+      </c>
+      <c r="B284" t="s">
+        <v>312</v>
       </c>
       <c r="C284" s="1">
         <v>283</v>
@@ -4534,10 +4659,10 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>283</v>
-      </c>
-      <c r="B285" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
+      </c>
+      <c r="B285" t="s">
+        <v>312</v>
       </c>
       <c r="C285" s="1">
         <v>284</v>
@@ -4545,10 +4670,10 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>284</v>
-      </c>
-      <c r="B286" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
+      </c>
+      <c r="B286" t="s">
+        <v>315</v>
       </c>
       <c r="C286" s="1">
         <v>285</v>
@@ -4556,10 +4681,10 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>285</v>
-      </c>
-      <c r="B287" s="1" t="s">
-        <v>310</v>
+        <v>316</v>
+      </c>
+      <c r="B287" t="s">
+        <v>317</v>
       </c>
       <c r="C287" s="1">
         <v>286</v>
@@ -4567,10 +4692,10 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>286</v>
-      </c>
-      <c r="B288" s="1" t="s">
-        <v>310</v>
+        <v>318</v>
+      </c>
+      <c r="B288" t="s">
+        <v>317</v>
       </c>
       <c r="C288" s="1">
         <v>287</v>
@@ -4578,10 +4703,10 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>287</v>
-      </c>
-      <c r="B289" s="1" t="s">
-        <v>310</v>
+        <v>319</v>
+      </c>
+      <c r="B289" t="s">
+        <v>317</v>
       </c>
       <c r="C289" s="1">
         <v>288</v>
@@ -4589,13 +4714,574 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>288</v>
-      </c>
-      <c r="B290" s="1" t="s">
-        <v>310</v>
+        <v>320</v>
+      </c>
+      <c r="B290" t="s">
+        <v>317</v>
       </c>
       <c r="C290" s="1">
         <v>289</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>321</v>
+      </c>
+      <c r="B291" t="s">
+        <v>317</v>
+      </c>
+      <c r="C291" s="1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>322</v>
+      </c>
+      <c r="B292" t="s">
+        <v>317</v>
+      </c>
+      <c r="C292" s="1">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>323</v>
+      </c>
+      <c r="B293" t="s">
+        <v>317</v>
+      </c>
+      <c r="C293" s="1">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>324</v>
+      </c>
+      <c r="B294" t="s">
+        <v>317</v>
+      </c>
+      <c r="C294" s="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>325</v>
+      </c>
+      <c r="B295" t="s">
+        <v>317</v>
+      </c>
+      <c r="C295" s="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>326</v>
+      </c>
+      <c r="B296" t="s">
+        <v>317</v>
+      </c>
+      <c r="C296" s="1">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>327</v>
+      </c>
+      <c r="B297" t="s">
+        <v>328</v>
+      </c>
+      <c r="C297" s="1">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>329</v>
+      </c>
+      <c r="B298" t="s">
+        <v>328</v>
+      </c>
+      <c r="C298" s="1">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>330</v>
+      </c>
+      <c r="B299" t="s">
+        <v>331</v>
+      </c>
+      <c r="C299" s="1">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>332</v>
+      </c>
+      <c r="B300" t="s">
+        <v>331</v>
+      </c>
+      <c r="C300" s="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>333</v>
+      </c>
+      <c r="B301" t="s">
+        <v>331</v>
+      </c>
+      <c r="C301" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>334</v>
+      </c>
+      <c r="B302" t="s">
+        <v>331</v>
+      </c>
+      <c r="C302" s="1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>335</v>
+      </c>
+      <c r="B303" t="s">
+        <v>331</v>
+      </c>
+      <c r="C303" s="1">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>336</v>
+      </c>
+      <c r="B304" t="s">
+        <v>331</v>
+      </c>
+      <c r="C304" s="1">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>337</v>
+      </c>
+      <c r="B305" t="s">
+        <v>331</v>
+      </c>
+      <c r="C305" s="1">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>338</v>
+      </c>
+      <c r="B306" t="s">
+        <v>331</v>
+      </c>
+      <c r="C306" s="1">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>339</v>
+      </c>
+      <c r="B307" t="s">
+        <v>331</v>
+      </c>
+      <c r="C307" s="1">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>340</v>
+      </c>
+      <c r="B308" t="s">
+        <v>331</v>
+      </c>
+      <c r="C308" s="1">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>341</v>
+      </c>
+      <c r="B309" t="s">
+        <v>331</v>
+      </c>
+      <c r="C309" s="1">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>342</v>
+      </c>
+      <c r="B310" t="s">
+        <v>331</v>
+      </c>
+      <c r="C310" s="1">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>343</v>
+      </c>
+      <c r="B311" t="s">
+        <v>331</v>
+      </c>
+      <c r="C311" s="1">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>344</v>
+      </c>
+      <c r="B312" t="s">
+        <v>331</v>
+      </c>
+      <c r="C312" s="1">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>345</v>
+      </c>
+      <c r="B313" t="s">
+        <v>346</v>
+      </c>
+      <c r="C313" s="1">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>347</v>
+      </c>
+      <c r="B314" t="s">
+        <v>346</v>
+      </c>
+      <c r="C314" s="1">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>348</v>
+      </c>
+      <c r="B315" t="s">
+        <v>346</v>
+      </c>
+      <c r="C315" s="1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>349</v>
+      </c>
+      <c r="B316" t="s">
+        <v>346</v>
+      </c>
+      <c r="C316" s="1">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>350</v>
+      </c>
+      <c r="B317" t="s">
+        <v>346</v>
+      </c>
+      <c r="C317" s="1">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>351</v>
+      </c>
+      <c r="B318" t="s">
+        <v>346</v>
+      </c>
+      <c r="C318" s="1">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>352</v>
+      </c>
+      <c r="B319" t="s">
+        <v>346</v>
+      </c>
+      <c r="C319" s="1">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>353</v>
+      </c>
+      <c r="B320" t="s">
+        <v>346</v>
+      </c>
+      <c r="C320" s="1">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>354</v>
+      </c>
+      <c r="B321" t="s">
+        <v>355</v>
+      </c>
+      <c r="C321" s="1">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>356</v>
+      </c>
+      <c r="B322" t="s">
+        <v>355</v>
+      </c>
+      <c r="C322" s="1">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>357</v>
+      </c>
+      <c r="B323" t="s">
+        <v>355</v>
+      </c>
+      <c r="C323" s="1">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>358</v>
+      </c>
+      <c r="B324" t="s">
+        <v>355</v>
+      </c>
+      <c r="C324" s="1">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>359</v>
+      </c>
+      <c r="B325" t="s">
+        <v>355</v>
+      </c>
+      <c r="C325" s="1">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>360</v>
+      </c>
+      <c r="B326" t="s">
+        <v>355</v>
+      </c>
+      <c r="C326" s="1">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>361</v>
+      </c>
+      <c r="B327" t="s">
+        <v>355</v>
+      </c>
+      <c r="C327" s="1">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>362</v>
+      </c>
+      <c r="B328" t="s">
+        <v>355</v>
+      </c>
+      <c r="C328" s="1">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>363</v>
+      </c>
+      <c r="B329" t="s">
+        <v>355</v>
+      </c>
+      <c r="C329" s="1">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>364</v>
+      </c>
+      <c r="B330" t="s">
+        <v>355</v>
+      </c>
+      <c r="C330" s="1">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>365</v>
+      </c>
+      <c r="B331" t="s">
+        <v>355</v>
+      </c>
+      <c r="C331" s="1">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A332" t="s">
+        <v>366</v>
+      </c>
+      <c r="B332" t="s">
+        <v>355</v>
+      </c>
+      <c r="C332" s="1">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A333" t="s">
+        <v>367</v>
+      </c>
+      <c r="B333" t="s">
+        <v>355</v>
+      </c>
+      <c r="C333" s="1">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A334" t="s">
+        <v>368</v>
+      </c>
+      <c r="B334" t="s">
+        <v>369</v>
+      </c>
+      <c r="C334" s="1">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A335" t="s">
+        <v>370</v>
+      </c>
+      <c r="B335" t="s">
+        <v>369</v>
+      </c>
+      <c r="C335" s="1">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A336" t="s">
+        <v>371</v>
+      </c>
+      <c r="B336" t="s">
+        <v>369</v>
+      </c>
+      <c r="C336" s="1">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A337" t="s">
+        <v>372</v>
+      </c>
+      <c r="B337" t="s">
+        <v>369</v>
+      </c>
+      <c r="C337" s="1">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A338" t="s">
+        <v>373</v>
+      </c>
+      <c r="B338" t="s">
+        <v>369</v>
+      </c>
+      <c r="C338" s="1">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A339" t="s">
+        <v>374</v>
+      </c>
+      <c r="B339" t="s">
+        <v>369</v>
+      </c>
+      <c r="C339" s="1">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A340" t="s">
+        <v>375</v>
+      </c>
+      <c r="B340" t="s">
+        <v>369</v>
+      </c>
+      <c r="C340" s="1">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A341" t="s">
+        <v>376</v>
+      </c>
+      <c r="B341" t="s">
+        <v>369</v>
+      </c>
+      <c r="C341" s="1">
+        <v>340</v>
       </c>
     </row>
   </sheetData>
